--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
     <sheet name="金色" sheetId="2" r:id="rId2"/>
+    <sheet name="暗金" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="129">
   <si>
     <t>_Id</t>
   </si>
@@ -394,6 +395,27 @@
   </si>
   <si>
     <t>50000104</t>
+  </si>
+  <si>
+    <t>50000105</t>
+  </si>
+  <si>
+    <t>50000106</t>
+  </si>
+  <si>
+    <t>50000107</t>
+  </si>
+  <si>
+    <t>50000108</t>
+  </si>
+  <si>
+    <t>50000109</t>
+  </si>
+  <si>
+    <t>50000110</t>
+  </si>
+  <si>
+    <t>50000111</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1374,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L109"/>
+  <dimension ref="C3:L165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -4155,6 +4177,1462 @@
         <v>80</v>
       </c>
     </row>
+    <row r="110" customHeight="1" spans="3:10">
+      <c r="C110" s="1">
+        <v>105</v>
+      </c>
+      <c r="D110" s="1">
+        <v>6</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="1">
+        <v>14</v>
+      </c>
+      <c r="G110" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H110" s="1">
+        <v>92</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J110" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:10">
+      <c r="C111" s="1">
+        <v>106</v>
+      </c>
+      <c r="D111" s="1">
+        <v>6</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="1">
+        <v>14</v>
+      </c>
+      <c r="G111" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H111" s="1">
+        <v>92</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J111" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:10">
+      <c r="C112" s="1">
+        <v>107</v>
+      </c>
+      <c r="D112" s="1">
+        <v>6</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" s="1">
+        <v>14</v>
+      </c>
+      <c r="G112" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H112" s="1">
+        <v>92</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J112" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:10">
+      <c r="C113" s="1">
+        <v>108</v>
+      </c>
+      <c r="D113" s="1">
+        <v>6</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F113" s="1">
+        <v>14</v>
+      </c>
+      <c r="G113" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H113" s="1">
+        <v>92</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J113" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:10">
+      <c r="C114" s="1">
+        <v>109</v>
+      </c>
+      <c r="D114" s="1">
+        <v>6</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F114" s="1">
+        <v>14</v>
+      </c>
+      <c r="G114" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H114" s="1">
+        <v>92</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J114" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:10">
+      <c r="C115" s="1">
+        <v>110</v>
+      </c>
+      <c r="D115" s="1">
+        <v>6</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F115" s="1">
+        <v>14</v>
+      </c>
+      <c r="G115" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H115" s="1">
+        <v>92</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J115" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:10">
+      <c r="C116" s="1">
+        <v>111</v>
+      </c>
+      <c r="D116" s="1">
+        <v>6</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F116" s="1">
+        <v>14</v>
+      </c>
+      <c r="G116" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H116" s="1">
+        <v>92</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J116" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:10">
+      <c r="C117" s="1">
+        <v>112</v>
+      </c>
+      <c r="D117" s="1">
+        <v>6</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F117" s="1">
+        <v>14</v>
+      </c>
+      <c r="G117" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H117" s="1">
+        <v>92</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J117" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:10">
+      <c r="C118" s="1">
+        <v>113</v>
+      </c>
+      <c r="D118" s="1">
+        <v>6</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" s="1">
+        <v>15</v>
+      </c>
+      <c r="G118" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H118" s="1">
+        <v>106</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J118" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:10">
+      <c r="C119" s="1">
+        <v>114</v>
+      </c>
+      <c r="D119" s="1">
+        <v>6</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119" s="1">
+        <v>15</v>
+      </c>
+      <c r="G119" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H119" s="1">
+        <v>106</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J119" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:10">
+      <c r="C120" s="1">
+        <v>115</v>
+      </c>
+      <c r="D120" s="1">
+        <v>6</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F120" s="1">
+        <v>15</v>
+      </c>
+      <c r="G120" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H120" s="1">
+        <v>106</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J120" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:10">
+      <c r="C121" s="1">
+        <v>116</v>
+      </c>
+      <c r="D121" s="1">
+        <v>6</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F121" s="1">
+        <v>15</v>
+      </c>
+      <c r="G121" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H121" s="1">
+        <v>106</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J121" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:10">
+      <c r="C122" s="1">
+        <v>117</v>
+      </c>
+      <c r="D122" s="1">
+        <v>6</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F122" s="1">
+        <v>15</v>
+      </c>
+      <c r="G122" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H122" s="1">
+        <v>106</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J122" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:10">
+      <c r="C123" s="1">
+        <v>118</v>
+      </c>
+      <c r="D123" s="1">
+        <v>6</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F123" s="1">
+        <v>15</v>
+      </c>
+      <c r="G123" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H123" s="1">
+        <v>106</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J123" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:10">
+      <c r="C124" s="1">
+        <v>119</v>
+      </c>
+      <c r="D124" s="1">
+        <v>6</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F124" s="1">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H124" s="1">
+        <v>106</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J124" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:10">
+      <c r="C125" s="1">
+        <v>120</v>
+      </c>
+      <c r="D125" s="1">
+        <v>6</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="1">
+        <v>15</v>
+      </c>
+      <c r="G125" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H125" s="1">
+        <v>106</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J125" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:10">
+      <c r="C126" s="1">
+        <v>121</v>
+      </c>
+      <c r="D126" s="1">
+        <v>6</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="1">
+        <v>16</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H126" s="1">
+        <v>121</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J126" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:10">
+      <c r="C127" s="1">
+        <v>122</v>
+      </c>
+      <c r="D127" s="1">
+        <v>6</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" s="1">
+        <v>16</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H127" s="1">
+        <v>121</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J127" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:10">
+      <c r="C128" s="1">
+        <v>123</v>
+      </c>
+      <c r="D128" s="1">
+        <v>6</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F128" s="1">
+        <v>16</v>
+      </c>
+      <c r="G128" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H128" s="1">
+        <v>121</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J128" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:10">
+      <c r="C129" s="1">
+        <v>124</v>
+      </c>
+      <c r="D129" s="1">
+        <v>6</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F129" s="1">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H129" s="1">
+        <v>121</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J129" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:10">
+      <c r="C130" s="1">
+        <v>125</v>
+      </c>
+      <c r="D130" s="1">
+        <v>6</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F130" s="1">
+        <v>16</v>
+      </c>
+      <c r="G130" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H130" s="1">
+        <v>121</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J130" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:10">
+      <c r="C131" s="1">
+        <v>126</v>
+      </c>
+      <c r="D131" s="1">
+        <v>6</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F131" s="1">
+        <v>16</v>
+      </c>
+      <c r="G131" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H131" s="1">
+        <v>121</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J131" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:10">
+      <c r="C132" s="1">
+        <v>127</v>
+      </c>
+      <c r="D132" s="1">
+        <v>6</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="1">
+        <v>16</v>
+      </c>
+      <c r="G132" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H132" s="1">
+        <v>121</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J132" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:10">
+      <c r="C133" s="1">
+        <v>128</v>
+      </c>
+      <c r="D133" s="1">
+        <v>6</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F133" s="1">
+        <v>16</v>
+      </c>
+      <c r="G133" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H133" s="1">
+        <v>121</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J133" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:10">
+      <c r="C134" s="1">
+        <v>129</v>
+      </c>
+      <c r="D134" s="1">
+        <v>6</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F134" s="1">
+        <v>17</v>
+      </c>
+      <c r="G134" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H134" s="1">
+        <v>137</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J134" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:10">
+      <c r="C135" s="1">
+        <v>130</v>
+      </c>
+      <c r="D135" s="1">
+        <v>6</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" s="1">
+        <v>17</v>
+      </c>
+      <c r="G135" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H135" s="1">
+        <v>137</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J135" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:10">
+      <c r="C136" s="1">
+        <v>131</v>
+      </c>
+      <c r="D136" s="1">
+        <v>6</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F136" s="1">
+        <v>17</v>
+      </c>
+      <c r="G136" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H136" s="1">
+        <v>137</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J136" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:10">
+      <c r="C137" s="1">
+        <v>132</v>
+      </c>
+      <c r="D137" s="1">
+        <v>6</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F137" s="1">
+        <v>17</v>
+      </c>
+      <c r="G137" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H137" s="1">
+        <v>137</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J137" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:10">
+      <c r="C138" s="1">
+        <v>133</v>
+      </c>
+      <c r="D138" s="1">
+        <v>6</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F138" s="1">
+        <v>17</v>
+      </c>
+      <c r="G138" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H138" s="1">
+        <v>137</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J138" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:10">
+      <c r="C139" s="1">
+        <v>134</v>
+      </c>
+      <c r="D139" s="1">
+        <v>6</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F139" s="1">
+        <v>17</v>
+      </c>
+      <c r="G139" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H139" s="1">
+        <v>137</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J139" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:10">
+      <c r="C140" s="1">
+        <v>135</v>
+      </c>
+      <c r="D140" s="1">
+        <v>6</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F140" s="1">
+        <v>17</v>
+      </c>
+      <c r="G140" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H140" s="1">
+        <v>137</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J140" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:10">
+      <c r="C141" s="1">
+        <v>136</v>
+      </c>
+      <c r="D141" s="1">
+        <v>6</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F141" s="1">
+        <v>17</v>
+      </c>
+      <c r="G141" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H141" s="1">
+        <v>137</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J141" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:10">
+      <c r="C142" s="1">
+        <v>137</v>
+      </c>
+      <c r="D142" s="1">
+        <v>6</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F142" s="1">
+        <v>18</v>
+      </c>
+      <c r="G142" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H142" s="1">
+        <v>154</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J142" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:10">
+      <c r="C143" s="1">
+        <v>138</v>
+      </c>
+      <c r="D143" s="1">
+        <v>6</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" s="1">
+        <v>18</v>
+      </c>
+      <c r="G143" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H143" s="1">
+        <v>154</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J143" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:10">
+      <c r="C144" s="1">
+        <v>139</v>
+      </c>
+      <c r="D144" s="1">
+        <v>6</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F144" s="1">
+        <v>18</v>
+      </c>
+      <c r="G144" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H144" s="1">
+        <v>154</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J144" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:10">
+      <c r="C145" s="1">
+        <v>140</v>
+      </c>
+      <c r="D145" s="1">
+        <v>6</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F145" s="1">
+        <v>18</v>
+      </c>
+      <c r="G145" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H145" s="1">
+        <v>154</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J145" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:10">
+      <c r="C146" s="1">
+        <v>141</v>
+      </c>
+      <c r="D146" s="1">
+        <v>6</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F146" s="1">
+        <v>18</v>
+      </c>
+      <c r="G146" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H146" s="1">
+        <v>154</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J146" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:10">
+      <c r="C147" s="1">
+        <v>142</v>
+      </c>
+      <c r="D147" s="1">
+        <v>6</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F147" s="1">
+        <v>18</v>
+      </c>
+      <c r="G147" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H147" s="1">
+        <v>154</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J147" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:10">
+      <c r="C148" s="1">
+        <v>143</v>
+      </c>
+      <c r="D148" s="1">
+        <v>6</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="1">
+        <v>18</v>
+      </c>
+      <c r="G148" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H148" s="1">
+        <v>154</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J148" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:10">
+      <c r="C149" s="1">
+        <v>144</v>
+      </c>
+      <c r="D149" s="1">
+        <v>6</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="1">
+        <v>18</v>
+      </c>
+      <c r="G149" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H149" s="1">
+        <v>154</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J149" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:10">
+      <c r="C150" s="1">
+        <v>145</v>
+      </c>
+      <c r="D150" s="1">
+        <v>6</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" s="1">
+        <v>19</v>
+      </c>
+      <c r="G150" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H150" s="1">
+        <v>172</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J150" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:10">
+      <c r="C151" s="1">
+        <v>146</v>
+      </c>
+      <c r="D151" s="1">
+        <v>6</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="1">
+        <v>19</v>
+      </c>
+      <c r="G151" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H151" s="1">
+        <v>172</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J151" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:10">
+      <c r="C152" s="1">
+        <v>147</v>
+      </c>
+      <c r="D152" s="1">
+        <v>6</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F152" s="1">
+        <v>19</v>
+      </c>
+      <c r="G152" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H152" s="1">
+        <v>172</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J152" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:10">
+      <c r="C153" s="1">
+        <v>148</v>
+      </c>
+      <c r="D153" s="1">
+        <v>6</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153" s="1">
+        <v>19</v>
+      </c>
+      <c r="G153" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H153" s="1">
+        <v>172</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J153" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:10">
+      <c r="C154" s="1">
+        <v>149</v>
+      </c>
+      <c r="D154" s="1">
+        <v>6</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F154" s="1">
+        <v>19</v>
+      </c>
+      <c r="G154" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H154" s="1">
+        <v>172</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J154" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:10">
+      <c r="C155" s="1">
+        <v>150</v>
+      </c>
+      <c r="D155" s="1">
+        <v>6</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F155" s="1">
+        <v>19</v>
+      </c>
+      <c r="G155" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H155" s="1">
+        <v>172</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J155" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:10">
+      <c r="C156" s="1">
+        <v>151</v>
+      </c>
+      <c r="D156" s="1">
+        <v>6</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="1">
+        <v>19</v>
+      </c>
+      <c r="G156" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H156" s="1">
+        <v>172</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J156" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:10">
+      <c r="C157" s="1">
+        <v>152</v>
+      </c>
+      <c r="D157" s="1">
+        <v>6</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F157" s="1">
+        <v>19</v>
+      </c>
+      <c r="G157" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H157" s="1">
+        <v>172</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J157" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="3:10">
+      <c r="C158" s="1">
+        <v>153</v>
+      </c>
+      <c r="D158" s="1">
+        <v>6</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" s="1">
+        <v>20</v>
+      </c>
+      <c r="G158" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H158" s="1">
+        <v>191</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J158" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="3:10">
+      <c r="C159" s="1">
+        <v>154</v>
+      </c>
+      <c r="D159" s="1">
+        <v>6</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159" s="1">
+        <v>20</v>
+      </c>
+      <c r="G159" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H159" s="1">
+        <v>191</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J159" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="3:10">
+      <c r="C160" s="1">
+        <v>155</v>
+      </c>
+      <c r="D160" s="1">
+        <v>6</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F160" s="1">
+        <v>20</v>
+      </c>
+      <c r="G160" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H160" s="1">
+        <v>191</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J160" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:10">
+      <c r="C161" s="1">
+        <v>156</v>
+      </c>
+      <c r="D161" s="1">
+        <v>6</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F161" s="1">
+        <v>20</v>
+      </c>
+      <c r="G161" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H161" s="1">
+        <v>191</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J161" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="3:10">
+      <c r="C162" s="1">
+        <v>157</v>
+      </c>
+      <c r="D162" s="1">
+        <v>6</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F162" s="1">
+        <v>20</v>
+      </c>
+      <c r="G162" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H162" s="1">
+        <v>191</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J162" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="3:10">
+      <c r="C163" s="1">
+        <v>158</v>
+      </c>
+      <c r="D163" s="1">
+        <v>6</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F163" s="1">
+        <v>20</v>
+      </c>
+      <c r="G163" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H163" s="1">
+        <v>191</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J163" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="3:10">
+      <c r="C164" s="1">
+        <v>159</v>
+      </c>
+      <c r="D164" s="1">
+        <v>6</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="1">
+        <v>20</v>
+      </c>
+      <c r="G164" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H164" s="1">
+        <v>191</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J164" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="3:10">
+      <c r="C165" s="1">
+        <v>160</v>
+      </c>
+      <c r="D165" s="1">
+        <v>6</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F165" s="1">
+        <v>20</v>
+      </c>
+      <c r="G165" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H165" s="1">
+        <v>191</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J165" s="1">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">
@@ -4167,6 +5645,3087 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:L117"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="11.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" ref="J6:J61" si="0">H6*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C12" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1">
+        <v>29</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H14" s="1">
+        <v>40</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C15" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>22</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H15" s="1">
+        <v>40</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C16" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1">
+        <v>23</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H16" s="1">
+        <v>40</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C17" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H17" s="1">
+        <v>40</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C18" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7</v>
+      </c>
+      <c r="E18" s="1">
+        <v>25</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H18" s="1">
+        <v>40</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C19" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1">
+        <v>27</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H19" s="1">
+        <v>40</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C20" s="1">
+        <v>1015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>7</v>
+      </c>
+      <c r="E20" s="1">
+        <v>29</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H20" s="1">
+        <v>40</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C21" s="1">
+        <v>1016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>7</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H21" s="1">
+        <v>40</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C22" s="1">
+        <v>1017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1">
+        <v>21</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H22" s="1">
+        <v>60</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C23" s="1">
+        <v>1018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>7</v>
+      </c>
+      <c r="E23" s="1">
+        <v>22</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H23" s="1">
+        <v>60</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C24" s="1">
+        <v>1019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1">
+        <v>23</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H24" s="1">
+        <v>60</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C25" s="1">
+        <v>1020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7</v>
+      </c>
+      <c r="E25" s="1">
+        <v>24</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H25" s="1">
+        <v>60</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C26" s="1">
+        <v>1021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1">
+        <v>25</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H26" s="1">
+        <v>60</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C27" s="1">
+        <v>1022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>7</v>
+      </c>
+      <c r="E27" s="1">
+        <v>27</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H27" s="1">
+        <v>60</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C28" s="1">
+        <v>1023</v>
+      </c>
+      <c r="D28" s="1">
+        <v>7</v>
+      </c>
+      <c r="E28" s="1">
+        <v>29</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H28" s="1">
+        <v>60</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C29" s="1">
+        <v>1024</v>
+      </c>
+      <c r="D29" s="1">
+        <v>7</v>
+      </c>
+      <c r="E29" s="1">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H29" s="1">
+        <v>60</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>1025</v>
+      </c>
+      <c r="D30" s="1">
+        <v>7</v>
+      </c>
+      <c r="E30" s="1">
+        <v>21</v>
+      </c>
+      <c r="F30" s="1">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H30" s="1">
+        <v>80</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>1026</v>
+      </c>
+      <c r="D31" s="1">
+        <v>7</v>
+      </c>
+      <c r="E31" s="1">
+        <v>22</v>
+      </c>
+      <c r="F31" s="1">
+        <v>4</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H31" s="1">
+        <v>80</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>1027</v>
+      </c>
+      <c r="D32" s="1">
+        <v>7</v>
+      </c>
+      <c r="E32" s="1">
+        <v>23</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H32" s="1">
+        <v>80</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>1028</v>
+      </c>
+      <c r="D33" s="1">
+        <v>7</v>
+      </c>
+      <c r="E33" s="1">
+        <v>24</v>
+      </c>
+      <c r="F33" s="1">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H33" s="1">
+        <v>80</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>1029</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H34" s="1">
+        <v>80</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>1030</v>
+      </c>
+      <c r="D35" s="1">
+        <v>7</v>
+      </c>
+      <c r="E35" s="1">
+        <v>27</v>
+      </c>
+      <c r="F35" s="1">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H35" s="1">
+        <v>80</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>1031</v>
+      </c>
+      <c r="D36" s="1">
+        <v>7</v>
+      </c>
+      <c r="E36" s="1">
+        <v>29</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H36" s="1">
+        <v>80</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>1032</v>
+      </c>
+      <c r="D37" s="1">
+        <v>7</v>
+      </c>
+      <c r="E37" s="1">
+        <v>30</v>
+      </c>
+      <c r="F37" s="1">
+        <v>4</v>
+      </c>
+      <c r="G37" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H37" s="1">
+        <v>80</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C38" s="1">
+        <v>1033</v>
+      </c>
+      <c r="D38" s="1">
+        <v>7</v>
+      </c>
+      <c r="E38" s="1">
+        <v>21</v>
+      </c>
+      <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H38" s="1">
+        <v>100</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C39" s="1">
+        <v>1034</v>
+      </c>
+      <c r="D39" s="1">
+        <v>7</v>
+      </c>
+      <c r="E39" s="1">
+        <v>22</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H39" s="1">
+        <v>100</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C40" s="1">
+        <v>1035</v>
+      </c>
+      <c r="D40" s="1">
+        <v>7</v>
+      </c>
+      <c r="E40" s="1">
+        <v>23</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H40" s="1">
+        <v>100</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>1036</v>
+      </c>
+      <c r="D41" s="1">
+        <v>7</v>
+      </c>
+      <c r="E41" s="1">
+        <v>24</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H41" s="1">
+        <v>100</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>1037</v>
+      </c>
+      <c r="D42" s="1">
+        <v>7</v>
+      </c>
+      <c r="E42" s="1">
+        <v>25</v>
+      </c>
+      <c r="F42" s="1">
+        <v>5</v>
+      </c>
+      <c r="G42" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H42" s="1">
+        <v>100</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C43" s="1">
+        <v>1038</v>
+      </c>
+      <c r="D43" s="1">
+        <v>7</v>
+      </c>
+      <c r="E43" s="1">
+        <v>27</v>
+      </c>
+      <c r="F43" s="1">
+        <v>5</v>
+      </c>
+      <c r="G43" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H43" s="1">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C44" s="1">
+        <v>1039</v>
+      </c>
+      <c r="D44" s="1">
+        <v>7</v>
+      </c>
+      <c r="E44" s="1">
+        <v>29</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H44" s="1">
+        <v>100</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C45" s="1">
+        <v>1040</v>
+      </c>
+      <c r="D45" s="1">
+        <v>7</v>
+      </c>
+      <c r="E45" s="1">
+        <v>30</v>
+      </c>
+      <c r="F45" s="1">
+        <v>5</v>
+      </c>
+      <c r="G45" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H45" s="1">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C46" s="1">
+        <v>1041</v>
+      </c>
+      <c r="D46" s="1">
+        <v>7</v>
+      </c>
+      <c r="E46" s="1">
+        <v>21</v>
+      </c>
+      <c r="F46" s="1">
+        <v>6</v>
+      </c>
+      <c r="G46" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H46" s="1">
+        <v>140</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C47" s="1">
+        <v>1042</v>
+      </c>
+      <c r="D47" s="1">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>22</v>
+      </c>
+      <c r="F47" s="1">
+        <v>6</v>
+      </c>
+      <c r="G47" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H47" s="1">
+        <v>140</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C48" s="1">
+        <v>1043</v>
+      </c>
+      <c r="D48" s="1">
+        <v>7</v>
+      </c>
+      <c r="E48" s="1">
+        <v>23</v>
+      </c>
+      <c r="F48" s="1">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H48" s="1">
+        <v>140</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C49" s="1">
+        <v>1044</v>
+      </c>
+      <c r="D49" s="1">
+        <v>7</v>
+      </c>
+      <c r="E49" s="1">
+        <v>24</v>
+      </c>
+      <c r="F49" s="1">
+        <v>6</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H49" s="1">
+        <v>140</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C50" s="1">
+        <v>1045</v>
+      </c>
+      <c r="D50" s="1">
+        <v>7</v>
+      </c>
+      <c r="E50" s="1">
+        <v>25</v>
+      </c>
+      <c r="F50" s="1">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H50" s="1">
+        <v>140</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C51" s="1">
+        <v>1046</v>
+      </c>
+      <c r="D51" s="1">
+        <v>7</v>
+      </c>
+      <c r="E51" s="1">
+        <v>27</v>
+      </c>
+      <c r="F51" s="1">
+        <v>6</v>
+      </c>
+      <c r="G51" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H51" s="1">
+        <v>140</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C52" s="1">
+        <v>1047</v>
+      </c>
+      <c r="D52" s="1">
+        <v>7</v>
+      </c>
+      <c r="E52" s="1">
+        <v>29</v>
+      </c>
+      <c r="F52" s="1">
+        <v>6</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H52" s="1">
+        <v>140</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C53" s="1">
+        <v>1048</v>
+      </c>
+      <c r="D53" s="1">
+        <v>7</v>
+      </c>
+      <c r="E53" s="1">
+        <v>30</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H53" s="1">
+        <v>140</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C54" s="1">
+        <v>1049</v>
+      </c>
+      <c r="D54" s="1">
+        <v>7</v>
+      </c>
+      <c r="E54" s="1">
+        <v>21</v>
+      </c>
+      <c r="F54" s="1">
+        <v>7</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H54" s="1">
+        <v>180</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C55" s="1">
+        <v>1050</v>
+      </c>
+      <c r="D55" s="1">
+        <v>7</v>
+      </c>
+      <c r="E55" s="1">
+        <v>22</v>
+      </c>
+      <c r="F55" s="1">
+        <v>7</v>
+      </c>
+      <c r="G55" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H55" s="1">
+        <v>180</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C56" s="1">
+        <v>1051</v>
+      </c>
+      <c r="D56" s="1">
+        <v>7</v>
+      </c>
+      <c r="E56" s="1">
+        <v>23</v>
+      </c>
+      <c r="F56" s="1">
+        <v>7</v>
+      </c>
+      <c r="G56" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H56" s="1">
+        <v>180</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C57" s="1">
+        <v>1052</v>
+      </c>
+      <c r="D57" s="1">
+        <v>7</v>
+      </c>
+      <c r="E57" s="1">
+        <v>24</v>
+      </c>
+      <c r="F57" s="1">
+        <v>7</v>
+      </c>
+      <c r="G57" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H57" s="1">
+        <v>180</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C58" s="1">
+        <v>1053</v>
+      </c>
+      <c r="D58" s="1">
+        <v>7</v>
+      </c>
+      <c r="E58" s="1">
+        <v>25</v>
+      </c>
+      <c r="F58" s="1">
+        <v>7</v>
+      </c>
+      <c r="G58" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H58" s="1">
+        <v>180</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
+        <v>1054</v>
+      </c>
+      <c r="D59" s="1">
+        <v>7</v>
+      </c>
+      <c r="E59" s="1">
+        <v>27</v>
+      </c>
+      <c r="F59" s="1">
+        <v>7</v>
+      </c>
+      <c r="G59" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H59" s="1">
+        <v>180</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>1055</v>
+      </c>
+      <c r="D60" s="1">
+        <v>7</v>
+      </c>
+      <c r="E60" s="1">
+        <v>29</v>
+      </c>
+      <c r="F60" s="1">
+        <v>7</v>
+      </c>
+      <c r="G60" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H60" s="1">
+        <v>180</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C61" s="1">
+        <v>1056</v>
+      </c>
+      <c r="D61" s="1">
+        <v>7</v>
+      </c>
+      <c r="E61" s="1">
+        <v>30</v>
+      </c>
+      <c r="F61" s="1">
+        <v>7</v>
+      </c>
+      <c r="G61" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H61" s="1">
+        <v>180</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J61" s="1">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:10">
+      <c r="C62" s="1">
+        <v>1057</v>
+      </c>
+      <c r="D62" s="1">
+        <v>7</v>
+      </c>
+      <c r="E62" s="1">
+        <v>21</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8</v>
+      </c>
+      <c r="G62" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H62" s="1">
+        <v>210</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
+      <c r="C63" s="1">
+        <v>1058</v>
+      </c>
+      <c r="D63" s="1">
+        <v>7</v>
+      </c>
+      <c r="E63" s="1">
+        <v>22</v>
+      </c>
+      <c r="F63" s="1">
+        <v>8</v>
+      </c>
+      <c r="G63" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H63" s="1">
+        <v>210</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>1059</v>
+      </c>
+      <c r="D64" s="1">
+        <v>7</v>
+      </c>
+      <c r="E64" s="1">
+        <v>23</v>
+      </c>
+      <c r="F64" s="1">
+        <v>8</v>
+      </c>
+      <c r="G64" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H64" s="1">
+        <v>210</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>1060</v>
+      </c>
+      <c r="D65" s="1">
+        <v>7</v>
+      </c>
+      <c r="E65" s="1">
+        <v>24</v>
+      </c>
+      <c r="F65" s="1">
+        <v>8</v>
+      </c>
+      <c r="G65" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H65" s="1">
+        <v>210</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
+        <v>1061</v>
+      </c>
+      <c r="D66" s="1">
+        <v>7</v>
+      </c>
+      <c r="E66" s="1">
+        <v>25</v>
+      </c>
+      <c r="F66" s="1">
+        <v>8</v>
+      </c>
+      <c r="G66" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H66" s="1">
+        <v>210</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="1">
+        <v>1062</v>
+      </c>
+      <c r="D67" s="1">
+        <v>7</v>
+      </c>
+      <c r="E67" s="1">
+        <v>27</v>
+      </c>
+      <c r="F67" s="1">
+        <v>8</v>
+      </c>
+      <c r="G67" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H67" s="1">
+        <v>210</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="1">
+        <v>1063</v>
+      </c>
+      <c r="D68" s="1">
+        <v>7</v>
+      </c>
+      <c r="E68" s="1">
+        <v>29</v>
+      </c>
+      <c r="F68" s="1">
+        <v>8</v>
+      </c>
+      <c r="G68" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H68" s="1">
+        <v>210</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="1">
+        <v>1064</v>
+      </c>
+      <c r="D69" s="1">
+        <v>7</v>
+      </c>
+      <c r="E69" s="1">
+        <v>30</v>
+      </c>
+      <c r="F69" s="1">
+        <v>8</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H69" s="1">
+        <v>210</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="1">
+        <v>1065</v>
+      </c>
+      <c r="D70" s="1">
+        <v>7</v>
+      </c>
+      <c r="E70" s="1">
+        <v>21</v>
+      </c>
+      <c r="F70" s="1">
+        <v>9</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H70" s="1">
+        <v>240</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="1">
+        <v>1066</v>
+      </c>
+      <c r="D71" s="1">
+        <v>7</v>
+      </c>
+      <c r="E71" s="1">
+        <v>22</v>
+      </c>
+      <c r="F71" s="1">
+        <v>9</v>
+      </c>
+      <c r="G71" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H71" s="1">
+        <v>240</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="1">
+        <v>1067</v>
+      </c>
+      <c r="D72" s="1">
+        <v>7</v>
+      </c>
+      <c r="E72" s="1">
+        <v>23</v>
+      </c>
+      <c r="F72" s="1">
+        <v>9</v>
+      </c>
+      <c r="G72" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H72" s="1">
+        <v>240</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J72" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="1">
+        <v>1068</v>
+      </c>
+      <c r="D73" s="1">
+        <v>7</v>
+      </c>
+      <c r="E73" s="1">
+        <v>24</v>
+      </c>
+      <c r="F73" s="1">
+        <v>9</v>
+      </c>
+      <c r="G73" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H73" s="1">
+        <v>240</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="1">
+        <v>1069</v>
+      </c>
+      <c r="D74" s="1">
+        <v>7</v>
+      </c>
+      <c r="E74" s="1">
+        <v>25</v>
+      </c>
+      <c r="F74" s="1">
+        <v>9</v>
+      </c>
+      <c r="G74" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H74" s="1">
+        <v>240</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J74" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="1">
+        <v>1070</v>
+      </c>
+      <c r="D75" s="1">
+        <v>7</v>
+      </c>
+      <c r="E75" s="1">
+        <v>27</v>
+      </c>
+      <c r="F75" s="1">
+        <v>9</v>
+      </c>
+      <c r="G75" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H75" s="1">
+        <v>240</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J75" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="1">
+        <v>1071</v>
+      </c>
+      <c r="D76" s="1">
+        <v>7</v>
+      </c>
+      <c r="E76" s="1">
+        <v>29</v>
+      </c>
+      <c r="F76" s="1">
+        <v>9</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H76" s="1">
+        <v>240</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="1">
+        <v>1072</v>
+      </c>
+      <c r="D77" s="1">
+        <v>7</v>
+      </c>
+      <c r="E77" s="1">
+        <v>30</v>
+      </c>
+      <c r="F77" s="1">
+        <v>9</v>
+      </c>
+      <c r="G77" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H77" s="1">
+        <v>240</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J77" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="1">
+        <v>1073</v>
+      </c>
+      <c r="D78" s="1">
+        <v>7</v>
+      </c>
+      <c r="E78" s="1">
+        <v>21</v>
+      </c>
+      <c r="F78" s="1">
+        <v>10</v>
+      </c>
+      <c r="G78" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H78" s="1">
+        <v>270</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="1">
+        <v>1074</v>
+      </c>
+      <c r="D79" s="1">
+        <v>7</v>
+      </c>
+      <c r="E79" s="1">
+        <v>22</v>
+      </c>
+      <c r="F79" s="1">
+        <v>10</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H79" s="1">
+        <v>270</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="1">
+        <v>1075</v>
+      </c>
+      <c r="D80" s="1">
+        <v>7</v>
+      </c>
+      <c r="E80" s="1">
+        <v>23</v>
+      </c>
+      <c r="F80" s="1">
+        <v>10</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H80" s="1">
+        <v>270</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J80" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="1">
+        <v>1076</v>
+      </c>
+      <c r="D81" s="1">
+        <v>7</v>
+      </c>
+      <c r="E81" s="1">
+        <v>24</v>
+      </c>
+      <c r="F81" s="1">
+        <v>10</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H81" s="1">
+        <v>270</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="1">
+        <v>1077</v>
+      </c>
+      <c r="D82" s="1">
+        <v>7</v>
+      </c>
+      <c r="E82" s="1">
+        <v>25</v>
+      </c>
+      <c r="F82" s="1">
+        <v>10</v>
+      </c>
+      <c r="G82" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H82" s="1">
+        <v>270</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="1">
+        <v>1078</v>
+      </c>
+      <c r="D83" s="1">
+        <v>7</v>
+      </c>
+      <c r="E83" s="1">
+        <v>27</v>
+      </c>
+      <c r="F83" s="1">
+        <v>10</v>
+      </c>
+      <c r="G83" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H83" s="1">
+        <v>270</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="1">
+        <v>1079</v>
+      </c>
+      <c r="D84" s="1">
+        <v>7</v>
+      </c>
+      <c r="E84" s="1">
+        <v>29</v>
+      </c>
+      <c r="F84" s="1">
+        <v>10</v>
+      </c>
+      <c r="G84" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H84" s="1">
+        <v>270</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="1">
+        <v>1080</v>
+      </c>
+      <c r="D85" s="1">
+        <v>7</v>
+      </c>
+      <c r="E85" s="1">
+        <v>30</v>
+      </c>
+      <c r="F85" s="1">
+        <v>10</v>
+      </c>
+      <c r="G85" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H85" s="1">
+        <v>270</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
+      <c r="C86" s="1">
+        <v>1081</v>
+      </c>
+      <c r="D86" s="1">
+        <v>7</v>
+      </c>
+      <c r="E86" s="1">
+        <v>21</v>
+      </c>
+      <c r="F86" s="1">
+        <v>11</v>
+      </c>
+      <c r="G86" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H86" s="1">
+        <v>300</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J86" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:10">
+      <c r="C87" s="1">
+        <v>1082</v>
+      </c>
+      <c r="D87" s="1">
+        <v>7</v>
+      </c>
+      <c r="E87" s="1">
+        <v>22</v>
+      </c>
+      <c r="F87" s="1">
+        <v>11</v>
+      </c>
+      <c r="G87" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H87" s="1">
+        <v>300</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J87" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:10">
+      <c r="C88" s="1">
+        <v>1083</v>
+      </c>
+      <c r="D88" s="1">
+        <v>7</v>
+      </c>
+      <c r="E88" s="1">
+        <v>23</v>
+      </c>
+      <c r="F88" s="1">
+        <v>11</v>
+      </c>
+      <c r="G88" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H88" s="1">
+        <v>300</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J88" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
+      <c r="C89" s="1">
+        <v>1084</v>
+      </c>
+      <c r="D89" s="1">
+        <v>7</v>
+      </c>
+      <c r="E89" s="1">
+        <v>24</v>
+      </c>
+      <c r="F89" s="1">
+        <v>11</v>
+      </c>
+      <c r="G89" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H89" s="1">
+        <v>300</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J89" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
+      <c r="C90" s="1">
+        <v>1085</v>
+      </c>
+      <c r="D90" s="1">
+        <v>7</v>
+      </c>
+      <c r="E90" s="1">
+        <v>25</v>
+      </c>
+      <c r="F90" s="1">
+        <v>11</v>
+      </c>
+      <c r="G90" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H90" s="1">
+        <v>300</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J90" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:10">
+      <c r="C91" s="1">
+        <v>1086</v>
+      </c>
+      <c r="D91" s="1">
+        <v>7</v>
+      </c>
+      <c r="E91" s="1">
+        <v>27</v>
+      </c>
+      <c r="F91" s="1">
+        <v>11</v>
+      </c>
+      <c r="G91" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H91" s="1">
+        <v>300</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J91" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:10">
+      <c r="C92" s="1">
+        <v>1087</v>
+      </c>
+      <c r="D92" s="1">
+        <v>7</v>
+      </c>
+      <c r="E92" s="1">
+        <v>29</v>
+      </c>
+      <c r="F92" s="1">
+        <v>11</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H92" s="1">
+        <v>300</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J92" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
+      <c r="C93" s="1">
+        <v>1088</v>
+      </c>
+      <c r="D93" s="1">
+        <v>7</v>
+      </c>
+      <c r="E93" s="1">
+        <v>30</v>
+      </c>
+      <c r="F93" s="1">
+        <v>11</v>
+      </c>
+      <c r="G93" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H93" s="1">
+        <v>300</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J93" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:10">
+      <c r="C94" s="1">
+        <v>1089</v>
+      </c>
+      <c r="D94" s="1">
+        <v>7</v>
+      </c>
+      <c r="E94" s="1">
+        <v>21</v>
+      </c>
+      <c r="F94" s="1">
+        <v>12</v>
+      </c>
+      <c r="G94" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H94" s="1">
+        <v>330</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J94" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:10">
+      <c r="C95" s="1">
+        <v>1090</v>
+      </c>
+      <c r="D95" s="1">
+        <v>7</v>
+      </c>
+      <c r="E95" s="1">
+        <v>22</v>
+      </c>
+      <c r="F95" s="1">
+        <v>12</v>
+      </c>
+      <c r="G95" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H95" s="1">
+        <v>330</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J95" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:10">
+      <c r="C96" s="1">
+        <v>1091</v>
+      </c>
+      <c r="D96" s="1">
+        <v>7</v>
+      </c>
+      <c r="E96" s="1">
+        <v>23</v>
+      </c>
+      <c r="F96" s="1">
+        <v>12</v>
+      </c>
+      <c r="G96" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H96" s="1">
+        <v>330</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J96" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:10">
+      <c r="C97" s="1">
+        <v>1092</v>
+      </c>
+      <c r="D97" s="1">
+        <v>7</v>
+      </c>
+      <c r="E97" s="1">
+        <v>24</v>
+      </c>
+      <c r="F97" s="1">
+        <v>12</v>
+      </c>
+      <c r="G97" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H97" s="1">
+        <v>330</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J97" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:10">
+      <c r="C98" s="1">
+        <v>1093</v>
+      </c>
+      <c r="D98" s="1">
+        <v>7</v>
+      </c>
+      <c r="E98" s="1">
+        <v>25</v>
+      </c>
+      <c r="F98" s="1">
+        <v>12</v>
+      </c>
+      <c r="G98" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H98" s="1">
+        <v>330</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J98" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:10">
+      <c r="C99" s="1">
+        <v>1094</v>
+      </c>
+      <c r="D99" s="1">
+        <v>7</v>
+      </c>
+      <c r="E99" s="1">
+        <v>27</v>
+      </c>
+      <c r="F99" s="1">
+        <v>12</v>
+      </c>
+      <c r="G99" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H99" s="1">
+        <v>330</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J99" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:10">
+      <c r="C100" s="1">
+        <v>1095</v>
+      </c>
+      <c r="D100" s="1">
+        <v>7</v>
+      </c>
+      <c r="E100" s="1">
+        <v>29</v>
+      </c>
+      <c r="F100" s="1">
+        <v>12</v>
+      </c>
+      <c r="G100" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H100" s="1">
+        <v>330</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:10">
+      <c r="C101" s="1">
+        <v>1096</v>
+      </c>
+      <c r="D101" s="1">
+        <v>7</v>
+      </c>
+      <c r="E101" s="1">
+        <v>30</v>
+      </c>
+      <c r="F101" s="1">
+        <v>12</v>
+      </c>
+      <c r="G101" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H101" s="1">
+        <v>330</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J101" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:10">
+      <c r="C102" s="1">
+        <v>1097</v>
+      </c>
+      <c r="D102" s="1">
+        <v>7</v>
+      </c>
+      <c r="E102" s="1">
+        <v>21</v>
+      </c>
+      <c r="F102" s="1">
+        <v>13</v>
+      </c>
+      <c r="G102" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H102" s="1">
+        <v>360</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J102" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:10">
+      <c r="C103" s="1">
+        <v>1098</v>
+      </c>
+      <c r="D103" s="1">
+        <v>7</v>
+      </c>
+      <c r="E103" s="1">
+        <v>22</v>
+      </c>
+      <c r="F103" s="1">
+        <v>13</v>
+      </c>
+      <c r="G103" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H103" s="1">
+        <v>360</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J103" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:10">
+      <c r="C104" s="1">
+        <v>1099</v>
+      </c>
+      <c r="D104" s="1">
+        <v>7</v>
+      </c>
+      <c r="E104" s="1">
+        <v>23</v>
+      </c>
+      <c r="F104" s="1">
+        <v>13</v>
+      </c>
+      <c r="G104" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H104" s="1">
+        <v>360</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J104" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:10">
+      <c r="C105" s="1">
+        <v>1100</v>
+      </c>
+      <c r="D105" s="1">
+        <v>7</v>
+      </c>
+      <c r="E105" s="1">
+        <v>24</v>
+      </c>
+      <c r="F105" s="1">
+        <v>13</v>
+      </c>
+      <c r="G105" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H105" s="1">
+        <v>360</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J105" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:10">
+      <c r="C106" s="1">
+        <v>1101</v>
+      </c>
+      <c r="D106" s="1">
+        <v>7</v>
+      </c>
+      <c r="E106" s="1">
+        <v>25</v>
+      </c>
+      <c r="F106" s="1">
+        <v>13</v>
+      </c>
+      <c r="G106" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H106" s="1">
+        <v>360</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J106" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:10">
+      <c r="C107" s="1">
+        <v>1102</v>
+      </c>
+      <c r="D107" s="1">
+        <v>7</v>
+      </c>
+      <c r="E107" s="1">
+        <v>27</v>
+      </c>
+      <c r="F107" s="1">
+        <v>13</v>
+      </c>
+      <c r="G107" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H107" s="1">
+        <v>360</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J107" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:10">
+      <c r="C108" s="1">
+        <v>1103</v>
+      </c>
+      <c r="D108" s="1">
+        <v>7</v>
+      </c>
+      <c r="E108" s="1">
+        <v>29</v>
+      </c>
+      <c r="F108" s="1">
+        <v>13</v>
+      </c>
+      <c r="G108" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H108" s="1">
+        <v>360</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J108" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:10">
+      <c r="C109" s="1">
+        <v>1104</v>
+      </c>
+      <c r="D109" s="1">
+        <v>7</v>
+      </c>
+      <c r="E109" s="1">
+        <v>30</v>
+      </c>
+      <c r="F109" s="1">
+        <v>13</v>
+      </c>
+      <c r="G109" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H109" s="1">
+        <v>360</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J109" s="1">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:10">
+      <c r="C110" s="1">
+        <v>1105</v>
+      </c>
+      <c r="D110" s="1">
+        <v>7</v>
+      </c>
+      <c r="E110" s="1">
+        <v>21</v>
+      </c>
+      <c r="F110" s="1">
+        <v>14</v>
+      </c>
+      <c r="G110" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H110" s="1">
+        <v>390</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J110" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:10">
+      <c r="C111" s="1">
+        <v>1106</v>
+      </c>
+      <c r="D111" s="1">
+        <v>7</v>
+      </c>
+      <c r="E111" s="1">
+        <v>22</v>
+      </c>
+      <c r="F111" s="1">
+        <v>14</v>
+      </c>
+      <c r="G111" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H111" s="1">
+        <v>390</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J111" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:10">
+      <c r="C112" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D112" s="1">
+        <v>7</v>
+      </c>
+      <c r="E112" s="1">
+        <v>23</v>
+      </c>
+      <c r="F112" s="1">
+        <v>14</v>
+      </c>
+      <c r="G112" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H112" s="1">
+        <v>390</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J112" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:10">
+      <c r="C113" s="1">
+        <v>1108</v>
+      </c>
+      <c r="D113" s="1">
+        <v>7</v>
+      </c>
+      <c r="E113" s="1">
+        <v>24</v>
+      </c>
+      <c r="F113" s="1">
+        <v>14</v>
+      </c>
+      <c r="G113" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H113" s="1">
+        <v>390</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J113" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:10">
+      <c r="C114" s="1">
+        <v>1109</v>
+      </c>
+      <c r="D114" s="1">
+        <v>7</v>
+      </c>
+      <c r="E114" s="1">
+        <v>25</v>
+      </c>
+      <c r="F114" s="1">
+        <v>14</v>
+      </c>
+      <c r="G114" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H114" s="1">
+        <v>390</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J114" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:10">
+      <c r="C115" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D115" s="1">
+        <v>7</v>
+      </c>
+      <c r="E115" s="1">
+        <v>27</v>
+      </c>
+      <c r="F115" s="1">
+        <v>14</v>
+      </c>
+      <c r="G115" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H115" s="1">
+        <v>390</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J115" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:10">
+      <c r="C116" s="1">
+        <v>1111</v>
+      </c>
+      <c r="D116" s="1">
+        <v>7</v>
+      </c>
+      <c r="E116" s="1">
+        <v>29</v>
+      </c>
+      <c r="F116" s="1">
+        <v>14</v>
+      </c>
+      <c r="G116" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H116" s="1">
+        <v>390</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J116" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:10">
+      <c r="C117" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D117" s="1">
+        <v>7</v>
+      </c>
+      <c r="E117" s="1">
+        <v>30</v>
+      </c>
+      <c r="F117" s="1">
+        <v>14</v>
+      </c>
+      <c r="G117" s="1">
+        <v>4011</v>
+      </c>
+      <c r="H117" s="1">
+        <v>390</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J117" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:L61"/>
@@ -4270,7 +8829,7 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C6" s="1">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="D6" s="1">
         <v>7</v>
@@ -4282,22 +8841,21 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" ref="J6:J61" si="0">H6*5</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C7" s="1">
-        <v>1002</v>
+        <v>2002</v>
       </c>
       <c r="D7" s="1">
         <v>7</v>
@@ -4309,22 +8867,21 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C8" s="1">
-        <v>1003</v>
+        <v>2003</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -4336,22 +8893,21 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C9" s="1">
-        <v>1004</v>
+        <v>2004</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -4363,22 +8919,21 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C10" s="1">
-        <v>1005</v>
+        <v>2005</v>
       </c>
       <c r="D10" s="1">
         <v>7</v>
@@ -4390,22 +8945,21 @@
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C11" s="1">
-        <v>1006</v>
+        <v>2006</v>
       </c>
       <c r="D11" s="1">
         <v>7</v>
@@ -4417,22 +8971,21 @@
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C12" s="1">
-        <v>1007</v>
+        <v>2007</v>
       </c>
       <c r="D12" s="1">
         <v>7</v>
@@ -4444,22 +8997,21 @@
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C13" s="1">
-        <v>1008</v>
+        <v>2008</v>
       </c>
       <c r="D13" s="1">
         <v>7</v>
@@ -4471,22 +9023,21 @@
         <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C14" s="1">
-        <v>1009</v>
+        <v>2009</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -4498,22 +9049,21 @@
         <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H14" s="1">
         <v>40</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C15" s="1">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -4525,22 +9075,21 @@
         <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H15" s="1">
         <v>40</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C16" s="1">
-        <v>1011</v>
+        <v>2011</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
@@ -4552,22 +9101,21 @@
         <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H16" s="1">
         <v>40</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C17" s="1">
-        <v>1012</v>
+        <v>2012</v>
       </c>
       <c r="D17" s="1">
         <v>7</v>
@@ -4579,22 +9127,21 @@
         <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H17" s="1">
         <v>40</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C18" s="1">
-        <v>1013</v>
+        <v>2013</v>
       </c>
       <c r="D18" s="1">
         <v>7</v>
@@ -4606,22 +9153,21 @@
         <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H18" s="1">
         <v>40</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C19" s="1">
-        <v>1014</v>
+        <v>2014</v>
       </c>
       <c r="D19" s="1">
         <v>7</v>
@@ -4633,22 +9179,21 @@
         <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H19" s="1">
         <v>40</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C20" s="1">
-        <v>1015</v>
+        <v>2015</v>
       </c>
       <c r="D20" s="1">
         <v>7</v>
@@ -4660,22 +9205,21 @@
         <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H20" s="1">
         <v>40</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C21" s="1">
-        <v>1016</v>
+        <v>2016</v>
       </c>
       <c r="D21" s="1">
         <v>7</v>
@@ -4687,22 +9231,21 @@
         <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H21" s="1">
         <v>40</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C22" s="1">
-        <v>1017</v>
+        <v>2017</v>
       </c>
       <c r="D22" s="1">
         <v>7</v>
@@ -4714,22 +9257,21 @@
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H22" s="1">
         <v>60</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C23" s="1">
-        <v>1018</v>
+        <v>2018</v>
       </c>
       <c r="D23" s="1">
         <v>7</v>
@@ -4741,22 +9283,21 @@
         <v>3</v>
       </c>
       <c r="G23" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H23" s="1">
         <v>60</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C24" s="1">
-        <v>1019</v>
+        <v>2019</v>
       </c>
       <c r="D24" s="1">
         <v>7</v>
@@ -4768,22 +9309,21 @@
         <v>3</v>
       </c>
       <c r="G24" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H24" s="1">
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C25" s="1">
-        <v>1020</v>
+        <v>2020</v>
       </c>
       <c r="D25" s="1">
         <v>7</v>
@@ -4795,22 +9335,21 @@
         <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H25" s="1">
         <v>60</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C26" s="1">
-        <v>1021</v>
+        <v>2021</v>
       </c>
       <c r="D26" s="1">
         <v>7</v>
@@ -4822,22 +9361,21 @@
         <v>3</v>
       </c>
       <c r="G26" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H26" s="1">
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C27" s="1">
-        <v>1022</v>
+        <v>2022</v>
       </c>
       <c r="D27" s="1">
         <v>7</v>
@@ -4849,22 +9387,21 @@
         <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H27" s="1">
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C28" s="1">
-        <v>1023</v>
+        <v>2023</v>
       </c>
       <c r="D28" s="1">
         <v>7</v>
@@ -4876,22 +9413,21 @@
         <v>3</v>
       </c>
       <c r="G28" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H28" s="1">
         <v>60</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C29" s="1">
-        <v>1024</v>
+        <v>2024</v>
       </c>
       <c r="D29" s="1">
         <v>7</v>
@@ -4903,22 +9439,21 @@
         <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H29" s="1">
         <v>60</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C30" s="1">
-        <v>1025</v>
+        <v>2025</v>
       </c>
       <c r="D30" s="1">
         <v>7</v>
@@ -4930,22 +9465,21 @@
         <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H30" s="1">
         <v>80</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C31" s="1">
-        <v>1026</v>
+        <v>2026</v>
       </c>
       <c r="D31" s="1">
         <v>7</v>
@@ -4957,22 +9491,21 @@
         <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H31" s="1">
         <v>80</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C32" s="1">
-        <v>1027</v>
+        <v>2027</v>
       </c>
       <c r="D32" s="1">
         <v>7</v>
@@ -4984,22 +9517,21 @@
         <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H32" s="1">
         <v>80</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C33" s="1">
-        <v>1028</v>
+        <v>2028</v>
       </c>
       <c r="D33" s="1">
         <v>7</v>
@@ -5011,22 +9543,21 @@
         <v>4</v>
       </c>
       <c r="G33" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H33" s="1">
         <v>80</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C34" s="1">
-        <v>1029</v>
+        <v>2029</v>
       </c>
       <c r="D34" s="1">
         <v>7</v>
@@ -5038,22 +9569,21 @@
         <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H34" s="1">
         <v>80</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C35" s="1">
-        <v>1030</v>
+        <v>2030</v>
       </c>
       <c r="D35" s="1">
         <v>7</v>
@@ -5065,22 +9595,21 @@
         <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H35" s="1">
         <v>80</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C36" s="1">
-        <v>1031</v>
+        <v>2031</v>
       </c>
       <c r="D36" s="1">
         <v>7</v>
@@ -5092,22 +9621,21 @@
         <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H36" s="1">
         <v>80</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C37" s="1">
-        <v>1032</v>
+        <v>2032</v>
       </c>
       <c r="D37" s="1">
         <v>7</v>
@@ -5119,22 +9647,21 @@
         <v>4</v>
       </c>
       <c r="G37" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H37" s="1">
         <v>80</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C38" s="1">
-        <v>1033</v>
+        <v>2033</v>
       </c>
       <c r="D38" s="1">
         <v>7</v>
@@ -5146,22 +9673,21 @@
         <v>5</v>
       </c>
       <c r="G38" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H38" s="1">
         <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C39" s="1">
-        <v>1034</v>
+        <v>2034</v>
       </c>
       <c r="D39" s="1">
         <v>7</v>
@@ -5173,22 +9699,21 @@
         <v>5</v>
       </c>
       <c r="G39" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H39" s="1">
         <v>100</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C40" s="1">
-        <v>1035</v>
+        <v>2035</v>
       </c>
       <c r="D40" s="1">
         <v>7</v>
@@ -5200,22 +9725,21 @@
         <v>5</v>
       </c>
       <c r="G40" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H40" s="1">
         <v>100</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C41" s="1">
-        <v>1036</v>
+        <v>2036</v>
       </c>
       <c r="D41" s="1">
         <v>7</v>
@@ -5227,22 +9751,21 @@
         <v>5</v>
       </c>
       <c r="G41" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H41" s="1">
         <v>100</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C42" s="1">
-        <v>1037</v>
+        <v>2037</v>
       </c>
       <c r="D42" s="1">
         <v>7</v>
@@ -5254,22 +9777,21 @@
         <v>5</v>
       </c>
       <c r="G42" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H42" s="1">
         <v>100</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C43" s="1">
-        <v>1038</v>
+        <v>2038</v>
       </c>
       <c r="D43" s="1">
         <v>7</v>
@@ -5281,22 +9803,21 @@
         <v>5</v>
       </c>
       <c r="G43" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H43" s="1">
         <v>100</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C44" s="1">
-        <v>1039</v>
+        <v>2039</v>
       </c>
       <c r="D44" s="1">
         <v>7</v>
@@ -5308,22 +9829,21 @@
         <v>5</v>
       </c>
       <c r="G44" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H44" s="1">
         <v>100</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C45" s="1">
-        <v>1040</v>
+        <v>2040</v>
       </c>
       <c r="D45" s="1">
         <v>7</v>
@@ -5335,22 +9855,21 @@
         <v>5</v>
       </c>
       <c r="G45" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H45" s="1">
         <v>100</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C46" s="1">
-        <v>1041</v>
+        <v>2041</v>
       </c>
       <c r="D46" s="1">
         <v>7</v>
@@ -5362,22 +9881,21 @@
         <v>6</v>
       </c>
       <c r="G46" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H46" s="1">
         <v>140</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C47" s="1">
-        <v>1042</v>
+        <v>2042</v>
       </c>
       <c r="D47" s="1">
         <v>7</v>
@@ -5389,22 +9907,21 @@
         <v>6</v>
       </c>
       <c r="G47" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H47" s="1">
         <v>140</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C48" s="1">
-        <v>1043</v>
+        <v>2043</v>
       </c>
       <c r="D48" s="1">
         <v>7</v>
@@ -5416,22 +9933,21 @@
         <v>6</v>
       </c>
       <c r="G48" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H48" s="1">
         <v>140</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C49" s="1">
-        <v>1044</v>
+        <v>2044</v>
       </c>
       <c r="D49" s="1">
         <v>7</v>
@@ -5443,22 +9959,21 @@
         <v>6</v>
       </c>
       <c r="G49" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H49" s="1">
         <v>140</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C50" s="1">
-        <v>1045</v>
+        <v>2045</v>
       </c>
       <c r="D50" s="1">
         <v>7</v>
@@ -5470,22 +9985,21 @@
         <v>6</v>
       </c>
       <c r="G50" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H50" s="1">
         <v>140</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C51" s="1">
-        <v>1046</v>
+        <v>2046</v>
       </c>
       <c r="D51" s="1">
         <v>7</v>
@@ -5497,22 +10011,21 @@
         <v>6</v>
       </c>
       <c r="G51" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H51" s="1">
         <v>140</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C52" s="1">
-        <v>1047</v>
+        <v>2047</v>
       </c>
       <c r="D52" s="1">
         <v>7</v>
@@ -5524,22 +10037,21 @@
         <v>6</v>
       </c>
       <c r="G52" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H52" s="1">
         <v>140</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C53" s="1">
-        <v>1048</v>
+        <v>2048</v>
       </c>
       <c r="D53" s="1">
         <v>7</v>
@@ -5551,22 +10063,21 @@
         <v>6</v>
       </c>
       <c r="G53" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H53" s="1">
         <v>140</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="J53" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C54" s="1">
-        <v>1049</v>
+        <v>2049</v>
       </c>
       <c r="D54" s="1">
         <v>7</v>
@@ -5578,22 +10089,21 @@
         <v>7</v>
       </c>
       <c r="G54" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H54" s="1">
         <v>180</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C55" s="1">
-        <v>1050</v>
+        <v>2050</v>
       </c>
       <c r="D55" s="1">
         <v>7</v>
@@ -5605,22 +10115,21 @@
         <v>7</v>
       </c>
       <c r="G55" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H55" s="1">
         <v>180</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="J55" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C56" s="1">
-        <v>1051</v>
+        <v>2051</v>
       </c>
       <c r="D56" s="1">
         <v>7</v>
@@ -5632,22 +10141,21 @@
         <v>7</v>
       </c>
       <c r="G56" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H56" s="1">
         <v>180</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J56" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C57" s="1">
-        <v>1052</v>
+        <v>2052</v>
       </c>
       <c r="D57" s="1">
         <v>7</v>
@@ -5659,22 +10167,21 @@
         <v>7</v>
       </c>
       <c r="G57" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H57" s="1">
         <v>180</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J57" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C58" s="1">
-        <v>1053</v>
+        <v>2053</v>
       </c>
       <c r="D58" s="1">
         <v>7</v>
@@ -5686,22 +10193,21 @@
         <v>7</v>
       </c>
       <c r="G58" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H58" s="1">
         <v>180</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C59" s="1">
-        <v>1054</v>
+        <v>2054</v>
       </c>
       <c r="D59" s="1">
         <v>7</v>
@@ -5713,22 +10219,21 @@
         <v>7</v>
       </c>
       <c r="G59" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H59" s="1">
         <v>180</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J59" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C60" s="1">
-        <v>1055</v>
+        <v>2055</v>
       </c>
       <c r="D60" s="1">
         <v>7</v>
@@ -5740,22 +10245,21 @@
         <v>7</v>
       </c>
       <c r="G60" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H60" s="1">
         <v>180</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C61" s="1">
-        <v>1056</v>
+        <v>2056</v>
       </c>
       <c r="D61" s="1">
         <v>7</v>
@@ -5767,17 +10271,16 @@
         <v>7</v>
       </c>
       <c r="G61" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="H61" s="1">
         <v>180</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J61" s="1">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>2200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -5769,7 +5769,7 @@
         <v>66</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" ref="J6:J61" si="0">H6*5</f>
+        <f t="shared" ref="J6:J70" si="0">H6*5</f>
         <v>100</v>
       </c>
     </row>
@@ -7275,13 +7275,14 @@
         <v>4011</v>
       </c>
       <c r="H62" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J62" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:10">
@@ -7301,13 +7302,14 @@
         <v>4011</v>
       </c>
       <c r="H63" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J63" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:10">
@@ -7327,13 +7329,14 @@
         <v>4011</v>
       </c>
       <c r="H64" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J64" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:10">
@@ -7353,13 +7356,14 @@
         <v>4011</v>
       </c>
       <c r="H65" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J65" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:10">
@@ -7379,13 +7383,14 @@
         <v>4011</v>
       </c>
       <c r="H66" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J66" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:10">
@@ -7405,13 +7410,14 @@
         <v>4011</v>
       </c>
       <c r="H67" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J67" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:10">
@@ -7431,13 +7437,14 @@
         <v>4011</v>
       </c>
       <c r="H68" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J68" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:10">
@@ -7457,13 +7464,14 @@
         <v>4011</v>
       </c>
       <c r="H69" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J69" s="1">
-        <v>1200</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:10">
@@ -7483,13 +7491,14 @@
         <v>4011</v>
       </c>
       <c r="H70" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J70" s="1">
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1100</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:10">
@@ -7509,13 +7518,14 @@
         <v>4011</v>
       </c>
       <c r="H71" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J71" s="1">
-        <v>1500</v>
+        <f t="shared" ref="J71:J117" si="1">H71*5</f>
+        <v>1100</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:10">
@@ -7535,13 +7545,14 @@
         <v>4011</v>
       </c>
       <c r="H72" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J72" s="1">
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1100</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:10">
@@ -7561,13 +7572,14 @@
         <v>4011</v>
       </c>
       <c r="H73" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J73" s="1">
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1100</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:10">
@@ -7587,13 +7599,14 @@
         <v>4011</v>
       </c>
       <c r="H74" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J74" s="1">
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1100</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:10">
@@ -7613,13 +7626,14 @@
         <v>4011</v>
       </c>
       <c r="H75" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J75" s="1">
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1100</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:10">
@@ -7639,13 +7653,14 @@
         <v>4011</v>
       </c>
       <c r="H76" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J76" s="1">
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1100</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:10">
@@ -7665,13 +7680,14 @@
         <v>4011</v>
       </c>
       <c r="H77" s="1">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J77" s="1">
-        <v>1500</v>
+        <f t="shared" si="1"/>
+        <v>1100</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:10">
@@ -7691,13 +7707,14 @@
         <v>4011</v>
       </c>
       <c r="H78" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J78" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:10">
@@ -7717,13 +7734,14 @@
         <v>4011</v>
       </c>
       <c r="H79" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J79" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:10">
@@ -7743,13 +7761,14 @@
         <v>4011</v>
       </c>
       <c r="H80" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J80" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:10">
@@ -7769,13 +7788,14 @@
         <v>4011</v>
       </c>
       <c r="H81" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J81" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:10">
@@ -7795,13 +7815,14 @@
         <v>4011</v>
       </c>
       <c r="H82" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J82" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:10">
@@ -7821,13 +7842,14 @@
         <v>4011</v>
       </c>
       <c r="H83" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J83" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:10">
@@ -7847,13 +7869,14 @@
         <v>4011</v>
       </c>
       <c r="H84" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J84" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:10">
@@ -7873,13 +7896,14 @@
         <v>4011</v>
       </c>
       <c r="H85" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J85" s="1">
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:10">
@@ -7899,13 +7923,14 @@
         <v>4011</v>
       </c>
       <c r="H86" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J86" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:10">
@@ -7925,13 +7950,14 @@
         <v>4011</v>
       </c>
       <c r="H87" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J87" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:10">
@@ -7951,13 +7977,14 @@
         <v>4011</v>
       </c>
       <c r="H88" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J88" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:10">
@@ -7977,13 +8004,14 @@
         <v>4011</v>
       </c>
       <c r="H89" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J89" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:10">
@@ -8003,13 +8031,14 @@
         <v>4011</v>
       </c>
       <c r="H90" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J90" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:10">
@@ -8029,13 +8058,14 @@
         <v>4011</v>
       </c>
       <c r="H91" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J91" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:10">
@@ -8055,13 +8085,14 @@
         <v>4011</v>
       </c>
       <c r="H92" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J92" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:10">
@@ -8081,13 +8112,14 @@
         <v>4011</v>
       </c>
       <c r="H93" s="1">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J93" s="1">
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>1300</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:10">
@@ -8107,13 +8139,14 @@
         <v>4011</v>
       </c>
       <c r="H94" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J94" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:10">
@@ -8133,13 +8166,14 @@
         <v>4011</v>
       </c>
       <c r="H95" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J95" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:10">
@@ -8159,13 +8193,14 @@
         <v>4011</v>
       </c>
       <c r="H96" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J96" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:10">
@@ -8185,13 +8220,14 @@
         <v>4011</v>
       </c>
       <c r="H97" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J97" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:10">
@@ -8211,13 +8247,14 @@
         <v>4011</v>
       </c>
       <c r="H98" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J98" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:10">
@@ -8237,13 +8274,14 @@
         <v>4011</v>
       </c>
       <c r="H99" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J99" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:10">
@@ -8263,13 +8301,14 @@
         <v>4011</v>
       </c>
       <c r="H100" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J100" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:10">
@@ -8289,13 +8328,14 @@
         <v>4011</v>
       </c>
       <c r="H101" s="1">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J101" s="1">
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:10">
@@ -8315,13 +8355,14 @@
         <v>4011</v>
       </c>
       <c r="H102" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J102" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:10">
@@ -8341,13 +8382,14 @@
         <v>4011</v>
       </c>
       <c r="H103" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J103" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:10">
@@ -8367,13 +8409,14 @@
         <v>4011</v>
       </c>
       <c r="H104" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J104" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:10">
@@ -8393,13 +8436,14 @@
         <v>4011</v>
       </c>
       <c r="H105" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J105" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:10">
@@ -8419,13 +8463,14 @@
         <v>4011</v>
       </c>
       <c r="H106" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J106" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:10">
@@ -8445,13 +8490,14 @@
         <v>4011</v>
       </c>
       <c r="H107" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J107" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:10">
@@ -8471,13 +8517,14 @@
         <v>4011</v>
       </c>
       <c r="H108" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J108" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:10">
@@ -8497,13 +8544,14 @@
         <v>4011</v>
       </c>
       <c r="H109" s="1">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J109" s="1">
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:10">
@@ -8523,13 +8571,14 @@
         <v>4011</v>
       </c>
       <c r="H110" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J110" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:10">
@@ -8549,13 +8598,14 @@
         <v>4011</v>
       </c>
       <c r="H111" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J111" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:10">
@@ -8575,13 +8625,14 @@
         <v>4011</v>
       </c>
       <c r="H112" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J112" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:10">
@@ -8601,13 +8652,14 @@
         <v>4011</v>
       </c>
       <c r="H113" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J113" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:10">
@@ -8627,13 +8679,14 @@
         <v>4011</v>
       </c>
       <c r="H114" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J114" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:10">
@@ -8653,13 +8706,14 @@
         <v>4011</v>
       </c>
       <c r="H115" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J115" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:10">
@@ -8679,13 +8733,14 @@
         <v>4011</v>
       </c>
       <c r="H116" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J116" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:10">
@@ -8705,13 +8760,14 @@
         <v>4011</v>
       </c>
       <c r="H117" s="1">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J117" s="1">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
@@ -8850,7 +8906,7 @@
         <v>122</v>
       </c>
       <c r="J6" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8876,7 +8932,7 @@
         <v>122</v>
       </c>
       <c r="J7" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8902,7 +8958,7 @@
         <v>122</v>
       </c>
       <c r="J8" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8928,7 +8984,7 @@
         <v>122</v>
       </c>
       <c r="J9" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8954,7 +9010,7 @@
         <v>122</v>
       </c>
       <c r="J10" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8980,7 +9036,7 @@
         <v>122</v>
       </c>
       <c r="J11" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9006,7 +9062,7 @@
         <v>122</v>
       </c>
       <c r="J12" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9032,7 +9088,7 @@
         <v>122</v>
       </c>
       <c r="J13" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9058,7 +9114,7 @@
         <v>123</v>
       </c>
       <c r="J14" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9084,7 +9140,7 @@
         <v>123</v>
       </c>
       <c r="J15" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9110,7 +9166,7 @@
         <v>123</v>
       </c>
       <c r="J16" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9136,7 +9192,7 @@
         <v>123</v>
       </c>
       <c r="J17" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9162,7 +9218,7 @@
         <v>123</v>
       </c>
       <c r="J18" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9188,7 +9244,7 @@
         <v>123</v>
       </c>
       <c r="J19" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9214,7 +9270,7 @@
         <v>123</v>
       </c>
       <c r="J20" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9240,7 +9296,7 @@
         <v>123</v>
       </c>
       <c r="J21" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9266,7 +9322,7 @@
         <v>124</v>
       </c>
       <c r="J22" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9292,7 +9348,7 @@
         <v>124</v>
       </c>
       <c r="J23" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9318,7 +9374,7 @@
         <v>124</v>
       </c>
       <c r="J24" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9344,7 +9400,7 @@
         <v>124</v>
       </c>
       <c r="J25" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9370,7 +9426,7 @@
         <v>124</v>
       </c>
       <c r="J26" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9396,7 +9452,7 @@
         <v>124</v>
       </c>
       <c r="J27" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9422,7 +9478,7 @@
         <v>124</v>
       </c>
       <c r="J28" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9448,7 +9504,7 @@
         <v>124</v>
       </c>
       <c r="J29" s="1">
-        <v>1400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9474,7 +9530,7 @@
         <v>125</v>
       </c>
       <c r="J30" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9500,7 +9556,7 @@
         <v>125</v>
       </c>
       <c r="J31" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9526,7 +9582,7 @@
         <v>125</v>
       </c>
       <c r="J32" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9552,7 +9608,7 @@
         <v>125</v>
       </c>
       <c r="J33" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9578,7 +9634,7 @@
         <v>125</v>
       </c>
       <c r="J34" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9604,7 +9660,7 @@
         <v>125</v>
       </c>
       <c r="J35" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9630,7 +9686,7 @@
         <v>125</v>
       </c>
       <c r="J36" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9656,7 +9712,7 @@
         <v>125</v>
       </c>
       <c r="J37" s="1">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9682,7 +9738,7 @@
         <v>126</v>
       </c>
       <c r="J38" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9708,7 +9764,7 @@
         <v>126</v>
       </c>
       <c r="J39" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9734,7 +9790,7 @@
         <v>126</v>
       </c>
       <c r="J40" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9760,7 +9816,7 @@
         <v>126</v>
       </c>
       <c r="J41" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9786,7 +9842,7 @@
         <v>126</v>
       </c>
       <c r="J42" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9812,7 +9868,7 @@
         <v>126</v>
       </c>
       <c r="J43" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9838,7 +9894,7 @@
         <v>126</v>
       </c>
       <c r="J44" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9864,7 +9920,7 @@
         <v>126</v>
       </c>
       <c r="J45" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9890,7 +9946,7 @@
         <v>127</v>
       </c>
       <c r="J46" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9916,7 +9972,7 @@
         <v>127</v>
       </c>
       <c r="J47" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9942,7 +9998,7 @@
         <v>127</v>
       </c>
       <c r="J48" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9968,7 +10024,7 @@
         <v>127</v>
       </c>
       <c r="J49" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9994,7 +10050,7 @@
         <v>127</v>
       </c>
       <c r="J50" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10020,7 +10076,7 @@
         <v>127</v>
       </c>
       <c r="J51" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10046,7 +10102,7 @@
         <v>127</v>
       </c>
       <c r="J52" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10072,7 +10128,7 @@
         <v>127</v>
       </c>
       <c r="J53" s="1">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10098,7 +10154,7 @@
         <v>128</v>
       </c>
       <c r="J54" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10124,7 +10180,7 @@
         <v>128</v>
       </c>
       <c r="J55" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10150,7 +10206,7 @@
         <v>128</v>
       </c>
       <c r="J56" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10176,7 +10232,7 @@
         <v>128</v>
       </c>
       <c r="J57" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10202,7 +10258,7 @@
         <v>128</v>
       </c>
       <c r="J58" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10228,7 +10284,7 @@
         <v>128</v>
       </c>
       <c r="J59" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10254,7 +10310,7 @@
         <v>128</v>
       </c>
       <c r="J60" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10280,7 +10336,7 @@
         <v>128</v>
       </c>
       <c r="J61" s="1">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -7272,7 +7272,7 @@
         <v>8</v>
       </c>
       <c r="G62" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H62" s="1">
         <v>200</v>
@@ -7299,7 +7299,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H63" s="1">
         <v>200</v>
@@ -7326,7 +7326,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H64" s="1">
         <v>200</v>
@@ -7353,7 +7353,7 @@
         <v>8</v>
       </c>
       <c r="G65" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H65" s="1">
         <v>200</v>
@@ -7380,7 +7380,7 @@
         <v>8</v>
       </c>
       <c r="G66" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H66" s="1">
         <v>200</v>
@@ -7407,7 +7407,7 @@
         <v>8</v>
       </c>
       <c r="G67" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H67" s="1">
         <v>200</v>
@@ -7434,7 +7434,7 @@
         <v>8</v>
       </c>
       <c r="G68" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H68" s="1">
         <v>200</v>
@@ -7461,7 +7461,7 @@
         <v>8</v>
       </c>
       <c r="G69" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H69" s="1">
         <v>200</v>
@@ -7488,7 +7488,7 @@
         <v>9</v>
       </c>
       <c r="G70" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H70" s="1">
         <v>220</v>
@@ -7515,7 +7515,7 @@
         <v>9</v>
       </c>
       <c r="G71" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H71" s="1">
         <v>220</v>
@@ -7542,7 +7542,7 @@
         <v>9</v>
       </c>
       <c r="G72" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H72" s="1">
         <v>220</v>
@@ -7569,7 +7569,7 @@
         <v>9</v>
       </c>
       <c r="G73" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H73" s="1">
         <v>220</v>
@@ -7596,7 +7596,7 @@
         <v>9</v>
       </c>
       <c r="G74" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H74" s="1">
         <v>220</v>
@@ -7623,7 +7623,7 @@
         <v>9</v>
       </c>
       <c r="G75" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H75" s="1">
         <v>220</v>
@@ -7650,7 +7650,7 @@
         <v>9</v>
       </c>
       <c r="G76" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H76" s="1">
         <v>220</v>
@@ -7677,7 +7677,7 @@
         <v>9</v>
       </c>
       <c r="G77" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H77" s="1">
         <v>220</v>
@@ -7704,7 +7704,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H78" s="1">
         <v>240</v>
@@ -7731,7 +7731,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H79" s="1">
         <v>240</v>
@@ -7758,7 +7758,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H80" s="1">
         <v>240</v>
@@ -7785,7 +7785,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H81" s="1">
         <v>240</v>
@@ -7812,7 +7812,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H82" s="1">
         <v>240</v>
@@ -7839,7 +7839,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H83" s="1">
         <v>240</v>
@@ -7866,7 +7866,7 @@
         <v>10</v>
       </c>
       <c r="G84" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H84" s="1">
         <v>240</v>
@@ -7893,7 +7893,7 @@
         <v>10</v>
       </c>
       <c r="G85" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H85" s="1">
         <v>240</v>
@@ -7920,7 +7920,7 @@
         <v>11</v>
       </c>
       <c r="G86" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H86" s="1">
         <v>260</v>
@@ -7947,7 +7947,7 @@
         <v>11</v>
       </c>
       <c r="G87" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H87" s="1">
         <v>260</v>
@@ -7974,7 +7974,7 @@
         <v>11</v>
       </c>
       <c r="G88" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H88" s="1">
         <v>260</v>
@@ -8001,7 +8001,7 @@
         <v>11</v>
       </c>
       <c r="G89" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H89" s="1">
         <v>260</v>
@@ -8028,7 +8028,7 @@
         <v>11</v>
       </c>
       <c r="G90" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H90" s="1">
         <v>260</v>
@@ -8055,7 +8055,7 @@
         <v>11</v>
       </c>
       <c r="G91" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H91" s="1">
         <v>260</v>
@@ -8082,7 +8082,7 @@
         <v>11</v>
       </c>
       <c r="G92" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H92" s="1">
         <v>260</v>
@@ -8109,7 +8109,7 @@
         <v>11</v>
       </c>
       <c r="G93" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H93" s="1">
         <v>260</v>
@@ -8136,7 +8136,7 @@
         <v>12</v>
       </c>
       <c r="G94" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H94" s="1">
         <v>280</v>
@@ -8163,7 +8163,7 @@
         <v>12</v>
       </c>
       <c r="G95" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H95" s="1">
         <v>280</v>
@@ -8190,7 +8190,7 @@
         <v>12</v>
       </c>
       <c r="G96" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H96" s="1">
         <v>280</v>
@@ -8217,7 +8217,7 @@
         <v>12</v>
       </c>
       <c r="G97" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H97" s="1">
         <v>280</v>
@@ -8244,7 +8244,7 @@
         <v>12</v>
       </c>
       <c r="G98" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H98" s="1">
         <v>280</v>
@@ -8271,7 +8271,7 @@
         <v>12</v>
       </c>
       <c r="G99" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H99" s="1">
         <v>280</v>
@@ -8298,7 +8298,7 @@
         <v>12</v>
       </c>
       <c r="G100" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H100" s="1">
         <v>280</v>
@@ -8325,7 +8325,7 @@
         <v>12</v>
       </c>
       <c r="G101" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H101" s="1">
         <v>280</v>
@@ -8352,7 +8352,7 @@
         <v>13</v>
       </c>
       <c r="G102" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H102" s="1">
         <v>300</v>
@@ -8379,7 +8379,7 @@
         <v>13</v>
       </c>
       <c r="G103" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H103" s="1">
         <v>300</v>
@@ -8406,7 +8406,7 @@
         <v>13</v>
       </c>
       <c r="G104" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H104" s="1">
         <v>300</v>
@@ -8433,7 +8433,7 @@
         <v>13</v>
       </c>
       <c r="G105" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H105" s="1">
         <v>300</v>
@@ -8460,7 +8460,7 @@
         <v>13</v>
       </c>
       <c r="G106" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H106" s="1">
         <v>300</v>
@@ -8487,7 +8487,7 @@
         <v>13</v>
       </c>
       <c r="G107" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H107" s="1">
         <v>300</v>
@@ -8514,7 +8514,7 @@
         <v>13</v>
       </c>
       <c r="G108" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H108" s="1">
         <v>300</v>
@@ -8541,7 +8541,7 @@
         <v>13</v>
       </c>
       <c r="G109" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H109" s="1">
         <v>300</v>
@@ -8568,7 +8568,7 @@
         <v>14</v>
       </c>
       <c r="G110" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H110" s="1">
         <v>320</v>
@@ -8595,7 +8595,7 @@
         <v>14</v>
       </c>
       <c r="G111" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H111" s="1">
         <v>320</v>
@@ -8622,7 +8622,7 @@
         <v>14</v>
       </c>
       <c r="G112" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H112" s="1">
         <v>320</v>
@@ -8649,7 +8649,7 @@
         <v>14</v>
       </c>
       <c r="G113" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H113" s="1">
         <v>320</v>
@@ -8676,7 +8676,7 @@
         <v>14</v>
       </c>
       <c r="G114" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H114" s="1">
         <v>320</v>
@@ -8703,7 +8703,7 @@
         <v>14</v>
       </c>
       <c r="G115" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H115" s="1">
         <v>320</v>
@@ -8730,7 +8730,7 @@
         <v>14</v>
       </c>
       <c r="G116" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H116" s="1">
         <v>320</v>
@@ -8757,7 +8757,7 @@
         <v>14</v>
       </c>
       <c r="G117" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="H117" s="1">
         <v>320</v>
@@ -8906,7 +8906,7 @@
         <v>122</v>
       </c>
       <c r="J6" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8932,7 +8932,7 @@
         <v>122</v>
       </c>
       <c r="J7" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8958,7 +8958,7 @@
         <v>122</v>
       </c>
       <c r="J8" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8984,7 +8984,7 @@
         <v>122</v>
       </c>
       <c r="J9" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9010,7 +9010,7 @@
         <v>122</v>
       </c>
       <c r="J10" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9036,7 +9036,7 @@
         <v>122</v>
       </c>
       <c r="J11" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9062,7 +9062,7 @@
         <v>122</v>
       </c>
       <c r="J12" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9088,7 +9088,7 @@
         <v>122</v>
       </c>
       <c r="J13" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9114,7 +9114,7 @@
         <v>123</v>
       </c>
       <c r="J14" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9140,7 +9140,7 @@
         <v>123</v>
       </c>
       <c r="J15" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9166,7 +9166,7 @@
         <v>123</v>
       </c>
       <c r="J16" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9192,7 +9192,7 @@
         <v>123</v>
       </c>
       <c r="J17" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9218,7 +9218,7 @@
         <v>123</v>
       </c>
       <c r="J18" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9244,7 +9244,7 @@
         <v>123</v>
       </c>
       <c r="J19" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9270,7 +9270,7 @@
         <v>123</v>
       </c>
       <c r="J20" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9296,7 +9296,7 @@
         <v>123</v>
       </c>
       <c r="J21" s="1">
-        <v>600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9322,7 +9322,7 @@
         <v>124</v>
       </c>
       <c r="J22" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9348,7 +9348,7 @@
         <v>124</v>
       </c>
       <c r="J23" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9374,7 +9374,7 @@
         <v>124</v>
       </c>
       <c r="J24" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9400,7 +9400,7 @@
         <v>124</v>
       </c>
       <c r="J25" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9426,7 +9426,7 @@
         <v>124</v>
       </c>
       <c r="J26" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9452,7 +9452,7 @@
         <v>124</v>
       </c>
       <c r="J27" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9478,7 +9478,7 @@
         <v>124</v>
       </c>
       <c r="J28" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9504,7 +9504,7 @@
         <v>124</v>
       </c>
       <c r="J29" s="1">
-        <v>800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9530,7 +9530,7 @@
         <v>125</v>
       </c>
       <c r="J30" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9556,7 +9556,7 @@
         <v>125</v>
       </c>
       <c r="J31" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9582,7 +9582,7 @@
         <v>125</v>
       </c>
       <c r="J32" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9608,7 +9608,7 @@
         <v>125</v>
       </c>
       <c r="J33" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9634,7 +9634,7 @@
         <v>125</v>
       </c>
       <c r="J34" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9660,7 +9660,7 @@
         <v>125</v>
       </c>
       <c r="J35" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9686,7 +9686,7 @@
         <v>125</v>
       </c>
       <c r="J36" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9712,7 +9712,7 @@
         <v>125</v>
       </c>
       <c r="J37" s="1">
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9738,7 +9738,7 @@
         <v>126</v>
       </c>
       <c r="J38" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9764,7 +9764,7 @@
         <v>126</v>
       </c>
       <c r="J39" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9790,7 +9790,7 @@
         <v>126</v>
       </c>
       <c r="J40" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9816,7 +9816,7 @@
         <v>126</v>
       </c>
       <c r="J41" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9842,7 +9842,7 @@
         <v>126</v>
       </c>
       <c r="J42" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9868,7 +9868,7 @@
         <v>126</v>
       </c>
       <c r="J43" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9894,7 +9894,7 @@
         <v>126</v>
       </c>
       <c r="J44" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9920,7 +9920,7 @@
         <v>126</v>
       </c>
       <c r="J45" s="1">
-        <v>1200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9946,7 +9946,7 @@
         <v>127</v>
       </c>
       <c r="J46" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9972,7 +9972,7 @@
         <v>127</v>
       </c>
       <c r="J47" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9998,7 +9998,7 @@
         <v>127</v>
       </c>
       <c r="J48" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10024,7 +10024,7 @@
         <v>127</v>
       </c>
       <c r="J49" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10050,7 +10050,7 @@
         <v>127</v>
       </c>
       <c r="J50" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10076,7 +10076,7 @@
         <v>127</v>
       </c>
       <c r="J51" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10102,7 +10102,7 @@
         <v>127</v>
       </c>
       <c r="J52" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10128,7 +10128,7 @@
         <v>127</v>
       </c>
       <c r="J53" s="1">
-        <v>1400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10154,7 +10154,7 @@
         <v>128</v>
       </c>
       <c r="J54" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10180,7 +10180,7 @@
         <v>128</v>
       </c>
       <c r="J55" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10206,7 +10206,7 @@
         <v>128</v>
       </c>
       <c r="J56" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10232,7 +10232,7 @@
         <v>128</v>
       </c>
       <c r="J57" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10258,7 +10258,7 @@
         <v>128</v>
       </c>
       <c r="J58" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10284,7 +10284,7 @@
         <v>128</v>
       </c>
       <c r="J59" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10310,7 +10310,7 @@
         <v>128</v>
       </c>
       <c r="J60" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10336,7 +10336,7 @@
         <v>128</v>
       </c>
       <c r="J61" s="1">
-        <v>1600</v>
+        <v>3300</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -7491,14 +7491,14 @@
         <v>4019</v>
       </c>
       <c r="H70" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J70" s="1">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:10">
@@ -7518,14 +7518,14 @@
         <v>4019</v>
       </c>
       <c r="H71" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J71" s="1">
         <f t="shared" ref="J71:J117" si="1">H71*5</f>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:10">
@@ -7545,14 +7545,14 @@
         <v>4019</v>
       </c>
       <c r="H72" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J72" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:10">
@@ -7572,14 +7572,14 @@
         <v>4019</v>
       </c>
       <c r="H73" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J73" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:10">
@@ -7599,14 +7599,14 @@
         <v>4019</v>
       </c>
       <c r="H74" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J74" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:10">
@@ -7626,14 +7626,14 @@
         <v>4019</v>
       </c>
       <c r="H75" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J75" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:10">
@@ -7653,14 +7653,14 @@
         <v>4019</v>
       </c>
       <c r="H76" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J76" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:10">
@@ -7680,14 +7680,14 @@
         <v>4019</v>
       </c>
       <c r="H77" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J77" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:10">
@@ -7707,14 +7707,14 @@
         <v>4019</v>
       </c>
       <c r="H78" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J78" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:10">
@@ -7734,14 +7734,14 @@
         <v>4019</v>
       </c>
       <c r="H79" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J79" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:10">
@@ -7761,14 +7761,14 @@
         <v>4019</v>
       </c>
       <c r="H80" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J80" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:10">
@@ -7788,14 +7788,14 @@
         <v>4019</v>
       </c>
       <c r="H81" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J81" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:10">
@@ -7815,14 +7815,14 @@
         <v>4019</v>
       </c>
       <c r="H82" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J82" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:10">
@@ -7842,14 +7842,14 @@
         <v>4019</v>
       </c>
       <c r="H83" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J83" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:10">
@@ -7869,14 +7869,14 @@
         <v>4019</v>
       </c>
       <c r="H84" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J84" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:10">
@@ -7896,14 +7896,14 @@
         <v>4019</v>
       </c>
       <c r="H85" s="1">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J85" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:10">
@@ -7923,14 +7923,14 @@
         <v>4019</v>
       </c>
       <c r="H86" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J86" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:10">
@@ -7950,14 +7950,14 @@
         <v>4019</v>
       </c>
       <c r="H87" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J87" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:10">
@@ -7977,14 +7977,14 @@
         <v>4019</v>
       </c>
       <c r="H88" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J88" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:10">
@@ -8004,14 +8004,14 @@
         <v>4019</v>
       </c>
       <c r="H89" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J89" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:10">
@@ -8031,14 +8031,14 @@
         <v>4019</v>
       </c>
       <c r="H90" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J90" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:10">
@@ -8058,14 +8058,14 @@
         <v>4019</v>
       </c>
       <c r="H91" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J91" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:10">
@@ -8085,14 +8085,14 @@
         <v>4019</v>
       </c>
       <c r="H92" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J92" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:10">
@@ -8112,14 +8112,14 @@
         <v>4019</v>
       </c>
       <c r="H93" s="1">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J93" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:10">
@@ -8139,14 +8139,14 @@
         <v>4019</v>
       </c>
       <c r="H94" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J94" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:10">
@@ -8166,14 +8166,14 @@
         <v>4019</v>
       </c>
       <c r="H95" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J95" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:10">
@@ -8193,14 +8193,14 @@
         <v>4019</v>
       </c>
       <c r="H96" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J96" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:10">
@@ -8220,14 +8220,14 @@
         <v>4019</v>
       </c>
       <c r="H97" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J97" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:10">
@@ -8247,14 +8247,14 @@
         <v>4019</v>
       </c>
       <c r="H98" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J98" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:10">
@@ -8274,14 +8274,14 @@
         <v>4019</v>
       </c>
       <c r="H99" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J99" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:10">
@@ -8301,14 +8301,14 @@
         <v>4019</v>
       </c>
       <c r="H100" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J100" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:10">
@@ -8328,14 +8328,14 @@
         <v>4019</v>
       </c>
       <c r="H101" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J101" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:10">
@@ -8355,14 +8355,14 @@
         <v>4019</v>
       </c>
       <c r="H102" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J102" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:10">
@@ -8382,14 +8382,14 @@
         <v>4019</v>
       </c>
       <c r="H103" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J103" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:10">
@@ -8409,14 +8409,14 @@
         <v>4019</v>
       </c>
       <c r="H104" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J104" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:10">
@@ -8436,14 +8436,14 @@
         <v>4019</v>
       </c>
       <c r="H105" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J105" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:10">
@@ -8463,14 +8463,14 @@
         <v>4019</v>
       </c>
       <c r="H106" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J106" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:10">
@@ -8490,14 +8490,14 @@
         <v>4019</v>
       </c>
       <c r="H107" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J107" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:10">
@@ -8517,14 +8517,14 @@
         <v>4019</v>
       </c>
       <c r="H108" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J108" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:10">
@@ -8544,14 +8544,14 @@
         <v>4019</v>
       </c>
       <c r="H109" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J109" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:10">
@@ -8571,14 +8571,14 @@
         <v>4019</v>
       </c>
       <c r="H110" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J110" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:10">
@@ -8598,14 +8598,14 @@
         <v>4019</v>
       </c>
       <c r="H111" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J111" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:10">
@@ -8625,14 +8625,14 @@
         <v>4019</v>
       </c>
       <c r="H112" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J112" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:10">
@@ -8652,14 +8652,14 @@
         <v>4019</v>
       </c>
       <c r="H113" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J113" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:10">
@@ -8679,14 +8679,14 @@
         <v>4019</v>
       </c>
       <c r="H114" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J114" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:10">
@@ -8706,14 +8706,14 @@
         <v>4019</v>
       </c>
       <c r="H115" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J115" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:10">
@@ -8733,14 +8733,14 @@
         <v>4019</v>
       </c>
       <c r="H116" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J116" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:10">
@@ -8760,14 +8760,14 @@
         <v>4019</v>
       </c>
       <c r="H117" s="1">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>128</v>
       </c>
       <c r="J117" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -8888,10 +8888,10 @@
         <v>2001</v>
       </c>
       <c r="D6" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -8914,10 +8914,10 @@
         <v>2002</v>
       </c>
       <c r="D7" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -8940,10 +8940,10 @@
         <v>2003</v>
       </c>
       <c r="D8" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -8966,10 +8966,10 @@
         <v>2004</v>
       </c>
       <c r="D9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -8992,10 +8992,10 @@
         <v>2005</v>
       </c>
       <c r="D10" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -9018,10 +9018,10 @@
         <v>2006</v>
       </c>
       <c r="D11" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -9044,10 +9044,10 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
@@ -9070,10 +9070,10 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
@@ -9096,10 +9096,10 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1">
         <v>2</v>
@@ -9122,10 +9122,10 @@
         <v>2010</v>
       </c>
       <c r="D15" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
@@ -9148,10 +9148,10 @@
         <v>2011</v>
       </c>
       <c r="D16" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1">
         <v>2</v>
@@ -9174,10 +9174,10 @@
         <v>2012</v>
       </c>
       <c r="D17" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1">
         <v>2</v>
@@ -9200,10 +9200,10 @@
         <v>2013</v>
       </c>
       <c r="D18" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F18" s="1">
         <v>2</v>
@@ -9226,10 +9226,10 @@
         <v>2014</v>
       </c>
       <c r="D19" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F19" s="1">
         <v>2</v>
@@ -9252,10 +9252,10 @@
         <v>2015</v>
       </c>
       <c r="D20" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F20" s="1">
         <v>2</v>
@@ -9278,10 +9278,10 @@
         <v>2016</v>
       </c>
       <c r="D21" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F21" s="1">
         <v>2</v>
@@ -9304,10 +9304,10 @@
         <v>2017</v>
       </c>
       <c r="D22" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
@@ -9330,10 +9330,10 @@
         <v>2018</v>
       </c>
       <c r="D23" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
@@ -9356,10 +9356,10 @@
         <v>2019</v>
       </c>
       <c r="D24" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -9382,10 +9382,10 @@
         <v>2020</v>
       </c>
       <c r="D25" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F25" s="1">
         <v>3</v>
@@ -9408,10 +9408,10 @@
         <v>2021</v>
       </c>
       <c r="D26" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F26" s="1">
         <v>3</v>
@@ -9434,10 +9434,10 @@
         <v>2022</v>
       </c>
       <c r="D27" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="1">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F27" s="1">
         <v>3</v>
@@ -9460,10 +9460,10 @@
         <v>2023</v>
       </c>
       <c r="D28" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
@@ -9486,10 +9486,10 @@
         <v>2024</v>
       </c>
       <c r="D29" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F29" s="1">
         <v>3</v>
@@ -9512,10 +9512,10 @@
         <v>2025</v>
       </c>
       <c r="D30" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F30" s="1">
         <v>4</v>
@@ -9538,10 +9538,10 @@
         <v>2026</v>
       </c>
       <c r="D31" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F31" s="1">
         <v>4</v>
@@ -9564,10 +9564,10 @@
         <v>2027</v>
       </c>
       <c r="D32" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
@@ -9590,10 +9590,10 @@
         <v>2028</v>
       </c>
       <c r="D33" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F33" s="1">
         <v>4</v>
@@ -9616,10 +9616,10 @@
         <v>2029</v>
       </c>
       <c r="D34" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F34" s="1">
         <v>4</v>
@@ -9642,10 +9642,10 @@
         <v>2030</v>
       </c>
       <c r="D35" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" s="1">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F35" s="1">
         <v>4</v>
@@ -9668,10 +9668,10 @@
         <v>2031</v>
       </c>
       <c r="D36" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F36" s="1">
         <v>4</v>
@@ -9694,10 +9694,10 @@
         <v>2032</v>
       </c>
       <c r="D37" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F37" s="1">
         <v>4</v>
@@ -9720,10 +9720,10 @@
         <v>2033</v>
       </c>
       <c r="D38" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F38" s="1">
         <v>5</v>
@@ -9746,10 +9746,10 @@
         <v>2034</v>
       </c>
       <c r="D39" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F39" s="1">
         <v>5</v>
@@ -9772,10 +9772,10 @@
         <v>2035</v>
       </c>
       <c r="D40" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
@@ -9798,10 +9798,10 @@
         <v>2036</v>
       </c>
       <c r="D41" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E41" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F41" s="1">
         <v>5</v>
@@ -9824,10 +9824,10 @@
         <v>2037</v>
       </c>
       <c r="D42" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F42" s="1">
         <v>5</v>
@@ -9850,10 +9850,10 @@
         <v>2038</v>
       </c>
       <c r="D43" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" s="1">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F43" s="1">
         <v>5</v>
@@ -9876,10 +9876,10 @@
         <v>2039</v>
       </c>
       <c r="D44" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1">
         <v>5</v>
@@ -9902,10 +9902,10 @@
         <v>2040</v>
       </c>
       <c r="D45" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F45" s="1">
         <v>5</v>
@@ -9928,10 +9928,10 @@
         <v>2041</v>
       </c>
       <c r="D46" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F46" s="1">
         <v>6</v>
@@ -9954,10 +9954,10 @@
         <v>2042</v>
       </c>
       <c r="D47" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E47" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F47" s="1">
         <v>6</v>
@@ -9980,10 +9980,10 @@
         <v>2043</v>
       </c>
       <c r="D48" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E48" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1">
         <v>6</v>
@@ -10006,10 +10006,10 @@
         <v>2044</v>
       </c>
       <c r="D49" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F49" s="1">
         <v>6</v>
@@ -10032,10 +10032,10 @@
         <v>2045</v>
       </c>
       <c r="D50" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F50" s="1">
         <v>6</v>
@@ -10058,10 +10058,10 @@
         <v>2046</v>
       </c>
       <c r="D51" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E51" s="1">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F51" s="1">
         <v>6</v>
@@ -10084,10 +10084,10 @@
         <v>2047</v>
       </c>
       <c r="D52" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E52" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F52" s="1">
         <v>6</v>
@@ -10110,10 +10110,10 @@
         <v>2048</v>
       </c>
       <c r="D53" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E53" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F53" s="1">
         <v>6</v>
@@ -10136,10 +10136,10 @@
         <v>2049</v>
       </c>
       <c r="D54" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E54" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F54" s="1">
         <v>7</v>
@@ -10162,10 +10162,10 @@
         <v>2050</v>
       </c>
       <c r="D55" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E55" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F55" s="1">
         <v>7</v>
@@ -10188,10 +10188,10 @@
         <v>2051</v>
       </c>
       <c r="D56" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E56" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F56" s="1">
         <v>7</v>
@@ -10214,10 +10214,10 @@
         <v>2052</v>
       </c>
       <c r="D57" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E57" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F57" s="1">
         <v>7</v>
@@ -10240,10 +10240,10 @@
         <v>2053</v>
       </c>
       <c r="D58" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E58" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F58" s="1">
         <v>7</v>
@@ -10266,10 +10266,10 @@
         <v>2054</v>
       </c>
       <c r="D59" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E59" s="1">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F59" s="1">
         <v>7</v>
@@ -10292,10 +10292,10 @@
         <v>2055</v>
       </c>
       <c r="D60" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E60" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F60" s="1">
         <v>7</v>
@@ -10318,10 +10318,10 @@
         <v>2056</v>
       </c>
       <c r="D61" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E61" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F61" s="1">
         <v>7</v>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -7524,8 +7524,7 @@
         <v>123</v>
       </c>
       <c r="J71" s="1">
-        <f t="shared" ref="J71:J117" si="1">H71*5</f>
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:10">
@@ -7551,8 +7550,7 @@
         <v>123</v>
       </c>
       <c r="J72" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:10">
@@ -7578,8 +7576,7 @@
         <v>123</v>
       </c>
       <c r="J73" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:10">
@@ -7605,8 +7602,7 @@
         <v>123</v>
       </c>
       <c r="J74" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:10">
@@ -7632,8 +7628,7 @@
         <v>123</v>
       </c>
       <c r="J75" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:10">
@@ -7659,8 +7654,7 @@
         <v>123</v>
       </c>
       <c r="J76" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:10">
@@ -7686,8 +7680,7 @@
         <v>123</v>
       </c>
       <c r="J77" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:10">
@@ -7713,8 +7706,7 @@
         <v>124</v>
       </c>
       <c r="J78" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:10">
@@ -7740,8 +7732,7 @@
         <v>124</v>
       </c>
       <c r="J79" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:10">
@@ -7767,8 +7758,7 @@
         <v>124</v>
       </c>
       <c r="J80" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:10">
@@ -7794,8 +7784,7 @@
         <v>124</v>
       </c>
       <c r="J81" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:10">
@@ -7821,8 +7810,7 @@
         <v>124</v>
       </c>
       <c r="J82" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:10">
@@ -7848,8 +7836,7 @@
         <v>124</v>
       </c>
       <c r="J83" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:10">
@@ -7875,8 +7862,7 @@
         <v>124</v>
       </c>
       <c r="J84" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:10">
@@ -7902,8 +7888,7 @@
         <v>124</v>
       </c>
       <c r="J85" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:10">
@@ -7929,8 +7914,7 @@
         <v>125</v>
       </c>
       <c r="J86" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:10">
@@ -7956,8 +7940,7 @@
         <v>125</v>
       </c>
       <c r="J87" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:10">
@@ -7983,8 +7966,7 @@
         <v>125</v>
       </c>
       <c r="J88" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:10">
@@ -8010,8 +7992,7 @@
         <v>125</v>
       </c>
       <c r="J89" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:10">
@@ -8037,8 +8018,7 @@
         <v>125</v>
       </c>
       <c r="J90" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:10">
@@ -8064,8 +8044,7 @@
         <v>125</v>
       </c>
       <c r="J91" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:10">
@@ -8091,8 +8070,7 @@
         <v>125</v>
       </c>
       <c r="J92" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:10">
@@ -8118,8 +8096,7 @@
         <v>125</v>
       </c>
       <c r="J93" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:10">
@@ -8145,8 +8122,7 @@
         <v>126</v>
       </c>
       <c r="J94" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:10">
@@ -8172,8 +8148,7 @@
         <v>126</v>
       </c>
       <c r="J95" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:10">
@@ -8199,8 +8174,7 @@
         <v>126</v>
       </c>
       <c r="J96" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:10">
@@ -8226,8 +8200,7 @@
         <v>126</v>
       </c>
       <c r="J97" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:10">
@@ -8253,8 +8226,7 @@
         <v>126</v>
       </c>
       <c r="J98" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:10">
@@ -8280,8 +8252,7 @@
         <v>126</v>
       </c>
       <c r="J99" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:10">
@@ -8307,8 +8278,7 @@
         <v>126</v>
       </c>
       <c r="J100" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:10">
@@ -8334,8 +8304,7 @@
         <v>126</v>
       </c>
       <c r="J101" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:10">
@@ -8361,8 +8330,7 @@
         <v>127</v>
       </c>
       <c r="J102" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:10">
@@ -8388,8 +8356,7 @@
         <v>127</v>
       </c>
       <c r="J103" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:10">
@@ -8415,8 +8382,7 @@
         <v>127</v>
       </c>
       <c r="J104" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:10">
@@ -8442,8 +8408,7 @@
         <v>127</v>
       </c>
       <c r="J105" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:10">
@@ -8469,8 +8434,7 @@
         <v>127</v>
       </c>
       <c r="J106" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:10">
@@ -8496,8 +8460,7 @@
         <v>127</v>
       </c>
       <c r="J107" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:10">
@@ -8523,8 +8486,7 @@
         <v>127</v>
       </c>
       <c r="J108" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:10">
@@ -8550,8 +8512,7 @@
         <v>127</v>
       </c>
       <c r="J109" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:10">
@@ -8577,8 +8538,7 @@
         <v>128</v>
       </c>
       <c r="J110" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:10">
@@ -8604,8 +8564,7 @@
         <v>128</v>
       </c>
       <c r="J111" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:10">
@@ -8631,8 +8590,7 @@
         <v>128</v>
       </c>
       <c r="J112" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:10">
@@ -8658,8 +8616,7 @@
         <v>128</v>
       </c>
       <c r="J113" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:10">
@@ -8685,8 +8642,7 @@
         <v>128</v>
       </c>
       <c r="J114" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:10">
@@ -8712,8 +8668,7 @@
         <v>128</v>
       </c>
       <c r="J115" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:10">
@@ -8739,8 +8694,7 @@
         <v>128</v>
       </c>
       <c r="J116" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:10">
@@ -8766,8 +8720,7 @@
         <v>128</v>
       </c>
       <c r="J117" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
   </sheetData>
@@ -8906,7 +8859,7 @@
         <v>122</v>
       </c>
       <c r="J6" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8932,7 +8885,7 @@
         <v>122</v>
       </c>
       <c r="J7" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8958,7 +8911,7 @@
         <v>122</v>
       </c>
       <c r="J8" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -8984,7 +8937,7 @@
         <v>122</v>
       </c>
       <c r="J9" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9010,7 +8963,7 @@
         <v>122</v>
       </c>
       <c r="J10" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9036,7 +8989,7 @@
         <v>122</v>
       </c>
       <c r="J11" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9062,7 +9015,7 @@
         <v>122</v>
       </c>
       <c r="J12" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9088,7 +9041,7 @@
         <v>122</v>
       </c>
       <c r="J13" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9114,7 +9067,7 @@
         <v>123</v>
       </c>
       <c r="J14" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9140,7 +9093,7 @@
         <v>123</v>
       </c>
       <c r="J15" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9166,7 +9119,7 @@
         <v>123</v>
       </c>
       <c r="J16" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9192,7 +9145,7 @@
         <v>123</v>
       </c>
       <c r="J17" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9218,7 +9171,7 @@
         <v>123</v>
       </c>
       <c r="J18" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9244,7 +9197,7 @@
         <v>123</v>
       </c>
       <c r="J19" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9270,7 +9223,7 @@
         <v>123</v>
       </c>
       <c r="J20" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9296,7 +9249,7 @@
         <v>123</v>
       </c>
       <c r="J21" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9322,7 +9275,7 @@
         <v>124</v>
       </c>
       <c r="J22" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9348,7 +9301,7 @@
         <v>124</v>
       </c>
       <c r="J23" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9374,7 +9327,7 @@
         <v>124</v>
       </c>
       <c r="J24" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9400,7 +9353,7 @@
         <v>124</v>
       </c>
       <c r="J25" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9426,7 +9379,7 @@
         <v>124</v>
       </c>
       <c r="J26" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9452,7 +9405,7 @@
         <v>124</v>
       </c>
       <c r="J27" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9478,7 +9431,7 @@
         <v>124</v>
       </c>
       <c r="J28" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9504,7 +9457,7 @@
         <v>124</v>
       </c>
       <c r="J29" s="1">
-        <v>2100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9530,7 +9483,7 @@
         <v>125</v>
       </c>
       <c r="J30" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9556,7 +9509,7 @@
         <v>125</v>
       </c>
       <c r="J31" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9582,7 +9535,7 @@
         <v>125</v>
       </c>
       <c r="J32" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9608,7 +9561,7 @@
         <v>125</v>
       </c>
       <c r="J33" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9634,7 +9587,7 @@
         <v>125</v>
       </c>
       <c r="J34" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9660,7 +9613,7 @@
         <v>125</v>
       </c>
       <c r="J35" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9686,7 +9639,7 @@
         <v>125</v>
       </c>
       <c r="J36" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9712,7 +9665,7 @@
         <v>125</v>
       </c>
       <c r="J37" s="1">
-        <v>2400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9738,7 +9691,7 @@
         <v>126</v>
       </c>
       <c r="J38" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9764,7 +9717,7 @@
         <v>126</v>
       </c>
       <c r="J39" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9790,7 +9743,7 @@
         <v>126</v>
       </c>
       <c r="J40" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9816,7 +9769,7 @@
         <v>126</v>
       </c>
       <c r="J41" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9842,7 +9795,7 @@
         <v>126</v>
       </c>
       <c r="J42" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9868,7 +9821,7 @@
         <v>126</v>
       </c>
       <c r="J43" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9894,7 +9847,7 @@
         <v>126</v>
       </c>
       <c r="J44" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9920,7 +9873,7 @@
         <v>126</v>
       </c>
       <c r="J45" s="1">
-        <v>2700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9946,7 +9899,7 @@
         <v>127</v>
       </c>
       <c r="J46" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9972,7 +9925,7 @@
         <v>127</v>
       </c>
       <c r="J47" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9998,7 +9951,7 @@
         <v>127</v>
       </c>
       <c r="J48" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10024,7 +9977,7 @@
         <v>127</v>
       </c>
       <c r="J49" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10050,7 +10003,7 @@
         <v>127</v>
       </c>
       <c r="J50" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10076,7 +10029,7 @@
         <v>127</v>
       </c>
       <c r="J51" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10102,7 +10055,7 @@
         <v>127</v>
       </c>
       <c r="J52" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10128,7 +10081,7 @@
         <v>127</v>
       </c>
       <c r="J53" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10154,7 +10107,7 @@
         <v>128</v>
       </c>
       <c r="J54" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10180,7 +10133,7 @@
         <v>128</v>
       </c>
       <c r="J55" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10206,7 +10159,7 @@
         <v>128</v>
       </c>
       <c r="J56" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10232,7 +10185,7 @@
         <v>128</v>
       </c>
       <c r="J57" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10258,7 +10211,7 @@
         <v>128</v>
       </c>
       <c r="J58" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10284,7 +10237,7 @@
         <v>128</v>
       </c>
       <c r="J59" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10310,7 +10263,7 @@
         <v>128</v>
       </c>
       <c r="J60" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10336,7 +10289,7 @@
         <v>128</v>
       </c>
       <c r="J61" s="1">
-        <v>3300</v>
+        <v>2200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="129">
   <si>
     <t>_Id</t>
   </si>
@@ -8737,7 +8737,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L61"/>
+  <dimension ref="C3:L53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -8856,7 +8856,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J6" s="1">
         <v>1000</v>
@@ -8882,7 +8882,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J7" s="1">
         <v>1000</v>
@@ -8908,7 +8908,7 @@
         <v>20</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J8" s="1">
         <v>1000</v>
@@ -8934,7 +8934,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J9" s="1">
         <v>1000</v>
@@ -8960,7 +8960,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J10" s="1">
         <v>1000</v>
@@ -8986,7 +8986,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J11" s="1">
         <v>1000</v>
@@ -9012,7 +9012,7 @@
         <v>20</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J12" s="1">
         <v>1000</v>
@@ -9038,7 +9038,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J13" s="1">
         <v>1000</v>
@@ -9064,7 +9064,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J14" s="1">
         <v>1200</v>
@@ -9090,7 +9090,7 @@
         <v>40</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J15" s="1">
         <v>1200</v>
@@ -9116,7 +9116,7 @@
         <v>40</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="1">
         <v>1200</v>
@@ -9142,7 +9142,7 @@
         <v>40</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J17" s="1">
         <v>1200</v>
@@ -9168,7 +9168,7 @@
         <v>40</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J18" s="1">
         <v>1200</v>
@@ -9194,7 +9194,7 @@
         <v>40</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J19" s="1">
         <v>1200</v>
@@ -9220,7 +9220,7 @@
         <v>40</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J20" s="1">
         <v>1200</v>
@@ -9246,7 +9246,7 @@
         <v>40</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J21" s="1">
         <v>1200</v>
@@ -9272,7 +9272,7 @@
         <v>60</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J22" s="1">
         <v>1400</v>
@@ -9298,7 +9298,7 @@
         <v>60</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J23" s="1">
         <v>1400</v>
@@ -9324,7 +9324,7 @@
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J24" s="1">
         <v>1400</v>
@@ -9350,7 +9350,7 @@
         <v>60</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J25" s="1">
         <v>1400</v>
@@ -9376,7 +9376,7 @@
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J26" s="1">
         <v>1400</v>
@@ -9402,7 +9402,7 @@
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J27" s="1">
         <v>1400</v>
@@ -9428,7 +9428,7 @@
         <v>60</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J28" s="1">
         <v>1400</v>
@@ -9454,7 +9454,7 @@
         <v>60</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J29" s="1">
         <v>1400</v>
@@ -9480,7 +9480,7 @@
         <v>80</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J30" s="1">
         <v>1600</v>
@@ -9506,7 +9506,7 @@
         <v>80</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J31" s="1">
         <v>1600</v>
@@ -9532,7 +9532,7 @@
         <v>80</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J32" s="1">
         <v>1600</v>
@@ -9558,7 +9558,7 @@
         <v>80</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J33" s="1">
         <v>1600</v>
@@ -9584,7 +9584,7 @@
         <v>80</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J34" s="1">
         <v>1600</v>
@@ -9610,7 +9610,7 @@
         <v>80</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J35" s="1">
         <v>1600</v>
@@ -9636,7 +9636,7 @@
         <v>80</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J36" s="1">
         <v>1600</v>
@@ -9662,7 +9662,7 @@
         <v>80</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J37" s="1">
         <v>1600</v>
@@ -9688,7 +9688,7 @@
         <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J38" s="1">
         <v>1800</v>
@@ -9714,7 +9714,7 @@
         <v>100</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J39" s="1">
         <v>1800</v>
@@ -9740,7 +9740,7 @@
         <v>100</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J40" s="1">
         <v>1800</v>
@@ -9766,7 +9766,7 @@
         <v>100</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J41" s="1">
         <v>1800</v>
@@ -9792,7 +9792,7 @@
         <v>100</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J42" s="1">
         <v>1800</v>
@@ -9818,7 +9818,7 @@
         <v>100</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J43" s="1">
         <v>1800</v>
@@ -9844,7 +9844,7 @@
         <v>100</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J44" s="1">
         <v>1800</v>
@@ -9870,7 +9870,7 @@
         <v>100</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J45" s="1">
         <v>1800</v>
@@ -9896,7 +9896,7 @@
         <v>140</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J46" s="1">
         <v>2000</v>
@@ -9922,7 +9922,7 @@
         <v>140</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J47" s="1">
         <v>2000</v>
@@ -9948,7 +9948,7 @@
         <v>140</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J48" s="1">
         <v>2000</v>
@@ -9974,7 +9974,7 @@
         <v>140</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J49" s="1">
         <v>2000</v>
@@ -10000,7 +10000,7 @@
         <v>140</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J50" s="1">
         <v>2000</v>
@@ -10026,7 +10026,7 @@
         <v>140</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J51" s="1">
         <v>2000</v>
@@ -10052,7 +10052,7 @@
         <v>140</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J52" s="1">
         <v>2000</v>
@@ -10078,218 +10078,10 @@
         <v>140</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J53" s="1">
         <v>2000</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C54" s="1">
-        <v>2049</v>
-      </c>
-      <c r="D54" s="1">
-        <v>8</v>
-      </c>
-      <c r="E54" s="1">
-        <v>31</v>
-      </c>
-      <c r="F54" s="1">
-        <v>7</v>
-      </c>
-      <c r="G54" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H54" s="1">
-        <v>180</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J54" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C55" s="1">
-        <v>2050</v>
-      </c>
-      <c r="D55" s="1">
-        <v>8</v>
-      </c>
-      <c r="E55" s="1">
-        <v>32</v>
-      </c>
-      <c r="F55" s="1">
-        <v>7</v>
-      </c>
-      <c r="G55" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H55" s="1">
-        <v>180</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J55" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C56" s="1">
-        <v>2051</v>
-      </c>
-      <c r="D56" s="1">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1">
-        <v>33</v>
-      </c>
-      <c r="F56" s="1">
-        <v>7</v>
-      </c>
-      <c r="G56" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H56" s="1">
-        <v>180</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J56" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C57" s="1">
-        <v>2052</v>
-      </c>
-      <c r="D57" s="1">
-        <v>8</v>
-      </c>
-      <c r="E57" s="1">
-        <v>34</v>
-      </c>
-      <c r="F57" s="1">
-        <v>7</v>
-      </c>
-      <c r="G57" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H57" s="1">
-        <v>180</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J57" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C58" s="1">
-        <v>2053</v>
-      </c>
-      <c r="D58" s="1">
-        <v>8</v>
-      </c>
-      <c r="E58" s="1">
-        <v>35</v>
-      </c>
-      <c r="F58" s="1">
-        <v>7</v>
-      </c>
-      <c r="G58" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H58" s="1">
-        <v>180</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J58" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C59" s="1">
-        <v>2054</v>
-      </c>
-      <c r="D59" s="1">
-        <v>8</v>
-      </c>
-      <c r="E59" s="1">
-        <v>37</v>
-      </c>
-      <c r="F59" s="1">
-        <v>7</v>
-      </c>
-      <c r="G59" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H59" s="1">
-        <v>180</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J59" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C60" s="1">
-        <v>2055</v>
-      </c>
-      <c r="D60" s="1">
-        <v>8</v>
-      </c>
-      <c r="E60" s="1">
-        <v>39</v>
-      </c>
-      <c r="F60" s="1">
-        <v>7</v>
-      </c>
-      <c r="G60" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H60" s="1">
-        <v>180</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J60" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C61" s="1">
-        <v>2056</v>
-      </c>
-      <c r="D61" s="1">
-        <v>8</v>
-      </c>
-      <c r="E61" s="1">
-        <v>40</v>
-      </c>
-      <c r="F61" s="1">
-        <v>7</v>
-      </c>
-      <c r="G61" s="1">
-        <v>4026</v>
-      </c>
-      <c r="H61" s="1">
-        <v>180</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J61" s="1">
-        <v>2200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -9275,7 +9275,7 @@
         <v>125</v>
       </c>
       <c r="J22" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9301,7 +9301,7 @@
         <v>125</v>
       </c>
       <c r="J23" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9327,7 +9327,7 @@
         <v>125</v>
       </c>
       <c r="J24" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9353,7 +9353,7 @@
         <v>125</v>
       </c>
       <c r="J25" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9379,7 +9379,7 @@
         <v>125</v>
       </c>
       <c r="J26" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9405,7 +9405,7 @@
         <v>125</v>
       </c>
       <c r="J27" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9431,7 +9431,7 @@
         <v>125</v>
       </c>
       <c r="J28" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9457,7 +9457,7 @@
         <v>125</v>
       </c>
       <c r="J29" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9483,7 +9483,7 @@
         <v>126</v>
       </c>
       <c r="J30" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9509,7 +9509,7 @@
         <v>126</v>
       </c>
       <c r="J31" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9535,7 +9535,7 @@
         <v>126</v>
       </c>
       <c r="J32" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9561,7 +9561,7 @@
         <v>126</v>
       </c>
       <c r="J33" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9587,7 +9587,7 @@
         <v>126</v>
       </c>
       <c r="J34" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9613,7 +9613,7 @@
         <v>126</v>
       </c>
       <c r="J35" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9639,7 +9639,7 @@
         <v>126</v>
       </c>
       <c r="J36" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9665,7 +9665,7 @@
         <v>126</v>
       </c>
       <c r="J37" s="1">
-        <v>1600</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9691,7 +9691,7 @@
         <v>127</v>
       </c>
       <c r="J38" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9717,7 +9717,7 @@
         <v>127</v>
       </c>
       <c r="J39" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9743,7 +9743,7 @@
         <v>127</v>
       </c>
       <c r="J40" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9769,7 +9769,7 @@
         <v>127</v>
       </c>
       <c r="J41" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9795,7 +9795,7 @@
         <v>127</v>
       </c>
       <c r="J42" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9821,7 +9821,7 @@
         <v>127</v>
       </c>
       <c r="J43" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9847,7 +9847,7 @@
         <v>127</v>
       </c>
       <c r="J44" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9873,7 +9873,7 @@
         <v>127</v>
       </c>
       <c r="J45" s="1">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9899,7 +9899,7 @@
         <v>128</v>
       </c>
       <c r="J46" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9925,7 +9925,7 @@
         <v>128</v>
       </c>
       <c r="J47" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9951,7 +9951,7 @@
         <v>128</v>
       </c>
       <c r="J48" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -9977,7 +9977,7 @@
         <v>128</v>
       </c>
       <c r="J49" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10003,7 +10003,7 @@
         <v>128</v>
       </c>
       <c r="J50" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10029,7 +10029,7 @@
         <v>128</v>
       </c>
       <c r="J51" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10055,7 +10055,7 @@
         <v>128</v>
       </c>
       <c r="J52" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -10081,7 +10081,7 @@
         <v>128</v>
       </c>
       <c r="J53" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="130">
   <si>
     <t>_Id</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>50000110</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>50000111</t>
@@ -1374,7 +1377,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L165"/>
+  <dimension ref="A3:L165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -5425,7 +5428,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="3:10">
+    <row r="158" customHeight="1" spans="1:10">
+      <c r="A158" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C158" s="1">
         <v>153</v>
       </c>
@@ -5445,13 +5454,19 @@
         <v>191</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J158" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="3:10">
+    <row r="159" customHeight="1" spans="1:10">
+      <c r="A159" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C159" s="1">
         <v>154</v>
       </c>
@@ -5471,13 +5486,19 @@
         <v>191</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J159" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="160" customHeight="1" spans="3:10">
+    <row r="160" customHeight="1" spans="1:10">
+      <c r="A160" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C160" s="1">
         <v>155</v>
       </c>
@@ -5497,13 +5518,19 @@
         <v>191</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J160" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="3:10">
+    <row r="161" customHeight="1" spans="1:10">
+      <c r="A161" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C161" s="1">
         <v>156</v>
       </c>
@@ -5523,13 +5550,19 @@
         <v>191</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J161" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="3:10">
+    <row r="162" customHeight="1" spans="1:10">
+      <c r="A162" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C162" s="1">
         <v>157</v>
       </c>
@@ -5549,13 +5582,19 @@
         <v>191</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J162" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="3:10">
+    <row r="163" customHeight="1" spans="1:10">
+      <c r="A163" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C163" s="1">
         <v>158</v>
       </c>
@@ -5575,13 +5614,19 @@
         <v>191</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J163" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="3:10">
+    <row r="164" customHeight="1" spans="1:10">
+      <c r="A164" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C164" s="1">
         <v>159</v>
       </c>
@@ -5601,13 +5646,19 @@
         <v>191</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J164" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="3:10">
+    <row r="165" customHeight="1" spans="1:10">
+      <c r="A165" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C165" s="1">
         <v>160</v>
       </c>
@@ -5627,7 +5678,7 @@
         <v>191</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J165" s="1">
         <v>220</v>
@@ -8535,7 +8586,7 @@
         <v>200</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J110" s="1">
         <v>2200</v>
@@ -8561,7 +8612,7 @@
         <v>200</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J111" s="1">
         <v>2200</v>
@@ -8587,7 +8638,7 @@
         <v>200</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J112" s="1">
         <v>2200</v>
@@ -8613,7 +8664,7 @@
         <v>200</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J113" s="1">
         <v>2200</v>
@@ -8639,7 +8690,7 @@
         <v>200</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J114" s="1">
         <v>2200</v>
@@ -8665,7 +8716,7 @@
         <v>200</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J115" s="1">
         <v>2200</v>
@@ -8691,7 +8742,7 @@
         <v>200</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J116" s="1">
         <v>2200</v>
@@ -8717,7 +8768,7 @@
         <v>200</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J117" s="1">
         <v>2200</v>
@@ -9896,7 +9947,7 @@
         <v>140</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J46" s="1">
         <v>3000</v>
@@ -9922,7 +9973,7 @@
         <v>140</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J47" s="1">
         <v>3000</v>
@@ -9948,7 +9999,7 @@
         <v>140</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J48" s="1">
         <v>3000</v>
@@ -9974,7 +10025,7 @@
         <v>140</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J49" s="1">
         <v>3000</v>
@@ -10000,7 +10051,7 @@
         <v>140</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J50" s="1">
         <v>3000</v>
@@ -10026,7 +10077,7 @@
         <v>140</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J51" s="1">
         <v>3000</v>
@@ -10052,7 +10103,7 @@
         <v>140</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J52" s="1">
         <v>3000</v>
@@ -10078,7 +10129,7 @@
         <v>140</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J53" s="1">
         <v>3000</v>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="131">
   <si>
     <t>_Id</t>
   </si>
@@ -419,6 +419,9 @@
   </si>
   <si>
     <t>50000111</t>
+  </si>
+  <si>
+    <t>50000112</t>
   </si>
 </sst>
 </file>
@@ -5698,7 +5701,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L117"/>
+  <dimension ref="C3:L125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -8774,6 +8777,214 @@
         <v>2200</v>
       </c>
     </row>
+    <row r="118" customHeight="1" spans="3:10">
+      <c r="C118" s="1">
+        <v>1113</v>
+      </c>
+      <c r="D118" s="1">
+        <v>7</v>
+      </c>
+      <c r="E118" s="1">
+        <v>21</v>
+      </c>
+      <c r="F118" s="1">
+        <v>15</v>
+      </c>
+      <c r="G118" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H118" s="1">
+        <v>200</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J118" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:10">
+      <c r="C119" s="1">
+        <v>1114</v>
+      </c>
+      <c r="D119" s="1">
+        <v>7</v>
+      </c>
+      <c r="E119" s="1">
+        <v>22</v>
+      </c>
+      <c r="F119" s="1">
+        <v>15</v>
+      </c>
+      <c r="G119" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H119" s="1">
+        <v>200</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J119" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:10">
+      <c r="C120" s="1">
+        <v>1115</v>
+      </c>
+      <c r="D120" s="1">
+        <v>7</v>
+      </c>
+      <c r="E120" s="1">
+        <v>23</v>
+      </c>
+      <c r="F120" s="1">
+        <v>15</v>
+      </c>
+      <c r="G120" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H120" s="1">
+        <v>200</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J120" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:10">
+      <c r="C121" s="1">
+        <v>1116</v>
+      </c>
+      <c r="D121" s="1">
+        <v>7</v>
+      </c>
+      <c r="E121" s="1">
+        <v>24</v>
+      </c>
+      <c r="F121" s="1">
+        <v>15</v>
+      </c>
+      <c r="G121" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H121" s="1">
+        <v>200</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J121" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:10">
+      <c r="C122" s="1">
+        <v>1117</v>
+      </c>
+      <c r="D122" s="1">
+        <v>7</v>
+      </c>
+      <c r="E122" s="1">
+        <v>25</v>
+      </c>
+      <c r="F122" s="1">
+        <v>15</v>
+      </c>
+      <c r="G122" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H122" s="1">
+        <v>200</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J122" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:10">
+      <c r="C123" s="1">
+        <v>1118</v>
+      </c>
+      <c r="D123" s="1">
+        <v>7</v>
+      </c>
+      <c r="E123" s="1">
+        <v>27</v>
+      </c>
+      <c r="F123" s="1">
+        <v>15</v>
+      </c>
+      <c r="G123" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H123" s="1">
+        <v>200</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J123" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:10">
+      <c r="C124" s="1">
+        <v>1119</v>
+      </c>
+      <c r="D124" s="1">
+        <v>7</v>
+      </c>
+      <c r="E124" s="1">
+        <v>29</v>
+      </c>
+      <c r="F124" s="1">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H124" s="1">
+        <v>200</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J124" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:10">
+      <c r="C125" s="1">
+        <v>1120</v>
+      </c>
+      <c r="D125" s="1">
+        <v>7</v>
+      </c>
+      <c r="E125" s="1">
+        <v>30</v>
+      </c>
+      <c r="F125" s="1">
+        <v>15</v>
+      </c>
+      <c r="G125" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H125" s="1">
+        <v>200</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J125" s="1">
+        <v>2400</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">
@@ -8788,7 +8999,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L53"/>
+  <dimension ref="C3:L61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -10135,6 +10346,214 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="54" customHeight="1" spans="3:10">
+      <c r="C54" s="1">
+        <v>2049</v>
+      </c>
+      <c r="D54" s="1">
+        <v>8</v>
+      </c>
+      <c r="E54" s="1">
+        <v>31</v>
+      </c>
+      <c r="F54" s="1">
+        <v>7</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H54" s="1">
+        <v>160</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J54" s="1">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:10">
+      <c r="C55" s="1">
+        <v>2050</v>
+      </c>
+      <c r="D55" s="1">
+        <v>8</v>
+      </c>
+      <c r="E55" s="1">
+        <v>32</v>
+      </c>
+      <c r="F55" s="1">
+        <v>7</v>
+      </c>
+      <c r="G55" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H55" s="1">
+        <v>160</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J55" s="1">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:10">
+      <c r="C56" s="1">
+        <v>2051</v>
+      </c>
+      <c r="D56" s="1">
+        <v>8</v>
+      </c>
+      <c r="E56" s="1">
+        <v>33</v>
+      </c>
+      <c r="F56" s="1">
+        <v>7</v>
+      </c>
+      <c r="G56" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H56" s="1">
+        <v>160</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J56" s="1">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:10">
+      <c r="C57" s="1">
+        <v>2052</v>
+      </c>
+      <c r="D57" s="1">
+        <v>8</v>
+      </c>
+      <c r="E57" s="1">
+        <v>34</v>
+      </c>
+      <c r="F57" s="1">
+        <v>7</v>
+      </c>
+      <c r="G57" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H57" s="1">
+        <v>160</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J57" s="1">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:10">
+      <c r="C58" s="1">
+        <v>2053</v>
+      </c>
+      <c r="D58" s="1">
+        <v>8</v>
+      </c>
+      <c r="E58" s="1">
+        <v>35</v>
+      </c>
+      <c r="F58" s="1">
+        <v>7</v>
+      </c>
+      <c r="G58" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H58" s="1">
+        <v>160</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J58" s="1">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
+        <v>2054</v>
+      </c>
+      <c r="D59" s="1">
+        <v>8</v>
+      </c>
+      <c r="E59" s="1">
+        <v>37</v>
+      </c>
+      <c r="F59" s="1">
+        <v>7</v>
+      </c>
+      <c r="G59" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H59" s="1">
+        <v>160</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J59" s="1">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>2055</v>
+      </c>
+      <c r="D60" s="1">
+        <v>8</v>
+      </c>
+      <c r="E60" s="1">
+        <v>39</v>
+      </c>
+      <c r="F60" s="1">
+        <v>7</v>
+      </c>
+      <c r="G60" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H60" s="1">
+        <v>160</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J60" s="1">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:10">
+      <c r="C61" s="1">
+        <v>2056</v>
+      </c>
+      <c r="D61" s="1">
+        <v>8</v>
+      </c>
+      <c r="E61" s="1">
+        <v>40</v>
+      </c>
+      <c r="F61" s="1">
+        <v>7</v>
+      </c>
+      <c r="G61" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H61" s="1">
+        <v>160</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J61" s="1">
+        <v>3600</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -10,6 +10,7 @@
     <sheet name="红色" sheetId="1" r:id="rId1"/>
     <sheet name="金色" sheetId="2" r:id="rId2"/>
     <sheet name="暗金" sheetId="3" r:id="rId3"/>
+    <sheet name="混沌" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="137">
   <si>
     <t>_Id</t>
   </si>
@@ -422,6 +423,24 @@
   </si>
   <si>
     <t>50000112</t>
+  </si>
+  <si>
+    <t>50000113</t>
+  </si>
+  <si>
+    <t>50000114</t>
+  </si>
+  <si>
+    <t>50000115</t>
+  </si>
+  <si>
+    <t>50000116</t>
+  </si>
+  <si>
+    <t>50000117</t>
+  </si>
+  <si>
+    <t>50000118</t>
   </si>
 </sst>
 </file>
@@ -5701,7 +5720,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L125"/>
+  <dimension ref="C3:L133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -8985,6 +9004,214 @@
         <v>2400</v>
       </c>
     </row>
+    <row r="126" customHeight="1" spans="3:10">
+      <c r="C126" s="1">
+        <v>1121</v>
+      </c>
+      <c r="D126" s="1">
+        <v>7</v>
+      </c>
+      <c r="E126" s="1">
+        <v>21</v>
+      </c>
+      <c r="F126" s="1">
+        <v>16</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H126" s="1">
+        <v>200</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J126" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:10">
+      <c r="C127" s="1">
+        <v>1122</v>
+      </c>
+      <c r="D127" s="1">
+        <v>7</v>
+      </c>
+      <c r="E127" s="1">
+        <v>22</v>
+      </c>
+      <c r="F127" s="1">
+        <v>16</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H127" s="1">
+        <v>200</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J127" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:10">
+      <c r="C128" s="1">
+        <v>1123</v>
+      </c>
+      <c r="D128" s="1">
+        <v>7</v>
+      </c>
+      <c r="E128" s="1">
+        <v>23</v>
+      </c>
+      <c r="F128" s="1">
+        <v>16</v>
+      </c>
+      <c r="G128" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H128" s="1">
+        <v>200</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J128" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:10">
+      <c r="C129" s="1">
+        <v>1124</v>
+      </c>
+      <c r="D129" s="1">
+        <v>7</v>
+      </c>
+      <c r="E129" s="1">
+        <v>24</v>
+      </c>
+      <c r="F129" s="1">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H129" s="1">
+        <v>200</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J129" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:10">
+      <c r="C130" s="1">
+        <v>1125</v>
+      </c>
+      <c r="D130" s="1">
+        <v>7</v>
+      </c>
+      <c r="E130" s="1">
+        <v>25</v>
+      </c>
+      <c r="F130" s="1">
+        <v>16</v>
+      </c>
+      <c r="G130" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H130" s="1">
+        <v>200</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J130" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:10">
+      <c r="C131" s="1">
+        <v>1126</v>
+      </c>
+      <c r="D131" s="1">
+        <v>7</v>
+      </c>
+      <c r="E131" s="1">
+        <v>27</v>
+      </c>
+      <c r="F131" s="1">
+        <v>16</v>
+      </c>
+      <c r="G131" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H131" s="1">
+        <v>200</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J131" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:10">
+      <c r="C132" s="1">
+        <v>1127</v>
+      </c>
+      <c r="D132" s="1">
+        <v>7</v>
+      </c>
+      <c r="E132" s="1">
+        <v>29</v>
+      </c>
+      <c r="F132" s="1">
+        <v>16</v>
+      </c>
+      <c r="G132" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H132" s="1">
+        <v>200</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J132" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:10">
+      <c r="C133" s="1">
+        <v>1128</v>
+      </c>
+      <c r="D133" s="1">
+        <v>7</v>
+      </c>
+      <c r="E133" s="1">
+        <v>30</v>
+      </c>
+      <c r="F133" s="1">
+        <v>16</v>
+      </c>
+      <c r="G133" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H133" s="1">
+        <v>200</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J133" s="1">
+        <v>2600</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">
@@ -8999,7 +9226,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L61"/>
+  <dimension ref="C3:L69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -10554,6 +10781,1575 @@
         <v>3600</v>
       </c>
     </row>
+    <row r="62" customHeight="1" spans="3:10">
+      <c r="C62" s="1">
+        <v>2057</v>
+      </c>
+      <c r="D62" s="1">
+        <v>8</v>
+      </c>
+      <c r="E62" s="1">
+        <v>31</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8</v>
+      </c>
+      <c r="G62" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H62" s="1">
+        <v>180</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
+      <c r="C63" s="1">
+        <v>2058</v>
+      </c>
+      <c r="D63" s="1">
+        <v>8</v>
+      </c>
+      <c r="E63" s="1">
+        <v>32</v>
+      </c>
+      <c r="F63" s="1">
+        <v>8</v>
+      </c>
+      <c r="G63" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H63" s="1">
+        <v>180</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>2059</v>
+      </c>
+      <c r="D64" s="1">
+        <v>8</v>
+      </c>
+      <c r="E64" s="1">
+        <v>33</v>
+      </c>
+      <c r="F64" s="1">
+        <v>8</v>
+      </c>
+      <c r="G64" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H64" s="1">
+        <v>180</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J64" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>2060</v>
+      </c>
+      <c r="D65" s="1">
+        <v>8</v>
+      </c>
+      <c r="E65" s="1">
+        <v>34</v>
+      </c>
+      <c r="F65" s="1">
+        <v>8</v>
+      </c>
+      <c r="G65" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H65" s="1">
+        <v>180</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J65" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
+        <v>2061</v>
+      </c>
+      <c r="D66" s="1">
+        <v>8</v>
+      </c>
+      <c r="E66" s="1">
+        <v>35</v>
+      </c>
+      <c r="F66" s="1">
+        <v>8</v>
+      </c>
+      <c r="G66" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H66" s="1">
+        <v>180</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="1">
+        <v>2062</v>
+      </c>
+      <c r="D67" s="1">
+        <v>8</v>
+      </c>
+      <c r="E67" s="1">
+        <v>37</v>
+      </c>
+      <c r="F67" s="1">
+        <v>8</v>
+      </c>
+      <c r="G67" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H67" s="1">
+        <v>180</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J67" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="1">
+        <v>2063</v>
+      </c>
+      <c r="D68" s="1">
+        <v>8</v>
+      </c>
+      <c r="E68" s="1">
+        <v>39</v>
+      </c>
+      <c r="F68" s="1">
+        <v>8</v>
+      </c>
+      <c r="G68" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H68" s="1">
+        <v>180</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J68" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="1">
+        <v>2064</v>
+      </c>
+      <c r="D69" s="1">
+        <v>8</v>
+      </c>
+      <c r="E69" s="1">
+        <v>40</v>
+      </c>
+      <c r="F69" s="1">
+        <v>8</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H69" s="1">
+        <v>180</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J69" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:L53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="11.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C6" s="1">
+        <v>3001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
+        <v>41</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C7" s="1">
+        <v>3002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C8" s="1">
+        <v>3003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C9" s="1">
+        <v>3004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C10" s="1">
+        <v>3005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
+        <v>45</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C11" s="1">
+        <v>3006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1">
+        <v>47</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C12" s="1">
+        <v>3007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
+        <v>49</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C13" s="1">
+        <v>3008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C14" s="1">
+        <v>3009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1">
+        <v>41</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H14" s="1">
+        <v>40</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C15" s="1">
+        <v>3010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1">
+        <v>42</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H15" s="1">
+        <v>40</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J15" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C16" s="1">
+        <v>3011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1">
+        <v>43</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H16" s="1">
+        <v>40</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C17" s="1">
+        <v>3012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1">
+        <v>44</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H17" s="1">
+        <v>40</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J17" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C18" s="1">
+        <v>3013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1">
+        <v>45</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H18" s="1">
+        <v>40</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C19" s="1">
+        <v>3014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1">
+        <v>47</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H19" s="1">
+        <v>40</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J19" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C20" s="1">
+        <v>3015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1">
+        <v>49</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H20" s="1">
+        <v>40</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J20" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C21" s="1">
+        <v>3016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>9</v>
+      </c>
+      <c r="E21" s="1">
+        <v>50</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H21" s="1">
+        <v>40</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J21" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C22" s="1">
+        <v>3017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1">
+        <v>41</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H22" s="1">
+        <v>60</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J22" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C23" s="1">
+        <v>3018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1">
+        <v>42</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H23" s="1">
+        <v>60</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J23" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C24" s="1">
+        <v>3019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9</v>
+      </c>
+      <c r="E24" s="1">
+        <v>43</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H24" s="1">
+        <v>60</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C25" s="1">
+        <v>3020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1">
+        <v>44</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H25" s="1">
+        <v>60</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C26" s="1">
+        <v>3021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1">
+        <v>45</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H26" s="1">
+        <v>60</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C27" s="1">
+        <v>3022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1">
+        <v>47</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H27" s="1">
+        <v>60</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C28" s="1">
+        <v>3023</v>
+      </c>
+      <c r="D28" s="1">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1">
+        <v>49</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H28" s="1">
+        <v>60</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C29" s="1">
+        <v>3024</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1">
+        <v>50</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H29" s="1">
+        <v>60</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J29" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>3025</v>
+      </c>
+      <c r="D30" s="1">
+        <v>9</v>
+      </c>
+      <c r="E30" s="1">
+        <v>41</v>
+      </c>
+      <c r="F30" s="1">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H30" s="1">
+        <v>80</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J30" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>3026</v>
+      </c>
+      <c r="D31" s="1">
+        <v>9</v>
+      </c>
+      <c r="E31" s="1">
+        <v>42</v>
+      </c>
+      <c r="F31" s="1">
+        <v>4</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H31" s="1">
+        <v>80</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>3027</v>
+      </c>
+      <c r="D32" s="1">
+        <v>9</v>
+      </c>
+      <c r="E32" s="1">
+        <v>43</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H32" s="1">
+        <v>80</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>3028</v>
+      </c>
+      <c r="D33" s="1">
+        <v>9</v>
+      </c>
+      <c r="E33" s="1">
+        <v>44</v>
+      </c>
+      <c r="F33" s="1">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H33" s="1">
+        <v>80</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>3029</v>
+      </c>
+      <c r="D34" s="1">
+        <v>9</v>
+      </c>
+      <c r="E34" s="1">
+        <v>45</v>
+      </c>
+      <c r="F34" s="1">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H34" s="1">
+        <v>80</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>3030</v>
+      </c>
+      <c r="D35" s="1">
+        <v>9</v>
+      </c>
+      <c r="E35" s="1">
+        <v>47</v>
+      </c>
+      <c r="F35" s="1">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H35" s="1">
+        <v>80</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>3031</v>
+      </c>
+      <c r="D36" s="1">
+        <v>9</v>
+      </c>
+      <c r="E36" s="1">
+        <v>49</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H36" s="1">
+        <v>80</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>3032</v>
+      </c>
+      <c r="D37" s="1">
+        <v>9</v>
+      </c>
+      <c r="E37" s="1">
+        <v>50</v>
+      </c>
+      <c r="F37" s="1">
+        <v>4</v>
+      </c>
+      <c r="G37" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H37" s="1">
+        <v>80</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C38" s="1">
+        <v>3033</v>
+      </c>
+      <c r="D38" s="1">
+        <v>9</v>
+      </c>
+      <c r="E38" s="1">
+        <v>41</v>
+      </c>
+      <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H38" s="1">
+        <v>100</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J38" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C39" s="1">
+        <v>3034</v>
+      </c>
+      <c r="D39" s="1">
+        <v>9</v>
+      </c>
+      <c r="E39" s="1">
+        <v>42</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H39" s="1">
+        <v>100</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J39" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C40" s="1">
+        <v>3035</v>
+      </c>
+      <c r="D40" s="1">
+        <v>9</v>
+      </c>
+      <c r="E40" s="1">
+        <v>43</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H40" s="1">
+        <v>100</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J40" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>3036</v>
+      </c>
+      <c r="D41" s="1">
+        <v>9</v>
+      </c>
+      <c r="E41" s="1">
+        <v>44</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H41" s="1">
+        <v>100</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J41" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>3037</v>
+      </c>
+      <c r="D42" s="1">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1">
+        <v>45</v>
+      </c>
+      <c r="F42" s="1">
+        <v>5</v>
+      </c>
+      <c r="G42" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H42" s="1">
+        <v>100</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J42" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C43" s="1">
+        <v>3038</v>
+      </c>
+      <c r="D43" s="1">
+        <v>9</v>
+      </c>
+      <c r="E43" s="1">
+        <v>47</v>
+      </c>
+      <c r="F43" s="1">
+        <v>5</v>
+      </c>
+      <c r="G43" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H43" s="1">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J43" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C44" s="1">
+        <v>3039</v>
+      </c>
+      <c r="D44" s="1">
+        <v>9</v>
+      </c>
+      <c r="E44" s="1">
+        <v>49</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H44" s="1">
+        <v>100</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J44" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C45" s="1">
+        <v>3040</v>
+      </c>
+      <c r="D45" s="1">
+        <v>9</v>
+      </c>
+      <c r="E45" s="1">
+        <v>50</v>
+      </c>
+      <c r="F45" s="1">
+        <v>5</v>
+      </c>
+      <c r="G45" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H45" s="1">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J45" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C46" s="1">
+        <v>3041</v>
+      </c>
+      <c r="D46" s="1">
+        <v>9</v>
+      </c>
+      <c r="E46" s="1">
+        <v>41</v>
+      </c>
+      <c r="F46" s="1">
+        <v>6</v>
+      </c>
+      <c r="G46" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H46" s="1">
+        <v>140</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J46" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C47" s="1">
+        <v>3042</v>
+      </c>
+      <c r="D47" s="1">
+        <v>9</v>
+      </c>
+      <c r="E47" s="1">
+        <v>42</v>
+      </c>
+      <c r="F47" s="1">
+        <v>6</v>
+      </c>
+      <c r="G47" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H47" s="1">
+        <v>140</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J47" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C48" s="1">
+        <v>3043</v>
+      </c>
+      <c r="D48" s="1">
+        <v>9</v>
+      </c>
+      <c r="E48" s="1">
+        <v>43</v>
+      </c>
+      <c r="F48" s="1">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H48" s="1">
+        <v>140</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J48" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C49" s="1">
+        <v>3044</v>
+      </c>
+      <c r="D49" s="1">
+        <v>9</v>
+      </c>
+      <c r="E49" s="1">
+        <v>44</v>
+      </c>
+      <c r="F49" s="1">
+        <v>6</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H49" s="1">
+        <v>140</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J49" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C50" s="1">
+        <v>3045</v>
+      </c>
+      <c r="D50" s="1">
+        <v>9</v>
+      </c>
+      <c r="E50" s="1">
+        <v>45</v>
+      </c>
+      <c r="F50" s="1">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H50" s="1">
+        <v>140</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C51" s="1">
+        <v>3046</v>
+      </c>
+      <c r="D51" s="1">
+        <v>9</v>
+      </c>
+      <c r="E51" s="1">
+        <v>47</v>
+      </c>
+      <c r="F51" s="1">
+        <v>6</v>
+      </c>
+      <c r="G51" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H51" s="1">
+        <v>140</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J51" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C52" s="1">
+        <v>3047</v>
+      </c>
+      <c r="D52" s="1">
+        <v>9</v>
+      </c>
+      <c r="E52" s="1">
+        <v>49</v>
+      </c>
+      <c r="F52" s="1">
+        <v>6</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H52" s="1">
+        <v>140</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J52" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C53" s="1">
+        <v>3048</v>
+      </c>
+      <c r="D53" s="1">
+        <v>9</v>
+      </c>
+      <c r="E53" s="1">
+        <v>50</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H53" s="1">
+        <v>140</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J53" s="1">
+        <v>7000</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="137">
   <si>
     <t>_Id</t>
   </si>
@@ -5720,7 +5720,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L133"/>
+  <dimension ref="C3:L165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -9212,6 +9212,838 @@
         <v>2600</v>
       </c>
     </row>
+    <row r="134" customHeight="1" spans="3:10">
+      <c r="C134" s="1">
+        <v>1129</v>
+      </c>
+      <c r="D134" s="1">
+        <v>7</v>
+      </c>
+      <c r="E134" s="1">
+        <v>21</v>
+      </c>
+      <c r="F134" s="1">
+        <v>17</v>
+      </c>
+      <c r="G134" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H134" s="1">
+        <v>200</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J134" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:10">
+      <c r="C135" s="1">
+        <v>1130</v>
+      </c>
+      <c r="D135" s="1">
+        <v>7</v>
+      </c>
+      <c r="E135" s="1">
+        <v>22</v>
+      </c>
+      <c r="F135" s="1">
+        <v>17</v>
+      </c>
+      <c r="G135" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H135" s="1">
+        <v>200</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J135" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:10">
+      <c r="C136" s="1">
+        <v>1131</v>
+      </c>
+      <c r="D136" s="1">
+        <v>7</v>
+      </c>
+      <c r="E136" s="1">
+        <v>23</v>
+      </c>
+      <c r="F136" s="1">
+        <v>17</v>
+      </c>
+      <c r="G136" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H136" s="1">
+        <v>200</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J136" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:10">
+      <c r="C137" s="1">
+        <v>1132</v>
+      </c>
+      <c r="D137" s="1">
+        <v>7</v>
+      </c>
+      <c r="E137" s="1">
+        <v>24</v>
+      </c>
+      <c r="F137" s="1">
+        <v>17</v>
+      </c>
+      <c r="G137" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H137" s="1">
+        <v>200</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J137" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:10">
+      <c r="C138" s="1">
+        <v>1133</v>
+      </c>
+      <c r="D138" s="1">
+        <v>7</v>
+      </c>
+      <c r="E138" s="1">
+        <v>25</v>
+      </c>
+      <c r="F138" s="1">
+        <v>17</v>
+      </c>
+      <c r="G138" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H138" s="1">
+        <v>200</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J138" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:10">
+      <c r="C139" s="1">
+        <v>1134</v>
+      </c>
+      <c r="D139" s="1">
+        <v>7</v>
+      </c>
+      <c r="E139" s="1">
+        <v>27</v>
+      </c>
+      <c r="F139" s="1">
+        <v>17</v>
+      </c>
+      <c r="G139" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H139" s="1">
+        <v>200</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J139" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:10">
+      <c r="C140" s="1">
+        <v>1135</v>
+      </c>
+      <c r="D140" s="1">
+        <v>7</v>
+      </c>
+      <c r="E140" s="1">
+        <v>29</v>
+      </c>
+      <c r="F140" s="1">
+        <v>17</v>
+      </c>
+      <c r="G140" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H140" s="1">
+        <v>200</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J140" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:10">
+      <c r="C141" s="1">
+        <v>1136</v>
+      </c>
+      <c r="D141" s="1">
+        <v>7</v>
+      </c>
+      <c r="E141" s="1">
+        <v>30</v>
+      </c>
+      <c r="F141" s="1">
+        <v>17</v>
+      </c>
+      <c r="G141" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H141" s="1">
+        <v>200</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J141" s="1">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:10">
+      <c r="C142" s="1">
+        <v>1137</v>
+      </c>
+      <c r="D142" s="1">
+        <v>7</v>
+      </c>
+      <c r="E142" s="1">
+        <v>21</v>
+      </c>
+      <c r="F142" s="1">
+        <v>18</v>
+      </c>
+      <c r="G142" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H142" s="1">
+        <v>200</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J142" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:10">
+      <c r="C143" s="1">
+        <v>1138</v>
+      </c>
+      <c r="D143" s="1">
+        <v>7</v>
+      </c>
+      <c r="E143" s="1">
+        <v>22</v>
+      </c>
+      <c r="F143" s="1">
+        <v>18</v>
+      </c>
+      <c r="G143" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H143" s="1">
+        <v>200</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J143" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:10">
+      <c r="C144" s="1">
+        <v>1139</v>
+      </c>
+      <c r="D144" s="1">
+        <v>7</v>
+      </c>
+      <c r="E144" s="1">
+        <v>23</v>
+      </c>
+      <c r="F144" s="1">
+        <v>18</v>
+      </c>
+      <c r="G144" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H144" s="1">
+        <v>200</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J144" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:10">
+      <c r="C145" s="1">
+        <v>1140</v>
+      </c>
+      <c r="D145" s="1">
+        <v>7</v>
+      </c>
+      <c r="E145" s="1">
+        <v>24</v>
+      </c>
+      <c r="F145" s="1">
+        <v>18</v>
+      </c>
+      <c r="G145" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H145" s="1">
+        <v>200</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J145" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:10">
+      <c r="C146" s="1">
+        <v>1141</v>
+      </c>
+      <c r="D146" s="1">
+        <v>7</v>
+      </c>
+      <c r="E146" s="1">
+        <v>25</v>
+      </c>
+      <c r="F146" s="1">
+        <v>18</v>
+      </c>
+      <c r="G146" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H146" s="1">
+        <v>200</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J146" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:10">
+      <c r="C147" s="1">
+        <v>1142</v>
+      </c>
+      <c r="D147" s="1">
+        <v>7</v>
+      </c>
+      <c r="E147" s="1">
+        <v>27</v>
+      </c>
+      <c r="F147" s="1">
+        <v>18</v>
+      </c>
+      <c r="G147" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H147" s="1">
+        <v>200</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J147" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:10">
+      <c r="C148" s="1">
+        <v>1143</v>
+      </c>
+      <c r="D148" s="1">
+        <v>7</v>
+      </c>
+      <c r="E148" s="1">
+        <v>29</v>
+      </c>
+      <c r="F148" s="1">
+        <v>18</v>
+      </c>
+      <c r="G148" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H148" s="1">
+        <v>200</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J148" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:10">
+      <c r="C149" s="1">
+        <v>1144</v>
+      </c>
+      <c r="D149" s="1">
+        <v>7</v>
+      </c>
+      <c r="E149" s="1">
+        <v>30</v>
+      </c>
+      <c r="F149" s="1">
+        <v>18</v>
+      </c>
+      <c r="G149" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H149" s="1">
+        <v>200</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J149" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:10">
+      <c r="C150" s="1">
+        <v>1145</v>
+      </c>
+      <c r="D150" s="1">
+        <v>7</v>
+      </c>
+      <c r="E150" s="1">
+        <v>21</v>
+      </c>
+      <c r="F150" s="1">
+        <v>19</v>
+      </c>
+      <c r="G150" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H150" s="1">
+        <v>200</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J150" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:10">
+      <c r="C151" s="1">
+        <v>1146</v>
+      </c>
+      <c r="D151" s="1">
+        <v>7</v>
+      </c>
+      <c r="E151" s="1">
+        <v>22</v>
+      </c>
+      <c r="F151" s="1">
+        <v>19</v>
+      </c>
+      <c r="G151" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H151" s="1">
+        <v>200</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J151" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:10">
+      <c r="C152" s="1">
+        <v>1147</v>
+      </c>
+      <c r="D152" s="1">
+        <v>7</v>
+      </c>
+      <c r="E152" s="1">
+        <v>23</v>
+      </c>
+      <c r="F152" s="1">
+        <v>19</v>
+      </c>
+      <c r="G152" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H152" s="1">
+        <v>200</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J152" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:10">
+      <c r="C153" s="1">
+        <v>1148</v>
+      </c>
+      <c r="D153" s="1">
+        <v>7</v>
+      </c>
+      <c r="E153" s="1">
+        <v>24</v>
+      </c>
+      <c r="F153" s="1">
+        <v>19</v>
+      </c>
+      <c r="G153" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H153" s="1">
+        <v>200</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J153" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:10">
+      <c r="C154" s="1">
+        <v>1149</v>
+      </c>
+      <c r="D154" s="1">
+        <v>7</v>
+      </c>
+      <c r="E154" s="1">
+        <v>25</v>
+      </c>
+      <c r="F154" s="1">
+        <v>19</v>
+      </c>
+      <c r="G154" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H154" s="1">
+        <v>200</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J154" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:10">
+      <c r="C155" s="1">
+        <v>1150</v>
+      </c>
+      <c r="D155" s="1">
+        <v>7</v>
+      </c>
+      <c r="E155" s="1">
+        <v>27</v>
+      </c>
+      <c r="F155" s="1">
+        <v>19</v>
+      </c>
+      <c r="G155" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H155" s="1">
+        <v>200</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J155" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:10">
+      <c r="C156" s="1">
+        <v>1151</v>
+      </c>
+      <c r="D156" s="1">
+        <v>7</v>
+      </c>
+      <c r="E156" s="1">
+        <v>29</v>
+      </c>
+      <c r="F156" s="1">
+        <v>19</v>
+      </c>
+      <c r="G156" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H156" s="1">
+        <v>200</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J156" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:10">
+      <c r="C157" s="1">
+        <v>1152</v>
+      </c>
+      <c r="D157" s="1">
+        <v>7</v>
+      </c>
+      <c r="E157" s="1">
+        <v>30</v>
+      </c>
+      <c r="F157" s="1">
+        <v>19</v>
+      </c>
+      <c r="G157" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H157" s="1">
+        <v>200</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J157" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="3:10">
+      <c r="C158" s="1">
+        <v>1153</v>
+      </c>
+      <c r="D158" s="1">
+        <v>7</v>
+      </c>
+      <c r="E158" s="1">
+        <v>21</v>
+      </c>
+      <c r="F158" s="1">
+        <v>20</v>
+      </c>
+      <c r="G158" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H158" s="1">
+        <v>200</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J158" s="1">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="3:10">
+      <c r="C159" s="1">
+        <v>1154</v>
+      </c>
+      <c r="D159" s="1">
+        <v>7</v>
+      </c>
+      <c r="E159" s="1">
+        <v>22</v>
+      </c>
+      <c r="F159" s="1">
+        <v>20</v>
+      </c>
+      <c r="G159" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H159" s="1">
+        <v>200</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J159" s="1">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="3:10">
+      <c r="C160" s="1">
+        <v>1155</v>
+      </c>
+      <c r="D160" s="1">
+        <v>7</v>
+      </c>
+      <c r="E160" s="1">
+        <v>23</v>
+      </c>
+      <c r="F160" s="1">
+        <v>20</v>
+      </c>
+      <c r="G160" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H160" s="1">
+        <v>200</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J160" s="1">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:10">
+      <c r="C161" s="1">
+        <v>1156</v>
+      </c>
+      <c r="D161" s="1">
+        <v>7</v>
+      </c>
+      <c r="E161" s="1">
+        <v>24</v>
+      </c>
+      <c r="F161" s="1">
+        <v>20</v>
+      </c>
+      <c r="G161" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H161" s="1">
+        <v>200</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J161" s="1">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="3:10">
+      <c r="C162" s="1">
+        <v>1157</v>
+      </c>
+      <c r="D162" s="1">
+        <v>7</v>
+      </c>
+      <c r="E162" s="1">
+        <v>25</v>
+      </c>
+      <c r="F162" s="1">
+        <v>20</v>
+      </c>
+      <c r="G162" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H162" s="1">
+        <v>200</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J162" s="1">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="3:10">
+      <c r="C163" s="1">
+        <v>1158</v>
+      </c>
+      <c r="D163" s="1">
+        <v>7</v>
+      </c>
+      <c r="E163" s="1">
+        <v>27</v>
+      </c>
+      <c r="F163" s="1">
+        <v>20</v>
+      </c>
+      <c r="G163" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H163" s="1">
+        <v>200</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J163" s="1">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="3:10">
+      <c r="C164" s="1">
+        <v>1159</v>
+      </c>
+      <c r="D164" s="1">
+        <v>7</v>
+      </c>
+      <c r="E164" s="1">
+        <v>29</v>
+      </c>
+      <c r="F164" s="1">
+        <v>20</v>
+      </c>
+      <c r="G164" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H164" s="1">
+        <v>200</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J164" s="1">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="3:10">
+      <c r="C165" s="1">
+        <v>1160</v>
+      </c>
+      <c r="D165" s="1">
+        <v>7</v>
+      </c>
+      <c r="E165" s="1">
+        <v>30</v>
+      </c>
+      <c r="F165" s="1">
+        <v>20</v>
+      </c>
+      <c r="G165" s="1">
+        <v>4019</v>
+      </c>
+      <c r="H165" s="1">
+        <v>200</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J165" s="1">
+        <v>3400</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">
@@ -9226,7 +10058,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L69"/>
+  <dimension ref="C3:L109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -10987,6 +11819,1046 @@
       </c>
       <c r="J69" s="1">
         <v>4200</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="1">
+        <v>2065</v>
+      </c>
+      <c r="D70" s="1">
+        <v>8</v>
+      </c>
+      <c r="E70" s="1">
+        <v>31</v>
+      </c>
+      <c r="F70" s="1">
+        <v>9</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H70" s="1">
+        <v>200</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J70" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="1">
+        <v>2066</v>
+      </c>
+      <c r="D71" s="1">
+        <v>8</v>
+      </c>
+      <c r="E71" s="1">
+        <v>32</v>
+      </c>
+      <c r="F71" s="1">
+        <v>9</v>
+      </c>
+      <c r="G71" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H71" s="1">
+        <v>200</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J71" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="1">
+        <v>2067</v>
+      </c>
+      <c r="D72" s="1">
+        <v>8</v>
+      </c>
+      <c r="E72" s="1">
+        <v>33</v>
+      </c>
+      <c r="F72" s="1">
+        <v>9</v>
+      </c>
+      <c r="G72" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H72" s="1">
+        <v>200</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J72" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="1">
+        <v>2068</v>
+      </c>
+      <c r="D73" s="1">
+        <v>8</v>
+      </c>
+      <c r="E73" s="1">
+        <v>34</v>
+      </c>
+      <c r="F73" s="1">
+        <v>9</v>
+      </c>
+      <c r="G73" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H73" s="1">
+        <v>200</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J73" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="1">
+        <v>2069</v>
+      </c>
+      <c r="D74" s="1">
+        <v>8</v>
+      </c>
+      <c r="E74" s="1">
+        <v>35</v>
+      </c>
+      <c r="F74" s="1">
+        <v>9</v>
+      </c>
+      <c r="G74" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H74" s="1">
+        <v>200</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J74" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="1">
+        <v>2070</v>
+      </c>
+      <c r="D75" s="1">
+        <v>8</v>
+      </c>
+      <c r="E75" s="1">
+        <v>37</v>
+      </c>
+      <c r="F75" s="1">
+        <v>9</v>
+      </c>
+      <c r="G75" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H75" s="1">
+        <v>200</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J75" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="1">
+        <v>2071</v>
+      </c>
+      <c r="D76" s="1">
+        <v>8</v>
+      </c>
+      <c r="E76" s="1">
+        <v>39</v>
+      </c>
+      <c r="F76" s="1">
+        <v>9</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H76" s="1">
+        <v>200</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J76" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="1">
+        <v>2072</v>
+      </c>
+      <c r="D77" s="1">
+        <v>8</v>
+      </c>
+      <c r="E77" s="1">
+        <v>40</v>
+      </c>
+      <c r="F77" s="1">
+        <v>9</v>
+      </c>
+      <c r="G77" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H77" s="1">
+        <v>200</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J77" s="1">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="1">
+        <v>2073</v>
+      </c>
+      <c r="D78" s="1">
+        <v>8</v>
+      </c>
+      <c r="E78" s="1">
+        <v>31</v>
+      </c>
+      <c r="F78" s="1">
+        <v>10</v>
+      </c>
+      <c r="G78" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H78" s="1">
+        <v>200</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J78" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="1">
+        <v>2074</v>
+      </c>
+      <c r="D79" s="1">
+        <v>8</v>
+      </c>
+      <c r="E79" s="1">
+        <v>32</v>
+      </c>
+      <c r="F79" s="1">
+        <v>10</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H79" s="1">
+        <v>200</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J79" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="1">
+        <v>2075</v>
+      </c>
+      <c r="D80" s="1">
+        <v>8</v>
+      </c>
+      <c r="E80" s="1">
+        <v>33</v>
+      </c>
+      <c r="F80" s="1">
+        <v>10</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H80" s="1">
+        <v>200</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="1">
+        <v>2076</v>
+      </c>
+      <c r="D81" s="1">
+        <v>8</v>
+      </c>
+      <c r="E81" s="1">
+        <v>34</v>
+      </c>
+      <c r="F81" s="1">
+        <v>10</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H81" s="1">
+        <v>200</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J81" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="1">
+        <v>2077</v>
+      </c>
+      <c r="D82" s="1">
+        <v>8</v>
+      </c>
+      <c r="E82" s="1">
+        <v>35</v>
+      </c>
+      <c r="F82" s="1">
+        <v>10</v>
+      </c>
+      <c r="G82" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H82" s="1">
+        <v>200</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J82" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="1">
+        <v>2078</v>
+      </c>
+      <c r="D83" s="1">
+        <v>8</v>
+      </c>
+      <c r="E83" s="1">
+        <v>37</v>
+      </c>
+      <c r="F83" s="1">
+        <v>10</v>
+      </c>
+      <c r="G83" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H83" s="1">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="1">
+        <v>2079</v>
+      </c>
+      <c r="D84" s="1">
+        <v>8</v>
+      </c>
+      <c r="E84" s="1">
+        <v>39</v>
+      </c>
+      <c r="F84" s="1">
+        <v>10</v>
+      </c>
+      <c r="G84" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H84" s="1">
+        <v>200</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="1">
+        <v>2080</v>
+      </c>
+      <c r="D85" s="1">
+        <v>8</v>
+      </c>
+      <c r="E85" s="1">
+        <v>40</v>
+      </c>
+      <c r="F85" s="1">
+        <v>10</v>
+      </c>
+      <c r="G85" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H85" s="1">
+        <v>200</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J85" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
+      <c r="C86" s="1">
+        <v>2081</v>
+      </c>
+      <c r="D86" s="1">
+        <v>8</v>
+      </c>
+      <c r="E86" s="1">
+        <v>31</v>
+      </c>
+      <c r="F86" s="1">
+        <v>11</v>
+      </c>
+      <c r="G86" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H86" s="1">
+        <v>200</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J86" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:10">
+      <c r="C87" s="1">
+        <v>2082</v>
+      </c>
+      <c r="D87" s="1">
+        <v>8</v>
+      </c>
+      <c r="E87" s="1">
+        <v>32</v>
+      </c>
+      <c r="F87" s="1">
+        <v>11</v>
+      </c>
+      <c r="G87" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H87" s="1">
+        <v>200</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J87" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:10">
+      <c r="C88" s="1">
+        <v>2083</v>
+      </c>
+      <c r="D88" s="1">
+        <v>8</v>
+      </c>
+      <c r="E88" s="1">
+        <v>33</v>
+      </c>
+      <c r="F88" s="1">
+        <v>11</v>
+      </c>
+      <c r="G88" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H88" s="1">
+        <v>200</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J88" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
+      <c r="C89" s="1">
+        <v>2084</v>
+      </c>
+      <c r="D89" s="1">
+        <v>8</v>
+      </c>
+      <c r="E89" s="1">
+        <v>34</v>
+      </c>
+      <c r="F89" s="1">
+        <v>11</v>
+      </c>
+      <c r="G89" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H89" s="1">
+        <v>200</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J89" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
+      <c r="C90" s="1">
+        <v>2085</v>
+      </c>
+      <c r="D90" s="1">
+        <v>8</v>
+      </c>
+      <c r="E90" s="1">
+        <v>35</v>
+      </c>
+      <c r="F90" s="1">
+        <v>11</v>
+      </c>
+      <c r="G90" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H90" s="1">
+        <v>200</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J90" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:10">
+      <c r="C91" s="1">
+        <v>2086</v>
+      </c>
+      <c r="D91" s="1">
+        <v>8</v>
+      </c>
+      <c r="E91" s="1">
+        <v>37</v>
+      </c>
+      <c r="F91" s="1">
+        <v>11</v>
+      </c>
+      <c r="G91" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H91" s="1">
+        <v>200</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J91" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:10">
+      <c r="C92" s="1">
+        <v>2087</v>
+      </c>
+      <c r="D92" s="1">
+        <v>8</v>
+      </c>
+      <c r="E92" s="1">
+        <v>39</v>
+      </c>
+      <c r="F92" s="1">
+        <v>11</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H92" s="1">
+        <v>200</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J92" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
+      <c r="C93" s="1">
+        <v>2088</v>
+      </c>
+      <c r="D93" s="1">
+        <v>8</v>
+      </c>
+      <c r="E93" s="1">
+        <v>40</v>
+      </c>
+      <c r="F93" s="1">
+        <v>11</v>
+      </c>
+      <c r="G93" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H93" s="1">
+        <v>200</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J93" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:10">
+      <c r="C94" s="1">
+        <v>2089</v>
+      </c>
+      <c r="D94" s="1">
+        <v>8</v>
+      </c>
+      <c r="E94" s="1">
+        <v>31</v>
+      </c>
+      <c r="F94" s="1">
+        <v>12</v>
+      </c>
+      <c r="G94" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H94" s="1">
+        <v>200</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J94" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:10">
+      <c r="C95" s="1">
+        <v>2090</v>
+      </c>
+      <c r="D95" s="1">
+        <v>8</v>
+      </c>
+      <c r="E95" s="1">
+        <v>32</v>
+      </c>
+      <c r="F95" s="1">
+        <v>12</v>
+      </c>
+      <c r="G95" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H95" s="1">
+        <v>200</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J95" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:10">
+      <c r="C96" s="1">
+        <v>2091</v>
+      </c>
+      <c r="D96" s="1">
+        <v>8</v>
+      </c>
+      <c r="E96" s="1">
+        <v>33</v>
+      </c>
+      <c r="F96" s="1">
+        <v>12</v>
+      </c>
+      <c r="G96" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H96" s="1">
+        <v>200</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J96" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:10">
+      <c r="C97" s="1">
+        <v>2092</v>
+      </c>
+      <c r="D97" s="1">
+        <v>8</v>
+      </c>
+      <c r="E97" s="1">
+        <v>34</v>
+      </c>
+      <c r="F97" s="1">
+        <v>12</v>
+      </c>
+      <c r="G97" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H97" s="1">
+        <v>200</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J97" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:10">
+      <c r="C98" s="1">
+        <v>2093</v>
+      </c>
+      <c r="D98" s="1">
+        <v>8</v>
+      </c>
+      <c r="E98" s="1">
+        <v>35</v>
+      </c>
+      <c r="F98" s="1">
+        <v>12</v>
+      </c>
+      <c r="G98" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H98" s="1">
+        <v>200</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J98" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:10">
+      <c r="C99" s="1">
+        <v>2094</v>
+      </c>
+      <c r="D99" s="1">
+        <v>8</v>
+      </c>
+      <c r="E99" s="1">
+        <v>37</v>
+      </c>
+      <c r="F99" s="1">
+        <v>12</v>
+      </c>
+      <c r="G99" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H99" s="1">
+        <v>200</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J99" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:10">
+      <c r="C100" s="1">
+        <v>2095</v>
+      </c>
+      <c r="D100" s="1">
+        <v>8</v>
+      </c>
+      <c r="E100" s="1">
+        <v>39</v>
+      </c>
+      <c r="F100" s="1">
+        <v>12</v>
+      </c>
+      <c r="G100" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H100" s="1">
+        <v>200</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J100" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:10">
+      <c r="C101" s="1">
+        <v>2096</v>
+      </c>
+      <c r="D101" s="1">
+        <v>8</v>
+      </c>
+      <c r="E101" s="1">
+        <v>40</v>
+      </c>
+      <c r="F101" s="1">
+        <v>12</v>
+      </c>
+      <c r="G101" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H101" s="1">
+        <v>200</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J101" s="1">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:10">
+      <c r="C102" s="1">
+        <v>2097</v>
+      </c>
+      <c r="D102" s="1">
+        <v>8</v>
+      </c>
+      <c r="E102" s="1">
+        <v>31</v>
+      </c>
+      <c r="F102" s="1">
+        <v>13</v>
+      </c>
+      <c r="G102" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H102" s="1">
+        <v>200</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J102" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:10">
+      <c r="C103" s="1">
+        <v>2098</v>
+      </c>
+      <c r="D103" s="1">
+        <v>8</v>
+      </c>
+      <c r="E103" s="1">
+        <v>32</v>
+      </c>
+      <c r="F103" s="1">
+        <v>13</v>
+      </c>
+      <c r="G103" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H103" s="1">
+        <v>200</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J103" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:10">
+      <c r="C104" s="1">
+        <v>2099</v>
+      </c>
+      <c r="D104" s="1">
+        <v>8</v>
+      </c>
+      <c r="E104" s="1">
+        <v>33</v>
+      </c>
+      <c r="F104" s="1">
+        <v>13</v>
+      </c>
+      <c r="G104" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H104" s="1">
+        <v>200</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J104" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:10">
+      <c r="C105" s="1">
+        <v>2100</v>
+      </c>
+      <c r="D105" s="1">
+        <v>8</v>
+      </c>
+      <c r="E105" s="1">
+        <v>34</v>
+      </c>
+      <c r="F105" s="1">
+        <v>13</v>
+      </c>
+      <c r="G105" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H105" s="1">
+        <v>200</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J105" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:10">
+      <c r="C106" s="1">
+        <v>2101</v>
+      </c>
+      <c r="D106" s="1">
+        <v>8</v>
+      </c>
+      <c r="E106" s="1">
+        <v>35</v>
+      </c>
+      <c r="F106" s="1">
+        <v>13</v>
+      </c>
+      <c r="G106" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H106" s="1">
+        <v>200</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J106" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:10">
+      <c r="C107" s="1">
+        <v>2102</v>
+      </c>
+      <c r="D107" s="1">
+        <v>8</v>
+      </c>
+      <c r="E107" s="1">
+        <v>37</v>
+      </c>
+      <c r="F107" s="1">
+        <v>13</v>
+      </c>
+      <c r="G107" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H107" s="1">
+        <v>200</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J107" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:10">
+      <c r="C108" s="1">
+        <v>2103</v>
+      </c>
+      <c r="D108" s="1">
+        <v>8</v>
+      </c>
+      <c r="E108" s="1">
+        <v>39</v>
+      </c>
+      <c r="F108" s="1">
+        <v>13</v>
+      </c>
+      <c r="G108" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H108" s="1">
+        <v>200</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J108" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:10">
+      <c r="C109" s="1">
+        <v>2104</v>
+      </c>
+      <c r="D109" s="1">
+        <v>8</v>
+      </c>
+      <c r="E109" s="1">
+        <v>40</v>
+      </c>
+      <c r="F109" s="1">
+        <v>13</v>
+      </c>
+      <c r="G109" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H109" s="1">
+        <v>200</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J109" s="1">
+        <v>7200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
     <sheet name="金色" sheetId="2" r:id="rId2"/>
     <sheet name="暗金" sheetId="3" r:id="rId3"/>
     <sheet name="混沌" sheetId="4" r:id="rId4"/>
+    <sheet name="虚无" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="144">
   <si>
     <t>_Id</t>
   </si>
@@ -441,6 +442,27 @@
   </si>
   <si>
     <t>50000118</t>
+  </si>
+  <si>
+    <t>50000119</t>
+  </si>
+  <si>
+    <t>50000120</t>
+  </si>
+  <si>
+    <t>50000121</t>
+  </si>
+  <si>
+    <t>50000122</t>
+  </si>
+  <si>
+    <t>50000123</t>
+  </si>
+  <si>
+    <t>50000124</t>
+  </si>
+  <si>
+    <t>50000125</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1520,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="3:10">
+    <row r="6" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1524,7 +1546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:10">
+    <row r="7" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1550,7 +1572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:10">
+    <row r="8" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1576,7 +1598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:10">
+    <row r="9" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1602,7 +1624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:10">
+    <row r="10" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1628,7 +1650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:10">
+    <row r="11" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1654,7 +1676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:10">
+    <row r="12" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1680,7 +1702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:10">
+    <row r="13" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1706,7 +1728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:10">
+    <row r="14" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1732,7 +1754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:10">
+    <row r="15" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1758,7 +1780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:10">
+    <row r="16" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -5112,7 +5134,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="3:10">
+    <row r="145" customHeight="1" spans="1:10">
       <c r="C145" s="1">
         <v>140</v>
       </c>
@@ -5138,7 +5160,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="3:10">
+    <row r="146" customHeight="1" spans="1:10">
       <c r="C146" s="1">
         <v>141</v>
       </c>
@@ -5164,7 +5186,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="3:10">
+    <row r="147" customHeight="1" spans="1:10">
       <c r="C147" s="1">
         <v>142</v>
       </c>
@@ -5190,7 +5212,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="3:10">
+    <row r="148" customHeight="1" spans="1:10">
       <c r="C148" s="1">
         <v>143</v>
       </c>
@@ -5216,7 +5238,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="3:10">
+    <row r="149" customHeight="1" spans="1:10">
       <c r="C149" s="1">
         <v>144</v>
       </c>
@@ -5242,7 +5264,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="150" customHeight="1" spans="3:10">
+    <row r="150" customHeight="1" spans="1:10">
       <c r="C150" s="1">
         <v>145</v>
       </c>
@@ -5268,7 +5290,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="3:10">
+    <row r="151" customHeight="1" spans="1:10">
       <c r="C151" s="1">
         <v>146</v>
       </c>
@@ -5294,7 +5316,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="3:10">
+    <row r="152" customHeight="1" spans="1:10">
       <c r="C152" s="1">
         <v>147</v>
       </c>
@@ -5320,7 +5342,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="3:10">
+    <row r="153" customHeight="1" spans="1:10">
       <c r="C153" s="1">
         <v>148</v>
       </c>
@@ -5346,7 +5368,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="3:10">
+    <row r="154" customHeight="1" spans="1:10">
       <c r="C154" s="1">
         <v>149</v>
       </c>
@@ -5372,7 +5394,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="3:10">
+    <row r="155" customHeight="1" spans="1:10">
       <c r="C155" s="1">
         <v>150</v>
       </c>
@@ -5398,7 +5420,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="156" customHeight="1" spans="3:10">
+    <row r="156" customHeight="1" spans="1:10">
       <c r="C156" s="1">
         <v>151</v>
       </c>
@@ -5424,7 +5446,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="3:10">
+    <row r="157" customHeight="1" spans="1:10">
       <c r="C157" s="1">
         <v>152</v>
       </c>
@@ -5819,7 +5841,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -5846,7 +5868,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -5873,7 +5895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -5900,7 +5922,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -5927,7 +5949,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -5954,7 +5976,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -5981,7 +6003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -6008,7 +6030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -6035,7 +6057,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -6062,7 +6084,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -6089,7 +6111,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -10058,7 +10080,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L109"/>
+  <dimension ref="C3:L157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -10157,7 +10179,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>2001</v>
       </c>
@@ -10183,7 +10205,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>2002</v>
       </c>
@@ -10209,7 +10231,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>2003</v>
       </c>
@@ -10235,7 +10257,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>2004</v>
       </c>
@@ -10261,7 +10283,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>2005</v>
       </c>
@@ -10287,7 +10309,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>2006</v>
       </c>
@@ -10313,7 +10335,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>2007</v>
       </c>
@@ -10339,7 +10361,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>2008</v>
       </c>
@@ -10365,7 +10387,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>2009</v>
       </c>
@@ -10391,7 +10413,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>2010</v>
       </c>
@@ -10417,7 +10439,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>2011</v>
       </c>
@@ -12859,6 +12881,1254 @@
       </c>
       <c r="J109" s="1">
         <v>7200</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:10">
+      <c r="C110" s="1">
+        <v>2105</v>
+      </c>
+      <c r="D110" s="1">
+        <v>8</v>
+      </c>
+      <c r="E110" s="1">
+        <v>31</v>
+      </c>
+      <c r="F110" s="1">
+        <v>14</v>
+      </c>
+      <c r="G110" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H110" s="1">
+        <v>200</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J110" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:10">
+      <c r="C111" s="1">
+        <v>2106</v>
+      </c>
+      <c r="D111" s="1">
+        <v>8</v>
+      </c>
+      <c r="E111" s="1">
+        <v>32</v>
+      </c>
+      <c r="F111" s="1">
+        <v>14</v>
+      </c>
+      <c r="G111" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H111" s="1">
+        <v>200</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J111" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:10">
+      <c r="C112" s="1">
+        <v>2107</v>
+      </c>
+      <c r="D112" s="1">
+        <v>8</v>
+      </c>
+      <c r="E112" s="1">
+        <v>33</v>
+      </c>
+      <c r="F112" s="1">
+        <v>14</v>
+      </c>
+      <c r="G112" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H112" s="1">
+        <v>200</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J112" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:10">
+      <c r="C113" s="1">
+        <v>2108</v>
+      </c>
+      <c r="D113" s="1">
+        <v>8</v>
+      </c>
+      <c r="E113" s="1">
+        <v>34</v>
+      </c>
+      <c r="F113" s="1">
+        <v>14</v>
+      </c>
+      <c r="G113" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H113" s="1">
+        <v>200</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J113" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:10">
+      <c r="C114" s="1">
+        <v>2109</v>
+      </c>
+      <c r="D114" s="1">
+        <v>8</v>
+      </c>
+      <c r="E114" s="1">
+        <v>35</v>
+      </c>
+      <c r="F114" s="1">
+        <v>14</v>
+      </c>
+      <c r="G114" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H114" s="1">
+        <v>200</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J114" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:10">
+      <c r="C115" s="1">
+        <v>2110</v>
+      </c>
+      <c r="D115" s="1">
+        <v>8</v>
+      </c>
+      <c r="E115" s="1">
+        <v>37</v>
+      </c>
+      <c r="F115" s="1">
+        <v>14</v>
+      </c>
+      <c r="G115" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H115" s="1">
+        <v>200</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J115" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:10">
+      <c r="C116" s="1">
+        <v>2111</v>
+      </c>
+      <c r="D116" s="1">
+        <v>8</v>
+      </c>
+      <c r="E116" s="1">
+        <v>39</v>
+      </c>
+      <c r="F116" s="1">
+        <v>14</v>
+      </c>
+      <c r="G116" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H116" s="1">
+        <v>200</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J116" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:10">
+      <c r="C117" s="1">
+        <v>2112</v>
+      </c>
+      <c r="D117" s="1">
+        <v>8</v>
+      </c>
+      <c r="E117" s="1">
+        <v>40</v>
+      </c>
+      <c r="F117" s="1">
+        <v>14</v>
+      </c>
+      <c r="G117" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H117" s="1">
+        <v>200</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J117" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:10">
+      <c r="C118" s="1">
+        <v>2113</v>
+      </c>
+      <c r="D118" s="1">
+        <v>8</v>
+      </c>
+      <c r="E118" s="1">
+        <v>31</v>
+      </c>
+      <c r="F118" s="1">
+        <v>15</v>
+      </c>
+      <c r="G118" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H118" s="1">
+        <v>200</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J118" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:10">
+      <c r="C119" s="1">
+        <v>2114</v>
+      </c>
+      <c r="D119" s="1">
+        <v>8</v>
+      </c>
+      <c r="E119" s="1">
+        <v>32</v>
+      </c>
+      <c r="F119" s="1">
+        <v>15</v>
+      </c>
+      <c r="G119" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H119" s="1">
+        <v>200</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J119" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:10">
+      <c r="C120" s="1">
+        <v>2115</v>
+      </c>
+      <c r="D120" s="1">
+        <v>8</v>
+      </c>
+      <c r="E120" s="1">
+        <v>33</v>
+      </c>
+      <c r="F120" s="1">
+        <v>15</v>
+      </c>
+      <c r="G120" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H120" s="1">
+        <v>200</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J120" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:10">
+      <c r="C121" s="1">
+        <v>2116</v>
+      </c>
+      <c r="D121" s="1">
+        <v>8</v>
+      </c>
+      <c r="E121" s="1">
+        <v>34</v>
+      </c>
+      <c r="F121" s="1">
+        <v>15</v>
+      </c>
+      <c r="G121" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H121" s="1">
+        <v>200</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J121" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:10">
+      <c r="C122" s="1">
+        <v>2117</v>
+      </c>
+      <c r="D122" s="1">
+        <v>8</v>
+      </c>
+      <c r="E122" s="1">
+        <v>35</v>
+      </c>
+      <c r="F122" s="1">
+        <v>15</v>
+      </c>
+      <c r="G122" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H122" s="1">
+        <v>200</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J122" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:10">
+      <c r="C123" s="1">
+        <v>2118</v>
+      </c>
+      <c r="D123" s="1">
+        <v>8</v>
+      </c>
+      <c r="E123" s="1">
+        <v>37</v>
+      </c>
+      <c r="F123" s="1">
+        <v>15</v>
+      </c>
+      <c r="G123" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H123" s="1">
+        <v>200</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J123" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:10">
+      <c r="C124" s="1">
+        <v>2119</v>
+      </c>
+      <c r="D124" s="1">
+        <v>8</v>
+      </c>
+      <c r="E124" s="1">
+        <v>39</v>
+      </c>
+      <c r="F124" s="1">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H124" s="1">
+        <v>200</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J124" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:10">
+      <c r="C125" s="1">
+        <v>2120</v>
+      </c>
+      <c r="D125" s="1">
+        <v>8</v>
+      </c>
+      <c r="E125" s="1">
+        <v>40</v>
+      </c>
+      <c r="F125" s="1">
+        <v>15</v>
+      </c>
+      <c r="G125" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H125" s="1">
+        <v>200</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J125" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:10">
+      <c r="C126" s="1">
+        <v>2121</v>
+      </c>
+      <c r="D126" s="1">
+        <v>8</v>
+      </c>
+      <c r="E126" s="1">
+        <v>31</v>
+      </c>
+      <c r="F126" s="1">
+        <v>16</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H126" s="1">
+        <v>200</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J126" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:10">
+      <c r="C127" s="1">
+        <v>2122</v>
+      </c>
+      <c r="D127" s="1">
+        <v>8</v>
+      </c>
+      <c r="E127" s="1">
+        <v>32</v>
+      </c>
+      <c r="F127" s="1">
+        <v>16</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H127" s="1">
+        <v>200</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J127" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:10">
+      <c r="C128" s="1">
+        <v>2123</v>
+      </c>
+      <c r="D128" s="1">
+        <v>8</v>
+      </c>
+      <c r="E128" s="1">
+        <v>33</v>
+      </c>
+      <c r="F128" s="1">
+        <v>16</v>
+      </c>
+      <c r="G128" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H128" s="1">
+        <v>200</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J128" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:10">
+      <c r="C129" s="1">
+        <v>2124</v>
+      </c>
+      <c r="D129" s="1">
+        <v>8</v>
+      </c>
+      <c r="E129" s="1">
+        <v>34</v>
+      </c>
+      <c r="F129" s="1">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H129" s="1">
+        <v>200</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J129" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:10">
+      <c r="C130" s="1">
+        <v>2125</v>
+      </c>
+      <c r="D130" s="1">
+        <v>8</v>
+      </c>
+      <c r="E130" s="1">
+        <v>35</v>
+      </c>
+      <c r="F130" s="1">
+        <v>16</v>
+      </c>
+      <c r="G130" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H130" s="1">
+        <v>200</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J130" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:10">
+      <c r="C131" s="1">
+        <v>2126</v>
+      </c>
+      <c r="D131" s="1">
+        <v>8</v>
+      </c>
+      <c r="E131" s="1">
+        <v>37</v>
+      </c>
+      <c r="F131" s="1">
+        <v>16</v>
+      </c>
+      <c r="G131" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H131" s="1">
+        <v>200</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J131" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:10">
+      <c r="C132" s="1">
+        <v>2127</v>
+      </c>
+      <c r="D132" s="1">
+        <v>8</v>
+      </c>
+      <c r="E132" s="1">
+        <v>39</v>
+      </c>
+      <c r="F132" s="1">
+        <v>16</v>
+      </c>
+      <c r="G132" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H132" s="1">
+        <v>200</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J132" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:10">
+      <c r="C133" s="1">
+        <v>2128</v>
+      </c>
+      <c r="D133" s="1">
+        <v>8</v>
+      </c>
+      <c r="E133" s="1">
+        <v>40</v>
+      </c>
+      <c r="F133" s="1">
+        <v>16</v>
+      </c>
+      <c r="G133" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H133" s="1">
+        <v>200</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J133" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:10">
+      <c r="C134" s="1">
+        <v>2129</v>
+      </c>
+      <c r="D134" s="1">
+        <v>8</v>
+      </c>
+      <c r="E134" s="1">
+        <v>31</v>
+      </c>
+      <c r="F134" s="1">
+        <v>17</v>
+      </c>
+      <c r="G134" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H134" s="1">
+        <v>200</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J134" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:10">
+      <c r="C135" s="1">
+        <v>2130</v>
+      </c>
+      <c r="D135" s="1">
+        <v>8</v>
+      </c>
+      <c r="E135" s="1">
+        <v>32</v>
+      </c>
+      <c r="F135" s="1">
+        <v>17</v>
+      </c>
+      <c r="G135" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H135" s="1">
+        <v>200</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J135" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:10">
+      <c r="C136" s="1">
+        <v>2131</v>
+      </c>
+      <c r="D136" s="1">
+        <v>8</v>
+      </c>
+      <c r="E136" s="1">
+        <v>33</v>
+      </c>
+      <c r="F136" s="1">
+        <v>17</v>
+      </c>
+      <c r="G136" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H136" s="1">
+        <v>200</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J136" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:10">
+      <c r="C137" s="1">
+        <v>2132</v>
+      </c>
+      <c r="D137" s="1">
+        <v>8</v>
+      </c>
+      <c r="E137" s="1">
+        <v>34</v>
+      </c>
+      <c r="F137" s="1">
+        <v>17</v>
+      </c>
+      <c r="G137" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H137" s="1">
+        <v>200</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J137" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:10">
+      <c r="C138" s="1">
+        <v>2133</v>
+      </c>
+      <c r="D138" s="1">
+        <v>8</v>
+      </c>
+      <c r="E138" s="1">
+        <v>35</v>
+      </c>
+      <c r="F138" s="1">
+        <v>17</v>
+      </c>
+      <c r="G138" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H138" s="1">
+        <v>200</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J138" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:10">
+      <c r="C139" s="1">
+        <v>2134</v>
+      </c>
+      <c r="D139" s="1">
+        <v>8</v>
+      </c>
+      <c r="E139" s="1">
+        <v>37</v>
+      </c>
+      <c r="F139" s="1">
+        <v>17</v>
+      </c>
+      <c r="G139" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H139" s="1">
+        <v>200</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J139" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:10">
+      <c r="C140" s="1">
+        <v>2135</v>
+      </c>
+      <c r="D140" s="1">
+        <v>8</v>
+      </c>
+      <c r="E140" s="1">
+        <v>39</v>
+      </c>
+      <c r="F140" s="1">
+        <v>17</v>
+      </c>
+      <c r="G140" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H140" s="1">
+        <v>200</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J140" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:10">
+      <c r="C141" s="1">
+        <v>2136</v>
+      </c>
+      <c r="D141" s="1">
+        <v>8</v>
+      </c>
+      <c r="E141" s="1">
+        <v>40</v>
+      </c>
+      <c r="F141" s="1">
+        <v>17</v>
+      </c>
+      <c r="G141" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H141" s="1">
+        <v>200</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J141" s="1">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:10">
+      <c r="C142" s="1">
+        <v>2137</v>
+      </c>
+      <c r="D142" s="1">
+        <v>8</v>
+      </c>
+      <c r="E142" s="1">
+        <v>31</v>
+      </c>
+      <c r="F142" s="1">
+        <v>18</v>
+      </c>
+      <c r="G142" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H142" s="1">
+        <v>200</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J142" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:10">
+      <c r="C143" s="1">
+        <v>2138</v>
+      </c>
+      <c r="D143" s="1">
+        <v>8</v>
+      </c>
+      <c r="E143" s="1">
+        <v>32</v>
+      </c>
+      <c r="F143" s="1">
+        <v>18</v>
+      </c>
+      <c r="G143" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H143" s="1">
+        <v>200</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J143" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:10">
+      <c r="C144" s="1">
+        <v>2139</v>
+      </c>
+      <c r="D144" s="1">
+        <v>8</v>
+      </c>
+      <c r="E144" s="1">
+        <v>33</v>
+      </c>
+      <c r="F144" s="1">
+        <v>18</v>
+      </c>
+      <c r="G144" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H144" s="1">
+        <v>200</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J144" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:10">
+      <c r="C145" s="1">
+        <v>2140</v>
+      </c>
+      <c r="D145" s="1">
+        <v>8</v>
+      </c>
+      <c r="E145" s="1">
+        <v>34</v>
+      </c>
+      <c r="F145" s="1">
+        <v>18</v>
+      </c>
+      <c r="G145" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H145" s="1">
+        <v>200</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J145" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:10">
+      <c r="C146" s="1">
+        <v>2141</v>
+      </c>
+      <c r="D146" s="1">
+        <v>8</v>
+      </c>
+      <c r="E146" s="1">
+        <v>35</v>
+      </c>
+      <c r="F146" s="1">
+        <v>18</v>
+      </c>
+      <c r="G146" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H146" s="1">
+        <v>200</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J146" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:10">
+      <c r="C147" s="1">
+        <v>2142</v>
+      </c>
+      <c r="D147" s="1">
+        <v>8</v>
+      </c>
+      <c r="E147" s="1">
+        <v>37</v>
+      </c>
+      <c r="F147" s="1">
+        <v>18</v>
+      </c>
+      <c r="G147" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H147" s="1">
+        <v>200</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J147" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:10">
+      <c r="C148" s="1">
+        <v>2143</v>
+      </c>
+      <c r="D148" s="1">
+        <v>8</v>
+      </c>
+      <c r="E148" s="1">
+        <v>39</v>
+      </c>
+      <c r="F148" s="1">
+        <v>18</v>
+      </c>
+      <c r="G148" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H148" s="1">
+        <v>200</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J148" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:10">
+      <c r="C149" s="1">
+        <v>2144</v>
+      </c>
+      <c r="D149" s="1">
+        <v>8</v>
+      </c>
+      <c r="E149" s="1">
+        <v>40</v>
+      </c>
+      <c r="F149" s="1">
+        <v>18</v>
+      </c>
+      <c r="G149" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H149" s="1">
+        <v>200</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J149" s="1">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:10">
+      <c r="C150" s="1">
+        <v>2145</v>
+      </c>
+      <c r="D150" s="1">
+        <v>8</v>
+      </c>
+      <c r="E150" s="1">
+        <v>31</v>
+      </c>
+      <c r="F150" s="1">
+        <v>19</v>
+      </c>
+      <c r="G150" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H150" s="1">
+        <v>200</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J150" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:10">
+      <c r="C151" s="1">
+        <v>2146</v>
+      </c>
+      <c r="D151" s="1">
+        <v>8</v>
+      </c>
+      <c r="E151" s="1">
+        <v>32</v>
+      </c>
+      <c r="F151" s="1">
+        <v>19</v>
+      </c>
+      <c r="G151" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H151" s="1">
+        <v>200</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J151" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:10">
+      <c r="C152" s="1">
+        <v>2147</v>
+      </c>
+      <c r="D152" s="1">
+        <v>8</v>
+      </c>
+      <c r="E152" s="1">
+        <v>33</v>
+      </c>
+      <c r="F152" s="1">
+        <v>19</v>
+      </c>
+      <c r="G152" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H152" s="1">
+        <v>200</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J152" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:10">
+      <c r="C153" s="1">
+        <v>2148</v>
+      </c>
+      <c r="D153" s="1">
+        <v>8</v>
+      </c>
+      <c r="E153" s="1">
+        <v>34</v>
+      </c>
+      <c r="F153" s="1">
+        <v>19</v>
+      </c>
+      <c r="G153" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H153" s="1">
+        <v>200</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J153" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:10">
+      <c r="C154" s="1">
+        <v>2149</v>
+      </c>
+      <c r="D154" s="1">
+        <v>8</v>
+      </c>
+      <c r="E154" s="1">
+        <v>35</v>
+      </c>
+      <c r="F154" s="1">
+        <v>19</v>
+      </c>
+      <c r="G154" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H154" s="1">
+        <v>200</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J154" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:10">
+      <c r="C155" s="1">
+        <v>2150</v>
+      </c>
+      <c r="D155" s="1">
+        <v>8</v>
+      </c>
+      <c r="E155" s="1">
+        <v>37</v>
+      </c>
+      <c r="F155" s="1">
+        <v>19</v>
+      </c>
+      <c r="G155" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H155" s="1">
+        <v>200</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J155" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:10">
+      <c r="C156" s="1">
+        <v>2151</v>
+      </c>
+      <c r="D156" s="1">
+        <v>8</v>
+      </c>
+      <c r="E156" s="1">
+        <v>39</v>
+      </c>
+      <c r="F156" s="1">
+        <v>19</v>
+      </c>
+      <c r="G156" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H156" s="1">
+        <v>200</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J156" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:10">
+      <c r="C157" s="1">
+        <v>2152</v>
+      </c>
+      <c r="D157" s="1">
+        <v>8</v>
+      </c>
+      <c r="E157" s="1">
+        <v>40</v>
+      </c>
+      <c r="F157" s="1">
+        <v>19</v>
+      </c>
+      <c r="G157" s="1">
+        <v>4026</v>
+      </c>
+      <c r="H157" s="1">
+        <v>200</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J157" s="1">
+        <v>10800</v>
       </c>
     </row>
   </sheetData>
@@ -12873,6 +14143,3959 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:L157"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="11.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C6" s="1">
+        <v>3001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
+        <v>41</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C7" s="1">
+        <v>3002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C8" s="1">
+        <v>3003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C9" s="1">
+        <v>3004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C10" s="1">
+        <v>3005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
+        <v>45</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C11" s="1">
+        <v>3006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1">
+        <v>47</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C12" s="1">
+        <v>3007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
+        <v>49</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C13" s="1">
+        <v>3008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C14" s="1">
+        <v>3009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1">
+        <v>41</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H14" s="1">
+        <v>40</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C15" s="1">
+        <v>3010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1">
+        <v>42</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H15" s="1">
+        <v>40</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J15" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C16" s="1">
+        <v>3011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1">
+        <v>43</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H16" s="1">
+        <v>40</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C17" s="1">
+        <v>3012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1">
+        <v>44</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H17" s="1">
+        <v>40</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J17" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C18" s="1">
+        <v>3013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1">
+        <v>45</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H18" s="1">
+        <v>40</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C19" s="1">
+        <v>3014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1">
+        <v>47</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H19" s="1">
+        <v>40</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J19" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C20" s="1">
+        <v>3015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1">
+        <v>49</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H20" s="1">
+        <v>40</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J20" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C21" s="1">
+        <v>3016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>9</v>
+      </c>
+      <c r="E21" s="1">
+        <v>50</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H21" s="1">
+        <v>40</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J21" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C22" s="1">
+        <v>3017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1">
+        <v>41</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H22" s="1">
+        <v>60</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J22" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C23" s="1">
+        <v>3018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1">
+        <v>42</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H23" s="1">
+        <v>60</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J23" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C24" s="1">
+        <v>3019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9</v>
+      </c>
+      <c r="E24" s="1">
+        <v>43</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H24" s="1">
+        <v>60</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C25" s="1">
+        <v>3020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1">
+        <v>44</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H25" s="1">
+        <v>60</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C26" s="1">
+        <v>3021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1">
+        <v>45</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H26" s="1">
+        <v>60</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C27" s="1">
+        <v>3022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1">
+        <v>47</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H27" s="1">
+        <v>60</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C28" s="1">
+        <v>3023</v>
+      </c>
+      <c r="D28" s="1">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1">
+        <v>49</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H28" s="1">
+        <v>60</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C29" s="1">
+        <v>3024</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1">
+        <v>50</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H29" s="1">
+        <v>60</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J29" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>3025</v>
+      </c>
+      <c r="D30" s="1">
+        <v>9</v>
+      </c>
+      <c r="E30" s="1">
+        <v>41</v>
+      </c>
+      <c r="F30" s="1">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H30" s="1">
+        <v>80</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J30" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>3026</v>
+      </c>
+      <c r="D31" s="1">
+        <v>9</v>
+      </c>
+      <c r="E31" s="1">
+        <v>42</v>
+      </c>
+      <c r="F31" s="1">
+        <v>4</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H31" s="1">
+        <v>80</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>3027</v>
+      </c>
+      <c r="D32" s="1">
+        <v>9</v>
+      </c>
+      <c r="E32" s="1">
+        <v>43</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H32" s="1">
+        <v>80</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>3028</v>
+      </c>
+      <c r="D33" s="1">
+        <v>9</v>
+      </c>
+      <c r="E33" s="1">
+        <v>44</v>
+      </c>
+      <c r="F33" s="1">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H33" s="1">
+        <v>80</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>3029</v>
+      </c>
+      <c r="D34" s="1">
+        <v>9</v>
+      </c>
+      <c r="E34" s="1">
+        <v>45</v>
+      </c>
+      <c r="F34" s="1">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H34" s="1">
+        <v>80</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>3030</v>
+      </c>
+      <c r="D35" s="1">
+        <v>9</v>
+      </c>
+      <c r="E35" s="1">
+        <v>47</v>
+      </c>
+      <c r="F35" s="1">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H35" s="1">
+        <v>80</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>3031</v>
+      </c>
+      <c r="D36" s="1">
+        <v>9</v>
+      </c>
+      <c r="E36" s="1">
+        <v>49</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H36" s="1">
+        <v>80</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>3032</v>
+      </c>
+      <c r="D37" s="1">
+        <v>9</v>
+      </c>
+      <c r="E37" s="1">
+        <v>50</v>
+      </c>
+      <c r="F37" s="1">
+        <v>4</v>
+      </c>
+      <c r="G37" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H37" s="1">
+        <v>80</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C38" s="1">
+        <v>3033</v>
+      </c>
+      <c r="D38" s="1">
+        <v>9</v>
+      </c>
+      <c r="E38" s="1">
+        <v>41</v>
+      </c>
+      <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H38" s="1">
+        <v>100</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J38" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C39" s="1">
+        <v>3034</v>
+      </c>
+      <c r="D39" s="1">
+        <v>9</v>
+      </c>
+      <c r="E39" s="1">
+        <v>42</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H39" s="1">
+        <v>100</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J39" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C40" s="1">
+        <v>3035</v>
+      </c>
+      <c r="D40" s="1">
+        <v>9</v>
+      </c>
+      <c r="E40" s="1">
+        <v>43</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H40" s="1">
+        <v>100</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J40" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>3036</v>
+      </c>
+      <c r="D41" s="1">
+        <v>9</v>
+      </c>
+      <c r="E41" s="1">
+        <v>44</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H41" s="1">
+        <v>100</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J41" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>3037</v>
+      </c>
+      <c r="D42" s="1">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1">
+        <v>45</v>
+      </c>
+      <c r="F42" s="1">
+        <v>5</v>
+      </c>
+      <c r="G42" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H42" s="1">
+        <v>100</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J42" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C43" s="1">
+        <v>3038</v>
+      </c>
+      <c r="D43" s="1">
+        <v>9</v>
+      </c>
+      <c r="E43" s="1">
+        <v>47</v>
+      </c>
+      <c r="F43" s="1">
+        <v>5</v>
+      </c>
+      <c r="G43" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H43" s="1">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J43" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C44" s="1">
+        <v>3039</v>
+      </c>
+      <c r="D44" s="1">
+        <v>9</v>
+      </c>
+      <c r="E44" s="1">
+        <v>49</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H44" s="1">
+        <v>100</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J44" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C45" s="1">
+        <v>3040</v>
+      </c>
+      <c r="D45" s="1">
+        <v>9</v>
+      </c>
+      <c r="E45" s="1">
+        <v>50</v>
+      </c>
+      <c r="F45" s="1">
+        <v>5</v>
+      </c>
+      <c r="G45" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H45" s="1">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J45" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C46" s="1">
+        <v>3041</v>
+      </c>
+      <c r="D46" s="1">
+        <v>9</v>
+      </c>
+      <c r="E46" s="1">
+        <v>41</v>
+      </c>
+      <c r="F46" s="1">
+        <v>6</v>
+      </c>
+      <c r="G46" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H46" s="1">
+        <v>140</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J46" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C47" s="1">
+        <v>3042</v>
+      </c>
+      <c r="D47" s="1">
+        <v>9</v>
+      </c>
+      <c r="E47" s="1">
+        <v>42</v>
+      </c>
+      <c r="F47" s="1">
+        <v>6</v>
+      </c>
+      <c r="G47" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H47" s="1">
+        <v>140</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J47" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C48" s="1">
+        <v>3043</v>
+      </c>
+      <c r="D48" s="1">
+        <v>9</v>
+      </c>
+      <c r="E48" s="1">
+        <v>43</v>
+      </c>
+      <c r="F48" s="1">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H48" s="1">
+        <v>140</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J48" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C49" s="1">
+        <v>3044</v>
+      </c>
+      <c r="D49" s="1">
+        <v>9</v>
+      </c>
+      <c r="E49" s="1">
+        <v>44</v>
+      </c>
+      <c r="F49" s="1">
+        <v>6</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H49" s="1">
+        <v>140</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J49" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C50" s="1">
+        <v>3045</v>
+      </c>
+      <c r="D50" s="1">
+        <v>9</v>
+      </c>
+      <c r="E50" s="1">
+        <v>45</v>
+      </c>
+      <c r="F50" s="1">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H50" s="1">
+        <v>140</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C51" s="1">
+        <v>3046</v>
+      </c>
+      <c r="D51" s="1">
+        <v>9</v>
+      </c>
+      <c r="E51" s="1">
+        <v>47</v>
+      </c>
+      <c r="F51" s="1">
+        <v>6</v>
+      </c>
+      <c r="G51" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H51" s="1">
+        <v>140</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J51" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C52" s="1">
+        <v>3047</v>
+      </c>
+      <c r="D52" s="1">
+        <v>9</v>
+      </c>
+      <c r="E52" s="1">
+        <v>49</v>
+      </c>
+      <c r="F52" s="1">
+        <v>6</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H52" s="1">
+        <v>140</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J52" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C53" s="1">
+        <v>3048</v>
+      </c>
+      <c r="D53" s="1">
+        <v>9</v>
+      </c>
+      <c r="E53" s="1">
+        <v>50</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H53" s="1">
+        <v>140</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J53" s="1">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:10">
+      <c r="C54" s="1">
+        <v>3049</v>
+      </c>
+      <c r="D54" s="1">
+        <v>9</v>
+      </c>
+      <c r="E54" s="1">
+        <v>41</v>
+      </c>
+      <c r="F54" s="1">
+        <v>7</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H54" s="1">
+        <v>160</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J54" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:10">
+      <c r="C55" s="1">
+        <v>3050</v>
+      </c>
+      <c r="D55" s="1">
+        <v>9</v>
+      </c>
+      <c r="E55" s="1">
+        <v>42</v>
+      </c>
+      <c r="F55" s="1">
+        <v>7</v>
+      </c>
+      <c r="G55" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H55" s="1">
+        <v>160</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J55" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:10">
+      <c r="C56" s="1">
+        <v>3051</v>
+      </c>
+      <c r="D56" s="1">
+        <v>9</v>
+      </c>
+      <c r="E56" s="1">
+        <v>43</v>
+      </c>
+      <c r="F56" s="1">
+        <v>7</v>
+      </c>
+      <c r="G56" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H56" s="1">
+        <v>160</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J56" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:10">
+      <c r="C57" s="1">
+        <v>3052</v>
+      </c>
+      <c r="D57" s="1">
+        <v>9</v>
+      </c>
+      <c r="E57" s="1">
+        <v>44</v>
+      </c>
+      <c r="F57" s="1">
+        <v>7</v>
+      </c>
+      <c r="G57" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H57" s="1">
+        <v>160</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J57" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:10">
+      <c r="C58" s="1">
+        <v>3053</v>
+      </c>
+      <c r="D58" s="1">
+        <v>9</v>
+      </c>
+      <c r="E58" s="1">
+        <v>45</v>
+      </c>
+      <c r="F58" s="1">
+        <v>7</v>
+      </c>
+      <c r="G58" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H58" s="1">
+        <v>160</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J58" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
+        <v>3054</v>
+      </c>
+      <c r="D59" s="1">
+        <v>9</v>
+      </c>
+      <c r="E59" s="1">
+        <v>47</v>
+      </c>
+      <c r="F59" s="1">
+        <v>7</v>
+      </c>
+      <c r="G59" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H59" s="1">
+        <v>160</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J59" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>3055</v>
+      </c>
+      <c r="D60" s="1">
+        <v>9</v>
+      </c>
+      <c r="E60" s="1">
+        <v>49</v>
+      </c>
+      <c r="F60" s="1">
+        <v>7</v>
+      </c>
+      <c r="G60" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H60" s="1">
+        <v>160</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J60" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:10">
+      <c r="C61" s="1">
+        <v>3056</v>
+      </c>
+      <c r="D61" s="1">
+        <v>9</v>
+      </c>
+      <c r="E61" s="1">
+        <v>50</v>
+      </c>
+      <c r="F61" s="1">
+        <v>7</v>
+      </c>
+      <c r="G61" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H61" s="1">
+        <v>160</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J61" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:10">
+      <c r="C62" s="1">
+        <v>3057</v>
+      </c>
+      <c r="D62" s="1">
+        <v>9</v>
+      </c>
+      <c r="E62" s="1">
+        <v>41</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8</v>
+      </c>
+      <c r="G62" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H62" s="1">
+        <v>180</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J62" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
+      <c r="C63" s="1">
+        <v>3058</v>
+      </c>
+      <c r="D63" s="1">
+        <v>9</v>
+      </c>
+      <c r="E63" s="1">
+        <v>42</v>
+      </c>
+      <c r="F63" s="1">
+        <v>8</v>
+      </c>
+      <c r="G63" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H63" s="1">
+        <v>180</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J63" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>3059</v>
+      </c>
+      <c r="D64" s="1">
+        <v>9</v>
+      </c>
+      <c r="E64" s="1">
+        <v>43</v>
+      </c>
+      <c r="F64" s="1">
+        <v>8</v>
+      </c>
+      <c r="G64" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H64" s="1">
+        <v>180</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J64" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>3060</v>
+      </c>
+      <c r="D65" s="1">
+        <v>9</v>
+      </c>
+      <c r="E65" s="1">
+        <v>44</v>
+      </c>
+      <c r="F65" s="1">
+        <v>8</v>
+      </c>
+      <c r="G65" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H65" s="1">
+        <v>180</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J65" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
+        <v>3061</v>
+      </c>
+      <c r="D66" s="1">
+        <v>9</v>
+      </c>
+      <c r="E66" s="1">
+        <v>45</v>
+      </c>
+      <c r="F66" s="1">
+        <v>8</v>
+      </c>
+      <c r="G66" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H66" s="1">
+        <v>180</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J66" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="1">
+        <v>3062</v>
+      </c>
+      <c r="D67" s="1">
+        <v>9</v>
+      </c>
+      <c r="E67" s="1">
+        <v>47</v>
+      </c>
+      <c r="F67" s="1">
+        <v>8</v>
+      </c>
+      <c r="G67" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H67" s="1">
+        <v>180</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J67" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="1">
+        <v>3063</v>
+      </c>
+      <c r="D68" s="1">
+        <v>9</v>
+      </c>
+      <c r="E68" s="1">
+        <v>49</v>
+      </c>
+      <c r="F68" s="1">
+        <v>8</v>
+      </c>
+      <c r="G68" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H68" s="1">
+        <v>180</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J68" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="1">
+        <v>3064</v>
+      </c>
+      <c r="D69" s="1">
+        <v>9</v>
+      </c>
+      <c r="E69" s="1">
+        <v>50</v>
+      </c>
+      <c r="F69" s="1">
+        <v>8</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H69" s="1">
+        <v>180</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J69" s="1">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="1">
+        <v>3065</v>
+      </c>
+      <c r="D70" s="1">
+        <v>9</v>
+      </c>
+      <c r="E70" s="1">
+        <v>41</v>
+      </c>
+      <c r="F70" s="1">
+        <v>9</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H70" s="1">
+        <v>200</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J70" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="1">
+        <v>3066</v>
+      </c>
+      <c r="D71" s="1">
+        <v>9</v>
+      </c>
+      <c r="E71" s="1">
+        <v>42</v>
+      </c>
+      <c r="F71" s="1">
+        <v>9</v>
+      </c>
+      <c r="G71" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H71" s="1">
+        <v>200</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J71" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="1">
+        <v>3067</v>
+      </c>
+      <c r="D72" s="1">
+        <v>9</v>
+      </c>
+      <c r="E72" s="1">
+        <v>43</v>
+      </c>
+      <c r="F72" s="1">
+        <v>9</v>
+      </c>
+      <c r="G72" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H72" s="1">
+        <v>200</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J72" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="1">
+        <v>3068</v>
+      </c>
+      <c r="D73" s="1">
+        <v>9</v>
+      </c>
+      <c r="E73" s="1">
+        <v>44</v>
+      </c>
+      <c r="F73" s="1">
+        <v>9</v>
+      </c>
+      <c r="G73" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H73" s="1">
+        <v>200</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J73" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="1">
+        <v>3069</v>
+      </c>
+      <c r="D74" s="1">
+        <v>9</v>
+      </c>
+      <c r="E74" s="1">
+        <v>45</v>
+      </c>
+      <c r="F74" s="1">
+        <v>9</v>
+      </c>
+      <c r="G74" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H74" s="1">
+        <v>200</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J74" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="1">
+        <v>3070</v>
+      </c>
+      <c r="D75" s="1">
+        <v>9</v>
+      </c>
+      <c r="E75" s="1">
+        <v>47</v>
+      </c>
+      <c r="F75" s="1">
+        <v>9</v>
+      </c>
+      <c r="G75" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H75" s="1">
+        <v>200</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J75" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="1">
+        <v>3071</v>
+      </c>
+      <c r="D76" s="1">
+        <v>9</v>
+      </c>
+      <c r="E76" s="1">
+        <v>49</v>
+      </c>
+      <c r="F76" s="1">
+        <v>9</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H76" s="1">
+        <v>200</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J76" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="1">
+        <v>3072</v>
+      </c>
+      <c r="D77" s="1">
+        <v>9</v>
+      </c>
+      <c r="E77" s="1">
+        <v>50</v>
+      </c>
+      <c r="F77" s="1">
+        <v>9</v>
+      </c>
+      <c r="G77" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H77" s="1">
+        <v>200</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J77" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="1">
+        <v>3073</v>
+      </c>
+      <c r="D78" s="1">
+        <v>9</v>
+      </c>
+      <c r="E78" s="1">
+        <v>41</v>
+      </c>
+      <c r="F78" s="1">
+        <v>10</v>
+      </c>
+      <c r="G78" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H78" s="1">
+        <v>200</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J78" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="1">
+        <v>3074</v>
+      </c>
+      <c r="D79" s="1">
+        <v>9</v>
+      </c>
+      <c r="E79" s="1">
+        <v>42</v>
+      </c>
+      <c r="F79" s="1">
+        <v>10</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H79" s="1">
+        <v>200</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J79" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="1">
+        <v>3075</v>
+      </c>
+      <c r="D80" s="1">
+        <v>9</v>
+      </c>
+      <c r="E80" s="1">
+        <v>43</v>
+      </c>
+      <c r="F80" s="1">
+        <v>10</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H80" s="1">
+        <v>200</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J80" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="1">
+        <v>3076</v>
+      </c>
+      <c r="D81" s="1">
+        <v>9</v>
+      </c>
+      <c r="E81" s="1">
+        <v>44</v>
+      </c>
+      <c r="F81" s="1">
+        <v>10</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H81" s="1">
+        <v>200</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J81" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="1">
+        <v>3077</v>
+      </c>
+      <c r="D82" s="1">
+        <v>9</v>
+      </c>
+      <c r="E82" s="1">
+        <v>45</v>
+      </c>
+      <c r="F82" s="1">
+        <v>10</v>
+      </c>
+      <c r="G82" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H82" s="1">
+        <v>200</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J82" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="1">
+        <v>3078</v>
+      </c>
+      <c r="D83" s="1">
+        <v>9</v>
+      </c>
+      <c r="E83" s="1">
+        <v>47</v>
+      </c>
+      <c r="F83" s="1">
+        <v>10</v>
+      </c>
+      <c r="G83" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H83" s="1">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J83" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="1">
+        <v>3079</v>
+      </c>
+      <c r="D84" s="1">
+        <v>9</v>
+      </c>
+      <c r="E84" s="1">
+        <v>49</v>
+      </c>
+      <c r="F84" s="1">
+        <v>10</v>
+      </c>
+      <c r="G84" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H84" s="1">
+        <v>200</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J84" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="1">
+        <v>3080</v>
+      </c>
+      <c r="D85" s="1">
+        <v>9</v>
+      </c>
+      <c r="E85" s="1">
+        <v>50</v>
+      </c>
+      <c r="F85" s="1">
+        <v>10</v>
+      </c>
+      <c r="G85" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H85" s="1">
+        <v>200</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J85" s="1">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
+      <c r="C86" s="1">
+        <v>3081</v>
+      </c>
+      <c r="D86" s="1">
+        <v>9</v>
+      </c>
+      <c r="E86" s="1">
+        <v>41</v>
+      </c>
+      <c r="F86" s="1">
+        <v>11</v>
+      </c>
+      <c r="G86" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H86" s="1">
+        <v>200</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J86" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:10">
+      <c r="C87" s="1">
+        <v>3082</v>
+      </c>
+      <c r="D87" s="1">
+        <v>9</v>
+      </c>
+      <c r="E87" s="1">
+        <v>42</v>
+      </c>
+      <c r="F87" s="1">
+        <v>11</v>
+      </c>
+      <c r="G87" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H87" s="1">
+        <v>200</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J87" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:10">
+      <c r="C88" s="1">
+        <v>3083</v>
+      </c>
+      <c r="D88" s="1">
+        <v>9</v>
+      </c>
+      <c r="E88" s="1">
+        <v>43</v>
+      </c>
+      <c r="F88" s="1">
+        <v>11</v>
+      </c>
+      <c r="G88" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H88" s="1">
+        <v>200</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J88" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
+      <c r="C89" s="1">
+        <v>3084</v>
+      </c>
+      <c r="D89" s="1">
+        <v>9</v>
+      </c>
+      <c r="E89" s="1">
+        <v>44</v>
+      </c>
+      <c r="F89" s="1">
+        <v>11</v>
+      </c>
+      <c r="G89" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H89" s="1">
+        <v>200</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J89" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
+      <c r="C90" s="1">
+        <v>3085</v>
+      </c>
+      <c r="D90" s="1">
+        <v>9</v>
+      </c>
+      <c r="E90" s="1">
+        <v>45</v>
+      </c>
+      <c r="F90" s="1">
+        <v>11</v>
+      </c>
+      <c r="G90" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H90" s="1">
+        <v>200</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J90" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:10">
+      <c r="C91" s="1">
+        <v>3086</v>
+      </c>
+      <c r="D91" s="1">
+        <v>9</v>
+      </c>
+      <c r="E91" s="1">
+        <v>47</v>
+      </c>
+      <c r="F91" s="1">
+        <v>11</v>
+      </c>
+      <c r="G91" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H91" s="1">
+        <v>200</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J91" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:10">
+      <c r="C92" s="1">
+        <v>3087</v>
+      </c>
+      <c r="D92" s="1">
+        <v>9</v>
+      </c>
+      <c r="E92" s="1">
+        <v>49</v>
+      </c>
+      <c r="F92" s="1">
+        <v>11</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H92" s="1">
+        <v>200</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J92" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
+      <c r="C93" s="1">
+        <v>3088</v>
+      </c>
+      <c r="D93" s="1">
+        <v>9</v>
+      </c>
+      <c r="E93" s="1">
+        <v>50</v>
+      </c>
+      <c r="F93" s="1">
+        <v>11</v>
+      </c>
+      <c r="G93" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H93" s="1">
+        <v>200</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J93" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:10">
+      <c r="C94" s="1">
+        <v>3089</v>
+      </c>
+      <c r="D94" s="1">
+        <v>9</v>
+      </c>
+      <c r="E94" s="1">
+        <v>41</v>
+      </c>
+      <c r="F94" s="1">
+        <v>12</v>
+      </c>
+      <c r="G94" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H94" s="1">
+        <v>200</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J94" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:10">
+      <c r="C95" s="1">
+        <v>3090</v>
+      </c>
+      <c r="D95" s="1">
+        <v>9</v>
+      </c>
+      <c r="E95" s="1">
+        <v>42</v>
+      </c>
+      <c r="F95" s="1">
+        <v>12</v>
+      </c>
+      <c r="G95" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H95" s="1">
+        <v>200</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J95" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:10">
+      <c r="C96" s="1">
+        <v>3091</v>
+      </c>
+      <c r="D96" s="1">
+        <v>9</v>
+      </c>
+      <c r="E96" s="1">
+        <v>43</v>
+      </c>
+      <c r="F96" s="1">
+        <v>12</v>
+      </c>
+      <c r="G96" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H96" s="1">
+        <v>200</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J96" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:10">
+      <c r="C97" s="1">
+        <v>3092</v>
+      </c>
+      <c r="D97" s="1">
+        <v>9</v>
+      </c>
+      <c r="E97" s="1">
+        <v>44</v>
+      </c>
+      <c r="F97" s="1">
+        <v>12</v>
+      </c>
+      <c r="G97" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H97" s="1">
+        <v>200</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J97" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:10">
+      <c r="C98" s="1">
+        <v>3093</v>
+      </c>
+      <c r="D98" s="1">
+        <v>9</v>
+      </c>
+      <c r="E98" s="1">
+        <v>45</v>
+      </c>
+      <c r="F98" s="1">
+        <v>12</v>
+      </c>
+      <c r="G98" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H98" s="1">
+        <v>200</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J98" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:10">
+      <c r="C99" s="1">
+        <v>3094</v>
+      </c>
+      <c r="D99" s="1">
+        <v>9</v>
+      </c>
+      <c r="E99" s="1">
+        <v>47</v>
+      </c>
+      <c r="F99" s="1">
+        <v>12</v>
+      </c>
+      <c r="G99" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H99" s="1">
+        <v>200</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J99" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:10">
+      <c r="C100" s="1">
+        <v>3095</v>
+      </c>
+      <c r="D100" s="1">
+        <v>9</v>
+      </c>
+      <c r="E100" s="1">
+        <v>49</v>
+      </c>
+      <c r="F100" s="1">
+        <v>12</v>
+      </c>
+      <c r="G100" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H100" s="1">
+        <v>200</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J100" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:10">
+      <c r="C101" s="1">
+        <v>3096</v>
+      </c>
+      <c r="D101" s="1">
+        <v>9</v>
+      </c>
+      <c r="E101" s="1">
+        <v>50</v>
+      </c>
+      <c r="F101" s="1">
+        <v>12</v>
+      </c>
+      <c r="G101" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H101" s="1">
+        <v>200</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J101" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:10">
+      <c r="C102" s="1">
+        <v>3097</v>
+      </c>
+      <c r="D102" s="1">
+        <v>9</v>
+      </c>
+      <c r="E102" s="1">
+        <v>41</v>
+      </c>
+      <c r="F102" s="1">
+        <v>13</v>
+      </c>
+      <c r="G102" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H102" s="1">
+        <v>200</v>
+      </c>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:10">
+      <c r="C103" s="1">
+        <v>3098</v>
+      </c>
+      <c r="D103" s="1">
+        <v>9</v>
+      </c>
+      <c r="E103" s="1">
+        <v>42</v>
+      </c>
+      <c r="F103" s="1">
+        <v>13</v>
+      </c>
+      <c r="G103" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H103" s="1">
+        <v>200</v>
+      </c>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:10">
+      <c r="C104" s="1">
+        <v>3099</v>
+      </c>
+      <c r="D104" s="1">
+        <v>9</v>
+      </c>
+      <c r="E104" s="1">
+        <v>43</v>
+      </c>
+      <c r="F104" s="1">
+        <v>13</v>
+      </c>
+      <c r="G104" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H104" s="1">
+        <v>200</v>
+      </c>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:10">
+      <c r="C105" s="1">
+        <v>3100</v>
+      </c>
+      <c r="D105" s="1">
+        <v>9</v>
+      </c>
+      <c r="E105" s="1">
+        <v>44</v>
+      </c>
+      <c r="F105" s="1">
+        <v>13</v>
+      </c>
+      <c r="G105" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H105" s="1">
+        <v>200</v>
+      </c>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:10">
+      <c r="C106" s="1">
+        <v>3101</v>
+      </c>
+      <c r="D106" s="1">
+        <v>9</v>
+      </c>
+      <c r="E106" s="1">
+        <v>45</v>
+      </c>
+      <c r="F106" s="1">
+        <v>13</v>
+      </c>
+      <c r="G106" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H106" s="1">
+        <v>200</v>
+      </c>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:10">
+      <c r="C107" s="1">
+        <v>3102</v>
+      </c>
+      <c r="D107" s="1">
+        <v>9</v>
+      </c>
+      <c r="E107" s="1">
+        <v>47</v>
+      </c>
+      <c r="F107" s="1">
+        <v>13</v>
+      </c>
+      <c r="G107" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H107" s="1">
+        <v>200</v>
+      </c>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:10">
+      <c r="C108" s="1">
+        <v>3103</v>
+      </c>
+      <c r="D108" s="1">
+        <v>9</v>
+      </c>
+      <c r="E108" s="1">
+        <v>49</v>
+      </c>
+      <c r="F108" s="1">
+        <v>13</v>
+      </c>
+      <c r="G108" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H108" s="1">
+        <v>200</v>
+      </c>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:10">
+      <c r="C109" s="1">
+        <v>3104</v>
+      </c>
+      <c r="D109" s="1">
+        <v>9</v>
+      </c>
+      <c r="E109" s="1">
+        <v>50</v>
+      </c>
+      <c r="F109" s="1">
+        <v>13</v>
+      </c>
+      <c r="G109" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H109" s="1">
+        <v>200</v>
+      </c>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:10">
+      <c r="C110" s="1">
+        <v>3105</v>
+      </c>
+      <c r="D110" s="1">
+        <v>9</v>
+      </c>
+      <c r="E110" s="1">
+        <v>41</v>
+      </c>
+      <c r="F110" s="1">
+        <v>14</v>
+      </c>
+      <c r="G110" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H110" s="1">
+        <v>200</v>
+      </c>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:10">
+      <c r="C111" s="1">
+        <v>3106</v>
+      </c>
+      <c r="D111" s="1">
+        <v>9</v>
+      </c>
+      <c r="E111" s="1">
+        <v>42</v>
+      </c>
+      <c r="F111" s="1">
+        <v>14</v>
+      </c>
+      <c r="G111" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H111" s="1">
+        <v>200</v>
+      </c>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:10">
+      <c r="C112" s="1">
+        <v>3107</v>
+      </c>
+      <c r="D112" s="1">
+        <v>9</v>
+      </c>
+      <c r="E112" s="1">
+        <v>43</v>
+      </c>
+      <c r="F112" s="1">
+        <v>14</v>
+      </c>
+      <c r="G112" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H112" s="1">
+        <v>200</v>
+      </c>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:10">
+      <c r="C113" s="1">
+        <v>3108</v>
+      </c>
+      <c r="D113" s="1">
+        <v>9</v>
+      </c>
+      <c r="E113" s="1">
+        <v>44</v>
+      </c>
+      <c r="F113" s="1">
+        <v>14</v>
+      </c>
+      <c r="G113" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H113" s="1">
+        <v>200</v>
+      </c>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:10">
+      <c r="C114" s="1">
+        <v>3109</v>
+      </c>
+      <c r="D114" s="1">
+        <v>9</v>
+      </c>
+      <c r="E114" s="1">
+        <v>45</v>
+      </c>
+      <c r="F114" s="1">
+        <v>14</v>
+      </c>
+      <c r="G114" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H114" s="1">
+        <v>200</v>
+      </c>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:10">
+      <c r="C115" s="1">
+        <v>3110</v>
+      </c>
+      <c r="D115" s="1">
+        <v>9</v>
+      </c>
+      <c r="E115" s="1">
+        <v>47</v>
+      </c>
+      <c r="F115" s="1">
+        <v>14</v>
+      </c>
+      <c r="G115" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H115" s="1">
+        <v>200</v>
+      </c>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:10">
+      <c r="C116" s="1">
+        <v>3111</v>
+      </c>
+      <c r="D116" s="1">
+        <v>9</v>
+      </c>
+      <c r="E116" s="1">
+        <v>49</v>
+      </c>
+      <c r="F116" s="1">
+        <v>14</v>
+      </c>
+      <c r="G116" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H116" s="1">
+        <v>200</v>
+      </c>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:10">
+      <c r="C117" s="1">
+        <v>3112</v>
+      </c>
+      <c r="D117" s="1">
+        <v>9</v>
+      </c>
+      <c r="E117" s="1">
+        <v>50</v>
+      </c>
+      <c r="F117" s="1">
+        <v>14</v>
+      </c>
+      <c r="G117" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H117" s="1">
+        <v>200</v>
+      </c>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:10">
+      <c r="C118" s="1">
+        <v>3113</v>
+      </c>
+      <c r="D118" s="1">
+        <v>9</v>
+      </c>
+      <c r="E118" s="1">
+        <v>41</v>
+      </c>
+      <c r="F118" s="1">
+        <v>15</v>
+      </c>
+      <c r="G118" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H118" s="1">
+        <v>200</v>
+      </c>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:10">
+      <c r="C119" s="1">
+        <v>3114</v>
+      </c>
+      <c r="D119" s="1">
+        <v>9</v>
+      </c>
+      <c r="E119" s="1">
+        <v>42</v>
+      </c>
+      <c r="F119" s="1">
+        <v>15</v>
+      </c>
+      <c r="G119" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H119" s="1">
+        <v>200</v>
+      </c>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:10">
+      <c r="C120" s="1">
+        <v>3115</v>
+      </c>
+      <c r="D120" s="1">
+        <v>9</v>
+      </c>
+      <c r="E120" s="1">
+        <v>43</v>
+      </c>
+      <c r="F120" s="1">
+        <v>15</v>
+      </c>
+      <c r="G120" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H120" s="1">
+        <v>200</v>
+      </c>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:10">
+      <c r="C121" s="1">
+        <v>3116</v>
+      </c>
+      <c r="D121" s="1">
+        <v>9</v>
+      </c>
+      <c r="E121" s="1">
+        <v>44</v>
+      </c>
+      <c r="F121" s="1">
+        <v>15</v>
+      </c>
+      <c r="G121" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H121" s="1">
+        <v>200</v>
+      </c>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:10">
+      <c r="C122" s="1">
+        <v>3117</v>
+      </c>
+      <c r="D122" s="1">
+        <v>9</v>
+      </c>
+      <c r="E122" s="1">
+        <v>45</v>
+      </c>
+      <c r="F122" s="1">
+        <v>15</v>
+      </c>
+      <c r="G122" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H122" s="1">
+        <v>200</v>
+      </c>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:10">
+      <c r="C123" s="1">
+        <v>3118</v>
+      </c>
+      <c r="D123" s="1">
+        <v>9</v>
+      </c>
+      <c r="E123" s="1">
+        <v>47</v>
+      </c>
+      <c r="F123" s="1">
+        <v>15</v>
+      </c>
+      <c r="G123" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H123" s="1">
+        <v>200</v>
+      </c>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:10">
+      <c r="C124" s="1">
+        <v>3119</v>
+      </c>
+      <c r="D124" s="1">
+        <v>9</v>
+      </c>
+      <c r="E124" s="1">
+        <v>49</v>
+      </c>
+      <c r="F124" s="1">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H124" s="1">
+        <v>200</v>
+      </c>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:10">
+      <c r="C125" s="1">
+        <v>3120</v>
+      </c>
+      <c r="D125" s="1">
+        <v>9</v>
+      </c>
+      <c r="E125" s="1">
+        <v>50</v>
+      </c>
+      <c r="F125" s="1">
+        <v>15</v>
+      </c>
+      <c r="G125" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H125" s="1">
+        <v>200</v>
+      </c>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:10">
+      <c r="C126" s="1">
+        <v>3121</v>
+      </c>
+      <c r="D126" s="1">
+        <v>9</v>
+      </c>
+      <c r="E126" s="1">
+        <v>41</v>
+      </c>
+      <c r="F126" s="1">
+        <v>16</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H126" s="1">
+        <v>200</v>
+      </c>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:10">
+      <c r="C127" s="1">
+        <v>3122</v>
+      </c>
+      <c r="D127" s="1">
+        <v>9</v>
+      </c>
+      <c r="E127" s="1">
+        <v>42</v>
+      </c>
+      <c r="F127" s="1">
+        <v>16</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H127" s="1">
+        <v>200</v>
+      </c>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:10">
+      <c r="C128" s="1">
+        <v>3123</v>
+      </c>
+      <c r="D128" s="1">
+        <v>9</v>
+      </c>
+      <c r="E128" s="1">
+        <v>43</v>
+      </c>
+      <c r="F128" s="1">
+        <v>16</v>
+      </c>
+      <c r="G128" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H128" s="1">
+        <v>200</v>
+      </c>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:10">
+      <c r="C129" s="1">
+        <v>3124</v>
+      </c>
+      <c r="D129" s="1">
+        <v>9</v>
+      </c>
+      <c r="E129" s="1">
+        <v>44</v>
+      </c>
+      <c r="F129" s="1">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H129" s="1">
+        <v>200</v>
+      </c>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:10">
+      <c r="C130" s="1">
+        <v>3125</v>
+      </c>
+      <c r="D130" s="1">
+        <v>9</v>
+      </c>
+      <c r="E130" s="1">
+        <v>45</v>
+      </c>
+      <c r="F130" s="1">
+        <v>16</v>
+      </c>
+      <c r="G130" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H130" s="1">
+        <v>200</v>
+      </c>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:10">
+      <c r="C131" s="1">
+        <v>3126</v>
+      </c>
+      <c r="D131" s="1">
+        <v>9</v>
+      </c>
+      <c r="E131" s="1">
+        <v>47</v>
+      </c>
+      <c r="F131" s="1">
+        <v>16</v>
+      </c>
+      <c r="G131" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H131" s="1">
+        <v>200</v>
+      </c>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:10">
+      <c r="C132" s="1">
+        <v>3127</v>
+      </c>
+      <c r="D132" s="1">
+        <v>9</v>
+      </c>
+      <c r="E132" s="1">
+        <v>49</v>
+      </c>
+      <c r="F132" s="1">
+        <v>16</v>
+      </c>
+      <c r="G132" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H132" s="1">
+        <v>200</v>
+      </c>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:10">
+      <c r="C133" s="1">
+        <v>3128</v>
+      </c>
+      <c r="D133" s="1">
+        <v>9</v>
+      </c>
+      <c r="E133" s="1">
+        <v>50</v>
+      </c>
+      <c r="F133" s="1">
+        <v>16</v>
+      </c>
+      <c r="G133" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H133" s="1">
+        <v>200</v>
+      </c>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:10">
+      <c r="C134" s="1">
+        <v>3129</v>
+      </c>
+      <c r="D134" s="1">
+        <v>9</v>
+      </c>
+      <c r="E134" s="1">
+        <v>41</v>
+      </c>
+      <c r="F134" s="1">
+        <v>17</v>
+      </c>
+      <c r="G134" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H134" s="1">
+        <v>200</v>
+      </c>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:10">
+      <c r="C135" s="1">
+        <v>3130</v>
+      </c>
+      <c r="D135" s="1">
+        <v>9</v>
+      </c>
+      <c r="E135" s="1">
+        <v>42</v>
+      </c>
+      <c r="F135" s="1">
+        <v>17</v>
+      </c>
+      <c r="G135" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H135" s="1">
+        <v>200</v>
+      </c>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:10">
+      <c r="C136" s="1">
+        <v>3131</v>
+      </c>
+      <c r="D136" s="1">
+        <v>9</v>
+      </c>
+      <c r="E136" s="1">
+        <v>43</v>
+      </c>
+      <c r="F136" s="1">
+        <v>17</v>
+      </c>
+      <c r="G136" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H136" s="1">
+        <v>200</v>
+      </c>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:10">
+      <c r="C137" s="1">
+        <v>3132</v>
+      </c>
+      <c r="D137" s="1">
+        <v>9</v>
+      </c>
+      <c r="E137" s="1">
+        <v>44</v>
+      </c>
+      <c r="F137" s="1">
+        <v>17</v>
+      </c>
+      <c r="G137" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H137" s="1">
+        <v>200</v>
+      </c>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:10">
+      <c r="C138" s="1">
+        <v>3133</v>
+      </c>
+      <c r="D138" s="1">
+        <v>9</v>
+      </c>
+      <c r="E138" s="1">
+        <v>45</v>
+      </c>
+      <c r="F138" s="1">
+        <v>17</v>
+      </c>
+      <c r="G138" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H138" s="1">
+        <v>200</v>
+      </c>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:10">
+      <c r="C139" s="1">
+        <v>3134</v>
+      </c>
+      <c r="D139" s="1">
+        <v>9</v>
+      </c>
+      <c r="E139" s="1">
+        <v>47</v>
+      </c>
+      <c r="F139" s="1">
+        <v>17</v>
+      </c>
+      <c r="G139" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H139" s="1">
+        <v>200</v>
+      </c>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:10">
+      <c r="C140" s="1">
+        <v>3135</v>
+      </c>
+      <c r="D140" s="1">
+        <v>9</v>
+      </c>
+      <c r="E140" s="1">
+        <v>49</v>
+      </c>
+      <c r="F140" s="1">
+        <v>17</v>
+      </c>
+      <c r="G140" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H140" s="1">
+        <v>200</v>
+      </c>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:10">
+      <c r="C141" s="1">
+        <v>3136</v>
+      </c>
+      <c r="D141" s="1">
+        <v>9</v>
+      </c>
+      <c r="E141" s="1">
+        <v>50</v>
+      </c>
+      <c r="F141" s="1">
+        <v>17</v>
+      </c>
+      <c r="G141" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H141" s="1">
+        <v>200</v>
+      </c>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:10">
+      <c r="C142" s="1">
+        <v>3137</v>
+      </c>
+      <c r="D142" s="1">
+        <v>9</v>
+      </c>
+      <c r="E142" s="1">
+        <v>41</v>
+      </c>
+      <c r="F142" s="1">
+        <v>18</v>
+      </c>
+      <c r="G142" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H142" s="1">
+        <v>200</v>
+      </c>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:10">
+      <c r="C143" s="1">
+        <v>3138</v>
+      </c>
+      <c r="D143" s="1">
+        <v>9</v>
+      </c>
+      <c r="E143" s="1">
+        <v>42</v>
+      </c>
+      <c r="F143" s="1">
+        <v>18</v>
+      </c>
+      <c r="G143" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H143" s="1">
+        <v>200</v>
+      </c>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:10">
+      <c r="C144" s="1">
+        <v>3139</v>
+      </c>
+      <c r="D144" s="1">
+        <v>9</v>
+      </c>
+      <c r="E144" s="1">
+        <v>43</v>
+      </c>
+      <c r="F144" s="1">
+        <v>18</v>
+      </c>
+      <c r="G144" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H144" s="1">
+        <v>200</v>
+      </c>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:10">
+      <c r="C145" s="1">
+        <v>3140</v>
+      </c>
+      <c r="D145" s="1">
+        <v>9</v>
+      </c>
+      <c r="E145" s="1">
+        <v>44</v>
+      </c>
+      <c r="F145" s="1">
+        <v>18</v>
+      </c>
+      <c r="G145" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H145" s="1">
+        <v>200</v>
+      </c>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:10">
+      <c r="C146" s="1">
+        <v>3141</v>
+      </c>
+      <c r="D146" s="1">
+        <v>9</v>
+      </c>
+      <c r="E146" s="1">
+        <v>45</v>
+      </c>
+      <c r="F146" s="1">
+        <v>18</v>
+      </c>
+      <c r="G146" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H146" s="1">
+        <v>200</v>
+      </c>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:10">
+      <c r="C147" s="1">
+        <v>3142</v>
+      </c>
+      <c r="D147" s="1">
+        <v>9</v>
+      </c>
+      <c r="E147" s="1">
+        <v>47</v>
+      </c>
+      <c r="F147" s="1">
+        <v>18</v>
+      </c>
+      <c r="G147" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H147" s="1">
+        <v>200</v>
+      </c>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:10">
+      <c r="C148" s="1">
+        <v>3143</v>
+      </c>
+      <c r="D148" s="1">
+        <v>9</v>
+      </c>
+      <c r="E148" s="1">
+        <v>49</v>
+      </c>
+      <c r="F148" s="1">
+        <v>18</v>
+      </c>
+      <c r="G148" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H148" s="1">
+        <v>200</v>
+      </c>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:10">
+      <c r="C149" s="1">
+        <v>3144</v>
+      </c>
+      <c r="D149" s="1">
+        <v>9</v>
+      </c>
+      <c r="E149" s="1">
+        <v>50</v>
+      </c>
+      <c r="F149" s="1">
+        <v>18</v>
+      </c>
+      <c r="G149" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H149" s="1">
+        <v>200</v>
+      </c>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:10">
+      <c r="C150" s="1">
+        <v>3145</v>
+      </c>
+      <c r="D150" s="1">
+        <v>9</v>
+      </c>
+      <c r="E150" s="1">
+        <v>41</v>
+      </c>
+      <c r="F150" s="1">
+        <v>19</v>
+      </c>
+      <c r="G150" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H150" s="1">
+        <v>200</v>
+      </c>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:10">
+      <c r="C151" s="1">
+        <v>3146</v>
+      </c>
+      <c r="D151" s="1">
+        <v>9</v>
+      </c>
+      <c r="E151" s="1">
+        <v>42</v>
+      </c>
+      <c r="F151" s="1">
+        <v>19</v>
+      </c>
+      <c r="G151" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H151" s="1">
+        <v>200</v>
+      </c>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:10">
+      <c r="C152" s="1">
+        <v>3147</v>
+      </c>
+      <c r="D152" s="1">
+        <v>9</v>
+      </c>
+      <c r="E152" s="1">
+        <v>43</v>
+      </c>
+      <c r="F152" s="1">
+        <v>19</v>
+      </c>
+      <c r="G152" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H152" s="1">
+        <v>200</v>
+      </c>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:10">
+      <c r="C153" s="1">
+        <v>3148</v>
+      </c>
+      <c r="D153" s="1">
+        <v>9</v>
+      </c>
+      <c r="E153" s="1">
+        <v>44</v>
+      </c>
+      <c r="F153" s="1">
+        <v>19</v>
+      </c>
+      <c r="G153" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H153" s="1">
+        <v>200</v>
+      </c>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:10">
+      <c r="C154" s="1">
+        <v>3149</v>
+      </c>
+      <c r="D154" s="1">
+        <v>9</v>
+      </c>
+      <c r="E154" s="1">
+        <v>45</v>
+      </c>
+      <c r="F154" s="1">
+        <v>19</v>
+      </c>
+      <c r="G154" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H154" s="1">
+        <v>200</v>
+      </c>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:10">
+      <c r="C155" s="1">
+        <v>3150</v>
+      </c>
+      <c r="D155" s="1">
+        <v>9</v>
+      </c>
+      <c r="E155" s="1">
+        <v>47</v>
+      </c>
+      <c r="F155" s="1">
+        <v>19</v>
+      </c>
+      <c r="G155" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H155" s="1">
+        <v>200</v>
+      </c>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:10">
+      <c r="C156" s="1">
+        <v>3151</v>
+      </c>
+      <c r="D156" s="1">
+        <v>9</v>
+      </c>
+      <c r="E156" s="1">
+        <v>49</v>
+      </c>
+      <c r="F156" s="1">
+        <v>19</v>
+      </c>
+      <c r="G156" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H156" s="1">
+        <v>200</v>
+      </c>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:10">
+      <c r="C157" s="1">
+        <v>3152</v>
+      </c>
+      <c r="D157" s="1">
+        <v>9</v>
+      </c>
+      <c r="E157" s="1">
+        <v>50</v>
+      </c>
+      <c r="F157" s="1">
+        <v>19</v>
+      </c>
+      <c r="G157" s="1">
+        <v>4038</v>
+      </c>
+      <c r="H157" s="1">
+        <v>200</v>
+      </c>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I5:J5 C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:L53"/>
@@ -12974,1252 +18197,1252 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="1">
-        <v>3001</v>
+        <v>4001</v>
       </c>
       <c r="D6" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J6" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="1">
-        <v>3002</v>
+        <v>4002</v>
       </c>
       <c r="D7" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J7" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="1">
-        <v>3003</v>
+        <v>4003</v>
       </c>
       <c r="D8" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J8" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
-        <v>3004</v>
+        <v>4004</v>
       </c>
       <c r="D9" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J9" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
-        <v>3005</v>
+        <v>4005</v>
       </c>
       <c r="D10" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J10" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
-        <v>3006</v>
+        <v>4006</v>
       </c>
       <c r="D11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J11" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
-        <v>3007</v>
+        <v>4007</v>
       </c>
       <c r="D12" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J12" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C13" s="1">
-        <v>3008</v>
+        <v>4008</v>
       </c>
       <c r="D13" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J13" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C14" s="1">
-        <v>3009</v>
+        <v>4009</v>
       </c>
       <c r="D14" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F14" s="1">
         <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H14" s="1">
         <v>40</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J14" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C15" s="1">
-        <v>3010</v>
+        <v>4010</v>
       </c>
       <c r="D15" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H15" s="1">
         <v>40</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J15" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C16" s="1">
-        <v>3011</v>
+        <v>4011</v>
       </c>
       <c r="D16" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F16" s="1">
         <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H16" s="1">
         <v>40</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J16" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C17" s="1">
-        <v>3012</v>
+        <v>4012</v>
       </c>
       <c r="D17" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1">
         <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H17" s="1">
         <v>40</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J17" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C18" s="1">
-        <v>3013</v>
+        <v>4013</v>
       </c>
       <c r="D18" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F18" s="1">
         <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H18" s="1">
         <v>40</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J18" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C19" s="1">
-        <v>3014</v>
+        <v>4014</v>
       </c>
       <c r="D19" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F19" s="1">
         <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H19" s="1">
         <v>40</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J19" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C20" s="1">
-        <v>3015</v>
+        <v>4015</v>
       </c>
       <c r="D20" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1">
         <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H20" s="1">
         <v>40</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J20" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C21" s="1">
-        <v>3016</v>
+        <v>4016</v>
       </c>
       <c r="D21" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F21" s="1">
         <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H21" s="1">
         <v>40</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J21" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C22" s="1">
-        <v>3017</v>
+        <v>4017</v>
       </c>
       <c r="D22" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H22" s="1">
         <v>60</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J22" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C23" s="1">
-        <v>3018</v>
+        <v>4018</v>
       </c>
       <c r="D23" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="1">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
       </c>
       <c r="G23" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H23" s="1">
         <v>60</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J23" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C24" s="1">
-        <v>3019</v>
+        <v>4019</v>
       </c>
       <c r="D24" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
       </c>
       <c r="G24" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H24" s="1">
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J24" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C25" s="1">
-        <v>3020</v>
+        <v>4020</v>
       </c>
       <c r="D25" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F25" s="1">
         <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H25" s="1">
         <v>60</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J25" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C26" s="1">
-        <v>3021</v>
+        <v>4021</v>
       </c>
       <c r="D26" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F26" s="1">
         <v>3</v>
       </c>
       <c r="G26" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H26" s="1">
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J26" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C27" s="1">
-        <v>3022</v>
+        <v>4022</v>
       </c>
       <c r="D27" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F27" s="1">
         <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H27" s="1">
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J27" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C28" s="1">
-        <v>3023</v>
+        <v>4023</v>
       </c>
       <c r="D28" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
       </c>
       <c r="G28" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H28" s="1">
         <v>60</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J28" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C29" s="1">
-        <v>3024</v>
+        <v>4024</v>
       </c>
       <c r="D29" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F29" s="1">
         <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H29" s="1">
         <v>60</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J29" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C30" s="1">
-        <v>3025</v>
+        <v>4025</v>
       </c>
       <c r="D30" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" s="1">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F30" s="1">
         <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H30" s="1">
         <v>80</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J30" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C31" s="1">
-        <v>3026</v>
+        <v>4026</v>
       </c>
       <c r="D31" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" s="1">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F31" s="1">
         <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H31" s="1">
         <v>80</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J31" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C32" s="1">
-        <v>3027</v>
+        <v>4027</v>
       </c>
       <c r="D32" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E32" s="1">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H32" s="1">
         <v>80</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J32" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C33" s="1">
-        <v>3028</v>
+        <v>4028</v>
       </c>
       <c r="D33" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F33" s="1">
         <v>4</v>
       </c>
       <c r="G33" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H33" s="1">
         <v>80</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J33" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C34" s="1">
-        <v>3029</v>
+        <v>4029</v>
       </c>
       <c r="D34" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F34" s="1">
         <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H34" s="1">
         <v>80</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J34" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C35" s="1">
-        <v>3030</v>
+        <v>4030</v>
       </c>
       <c r="D35" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F35" s="1">
         <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H35" s="1">
         <v>80</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J35" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C36" s="1">
-        <v>3031</v>
+        <v>4031</v>
       </c>
       <c r="D36" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F36" s="1">
         <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H36" s="1">
         <v>80</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J36" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C37" s="1">
-        <v>3032</v>
+        <v>4032</v>
       </c>
       <c r="D37" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1">
         <v>4</v>
       </c>
       <c r="G37" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H37" s="1">
         <v>80</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J37" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C38" s="1">
-        <v>3033</v>
+        <v>4033</v>
       </c>
       <c r="D38" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38" s="1">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F38" s="1">
         <v>5</v>
       </c>
       <c r="G38" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H38" s="1">
         <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J38" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C39" s="1">
-        <v>3034</v>
+        <v>4034</v>
       </c>
       <c r="D39" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" s="1">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F39" s="1">
         <v>5</v>
       </c>
       <c r="G39" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H39" s="1">
         <v>100</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J39" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C40" s="1">
-        <v>3035</v>
+        <v>4035</v>
       </c>
       <c r="D40" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" s="1">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
       </c>
       <c r="G40" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H40" s="1">
         <v>100</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J40" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C41" s="1">
-        <v>3036</v>
+        <v>4036</v>
       </c>
       <c r="D41" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E41" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F41" s="1">
         <v>5</v>
       </c>
       <c r="G41" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H41" s="1">
         <v>100</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J41" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C42" s="1">
-        <v>3037</v>
+        <v>4037</v>
       </c>
       <c r="D42" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F42" s="1">
         <v>5</v>
       </c>
       <c r="G42" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H42" s="1">
         <v>100</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J42" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C43" s="1">
-        <v>3038</v>
+        <v>4038</v>
       </c>
       <c r="D43" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F43" s="1">
         <v>5</v>
       </c>
       <c r="G43" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H43" s="1">
         <v>100</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J43" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C44" s="1">
-        <v>3039</v>
+        <v>4039</v>
       </c>
       <c r="D44" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F44" s="1">
         <v>5</v>
       </c>
       <c r="G44" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H44" s="1">
         <v>100</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J44" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C45" s="1">
-        <v>3040</v>
+        <v>4040</v>
       </c>
       <c r="D45" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F45" s="1">
         <v>5</v>
       </c>
       <c r="G45" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H45" s="1">
         <v>100</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J45" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C46" s="1">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="D46" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46" s="1">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F46" s="1">
         <v>6</v>
       </c>
       <c r="G46" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H46" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J46" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C47" s="1">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="D47" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47" s="1">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F47" s="1">
         <v>6</v>
       </c>
       <c r="G47" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H47" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J47" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C48" s="1">
-        <v>3043</v>
+        <v>4043</v>
       </c>
       <c r="D48" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E48" s="1">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F48" s="1">
         <v>6</v>
       </c>
       <c r="G48" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H48" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J48" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C49" s="1">
-        <v>3044</v>
+        <v>4044</v>
       </c>
       <c r="D49" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E49" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F49" s="1">
         <v>6</v>
       </c>
       <c r="G49" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H49" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J49" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C50" s="1">
-        <v>3045</v>
+        <v>4045</v>
       </c>
       <c r="D50" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E50" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F50" s="1">
         <v>6</v>
       </c>
       <c r="G50" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H50" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J50" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C51" s="1">
-        <v>3046</v>
+        <v>4046</v>
       </c>
       <c r="D51" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F51" s="1">
         <v>6</v>
       </c>
       <c r="G51" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H51" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J51" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C52" s="1">
-        <v>3047</v>
+        <v>4047</v>
       </c>
       <c r="D52" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E52" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F52" s="1">
         <v>6</v>
       </c>
       <c r="G52" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H52" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J52" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C53" s="1">
-        <v>3048</v>
+        <v>4048</v>
       </c>
       <c r="D53" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E53" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1">
         <v>6</v>
       </c>
       <c r="G53" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="H53" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J53" s="1">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="红色" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="150">
   <si>
     <t>_Id</t>
   </si>
@@ -463,6 +463,24 @@
   </si>
   <si>
     <t>50000125</t>
+  </si>
+  <si>
+    <t>50000126</t>
+  </si>
+  <si>
+    <t>50000127</t>
+  </si>
+  <si>
+    <t>50000128</t>
+  </si>
+  <si>
+    <t>50000129</t>
+  </si>
+  <si>
+    <t>50000130</t>
+  </si>
+  <si>
+    <t>50000131</t>
   </si>
 </sst>
 </file>
@@ -16759,7 +16777,9 @@
       <c r="H102" s="1">
         <v>200</v>
       </c>
-      <c r="I102" s="1"/>
+      <c r="I102" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J102" s="1">
         <v>14000</v>
       </c>
@@ -16783,7 +16803,9 @@
       <c r="H103" s="1">
         <v>200</v>
       </c>
-      <c r="I103" s="1"/>
+      <c r="I103" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J103" s="1">
         <v>14000</v>
       </c>
@@ -16807,7 +16829,9 @@
       <c r="H104" s="1">
         <v>200</v>
       </c>
-      <c r="I104" s="1"/>
+      <c r="I104" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J104" s="1">
         <v>14000</v>
       </c>
@@ -16831,7 +16855,9 @@
       <c r="H105" s="1">
         <v>200</v>
       </c>
-      <c r="I105" s="1"/>
+      <c r="I105" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J105" s="1">
         <v>14000</v>
       </c>
@@ -16855,7 +16881,9 @@
       <c r="H106" s="1">
         <v>200</v>
       </c>
-      <c r="I106" s="1"/>
+      <c r="I106" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J106" s="1">
         <v>14000</v>
       </c>
@@ -16879,7 +16907,9 @@
       <c r="H107" s="1">
         <v>200</v>
       </c>
-      <c r="I107" s="1"/>
+      <c r="I107" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J107" s="1">
         <v>14000</v>
       </c>
@@ -16903,7 +16933,9 @@
       <c r="H108" s="1">
         <v>200</v>
       </c>
-      <c r="I108" s="1"/>
+      <c r="I108" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J108" s="1">
         <v>14000</v>
       </c>
@@ -16927,7 +16959,9 @@
       <c r="H109" s="1">
         <v>200</v>
       </c>
-      <c r="I109" s="1"/>
+      <c r="I109" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J109" s="1">
         <v>14000</v>
       </c>
@@ -16951,7 +16985,9 @@
       <c r="H110" s="1">
         <v>200</v>
       </c>
-      <c r="I110" s="1"/>
+      <c r="I110" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J110" s="1">
         <v>15000</v>
       </c>
@@ -16975,7 +17011,9 @@
       <c r="H111" s="1">
         <v>200</v>
       </c>
-      <c r="I111" s="1"/>
+      <c r="I111" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J111" s="1">
         <v>15000</v>
       </c>
@@ -16999,7 +17037,9 @@
       <c r="H112" s="1">
         <v>200</v>
       </c>
-      <c r="I112" s="1"/>
+      <c r="I112" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J112" s="1">
         <v>15000</v>
       </c>
@@ -17023,7 +17063,9 @@
       <c r="H113" s="1">
         <v>200</v>
       </c>
-      <c r="I113" s="1"/>
+      <c r="I113" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J113" s="1">
         <v>15000</v>
       </c>
@@ -17047,7 +17089,9 @@
       <c r="H114" s="1">
         <v>200</v>
       </c>
-      <c r="I114" s="1"/>
+      <c r="I114" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J114" s="1">
         <v>15000</v>
       </c>
@@ -17071,7 +17115,9 @@
       <c r="H115" s="1">
         <v>200</v>
       </c>
-      <c r="I115" s="1"/>
+      <c r="I115" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J115" s="1">
         <v>15000</v>
       </c>
@@ -17095,7 +17141,9 @@
       <c r="H116" s="1">
         <v>200</v>
       </c>
-      <c r="I116" s="1"/>
+      <c r="I116" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J116" s="1">
         <v>15000</v>
       </c>
@@ -17119,7 +17167,9 @@
       <c r="H117" s="1">
         <v>200</v>
       </c>
-      <c r="I117" s="1"/>
+      <c r="I117" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="J117" s="1">
         <v>15000</v>
       </c>
@@ -17143,7 +17193,9 @@
       <c r="H118" s="1">
         <v>200</v>
       </c>
-      <c r="I118" s="1"/>
+      <c r="I118" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J118" s="1">
         <v>16000</v>
       </c>
@@ -17167,7 +17219,9 @@
       <c r="H119" s="1">
         <v>200</v>
       </c>
-      <c r="I119" s="1"/>
+      <c r="I119" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J119" s="1">
         <v>16000</v>
       </c>
@@ -17191,7 +17245,9 @@
       <c r="H120" s="1">
         <v>200</v>
       </c>
-      <c r="I120" s="1"/>
+      <c r="I120" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J120" s="1">
         <v>16000</v>
       </c>
@@ -17215,7 +17271,9 @@
       <c r="H121" s="1">
         <v>200</v>
       </c>
-      <c r="I121" s="1"/>
+      <c r="I121" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J121" s="1">
         <v>16000</v>
       </c>
@@ -17239,7 +17297,9 @@
       <c r="H122" s="1">
         <v>200</v>
       </c>
-      <c r="I122" s="1"/>
+      <c r="I122" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J122" s="1">
         <v>16000</v>
       </c>
@@ -17263,7 +17323,9 @@
       <c r="H123" s="1">
         <v>200</v>
       </c>
-      <c r="I123" s="1"/>
+      <c r="I123" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J123" s="1">
         <v>16000</v>
       </c>
@@ -17287,7 +17349,9 @@
       <c r="H124" s="1">
         <v>200</v>
       </c>
-      <c r="I124" s="1"/>
+      <c r="I124" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J124" s="1">
         <v>16000</v>
       </c>
@@ -17311,7 +17375,9 @@
       <c r="H125" s="1">
         <v>200</v>
       </c>
-      <c r="I125" s="1"/>
+      <c r="I125" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J125" s="1">
         <v>16000</v>
       </c>
@@ -17335,7 +17401,9 @@
       <c r="H126" s="1">
         <v>200</v>
       </c>
-      <c r="I126" s="1"/>
+      <c r="I126" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J126" s="1">
         <v>17000</v>
       </c>
@@ -17359,7 +17427,9 @@
       <c r="H127" s="1">
         <v>200</v>
       </c>
-      <c r="I127" s="1"/>
+      <c r="I127" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J127" s="1">
         <v>17000</v>
       </c>
@@ -17383,7 +17453,9 @@
       <c r="H128" s="1">
         <v>200</v>
       </c>
-      <c r="I128" s="1"/>
+      <c r="I128" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J128" s="1">
         <v>17000</v>
       </c>
@@ -17407,7 +17479,9 @@
       <c r="H129" s="1">
         <v>200</v>
       </c>
-      <c r="I129" s="1"/>
+      <c r="I129" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J129" s="1">
         <v>17000</v>
       </c>
@@ -17431,7 +17505,9 @@
       <c r="H130" s="1">
         <v>200</v>
       </c>
-      <c r="I130" s="1"/>
+      <c r="I130" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J130" s="1">
         <v>17000</v>
       </c>
@@ -17455,7 +17531,9 @@
       <c r="H131" s="1">
         <v>200</v>
       </c>
-      <c r="I131" s="1"/>
+      <c r="I131" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J131" s="1">
         <v>17000</v>
       </c>
@@ -17479,7 +17557,9 @@
       <c r="H132" s="1">
         <v>200</v>
       </c>
-      <c r="I132" s="1"/>
+      <c r="I132" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J132" s="1">
         <v>17000</v>
       </c>
@@ -17503,7 +17583,9 @@
       <c r="H133" s="1">
         <v>200</v>
       </c>
-      <c r="I133" s="1"/>
+      <c r="I133" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J133" s="1">
         <v>17000</v>
       </c>
@@ -17527,7 +17609,9 @@
       <c r="H134" s="1">
         <v>200</v>
       </c>
-      <c r="I134" s="1"/>
+      <c r="I134" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J134" s="1">
         <v>18000</v>
       </c>
@@ -17551,7 +17635,9 @@
       <c r="H135" s="1">
         <v>200</v>
       </c>
-      <c r="I135" s="1"/>
+      <c r="I135" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J135" s="1">
         <v>18000</v>
       </c>
@@ -17575,7 +17661,9 @@
       <c r="H136" s="1">
         <v>200</v>
       </c>
-      <c r="I136" s="1"/>
+      <c r="I136" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J136" s="1">
         <v>18000</v>
       </c>
@@ -17599,7 +17687,9 @@
       <c r="H137" s="1">
         <v>200</v>
       </c>
-      <c r="I137" s="1"/>
+      <c r="I137" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J137" s="1">
         <v>18000</v>
       </c>
@@ -17623,7 +17713,9 @@
       <c r="H138" s="1">
         <v>200</v>
       </c>
-      <c r="I138" s="1"/>
+      <c r="I138" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J138" s="1">
         <v>18000</v>
       </c>
@@ -17647,7 +17739,9 @@
       <c r="H139" s="1">
         <v>200</v>
       </c>
-      <c r="I139" s="1"/>
+      <c r="I139" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J139" s="1">
         <v>18000</v>
       </c>
@@ -17671,7 +17765,9 @@
       <c r="H140" s="1">
         <v>200</v>
       </c>
-      <c r="I140" s="1"/>
+      <c r="I140" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J140" s="1">
         <v>18000</v>
       </c>
@@ -17695,7 +17791,9 @@
       <c r="H141" s="1">
         <v>200</v>
       </c>
-      <c r="I141" s="1"/>
+      <c r="I141" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="J141" s="1">
         <v>18000</v>
       </c>
@@ -17719,7 +17817,9 @@
       <c r="H142" s="1">
         <v>200</v>
       </c>
-      <c r="I142" s="1"/>
+      <c r="I142" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J142" s="1">
         <v>19000</v>
       </c>
@@ -17743,7 +17843,9 @@
       <c r="H143" s="1">
         <v>200</v>
       </c>
-      <c r="I143" s="1"/>
+      <c r="I143" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J143" s="1">
         <v>19000</v>
       </c>
@@ -17767,7 +17869,9 @@
       <c r="H144" s="1">
         <v>200</v>
       </c>
-      <c r="I144" s="1"/>
+      <c r="I144" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J144" s="1">
         <v>19000</v>
       </c>
@@ -17791,7 +17895,9 @@
       <c r="H145" s="1">
         <v>200</v>
       </c>
-      <c r="I145" s="1"/>
+      <c r="I145" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J145" s="1">
         <v>19000</v>
       </c>
@@ -17815,7 +17921,9 @@
       <c r="H146" s="1">
         <v>200</v>
       </c>
-      <c r="I146" s="1"/>
+      <c r="I146" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J146" s="1">
         <v>19000</v>
       </c>
@@ -17839,7 +17947,9 @@
       <c r="H147" s="1">
         <v>200</v>
       </c>
-      <c r="I147" s="1"/>
+      <c r="I147" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J147" s="1">
         <v>19000</v>
       </c>
@@ -17863,7 +17973,9 @@
       <c r="H148" s="1">
         <v>200</v>
       </c>
-      <c r="I148" s="1"/>
+      <c r="I148" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J148" s="1">
         <v>19000</v>
       </c>
@@ -17887,7 +17999,9 @@
       <c r="H149" s="1">
         <v>200</v>
       </c>
-      <c r="I149" s="1"/>
+      <c r="I149" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J149" s="1">
         <v>19000</v>
       </c>
@@ -17911,7 +18025,9 @@
       <c r="H150" s="1">
         <v>200</v>
       </c>
-      <c r="I150" s="1"/>
+      <c r="I150" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J150" s="1">
         <v>20000</v>
       </c>
@@ -17935,7 +18051,9 @@
       <c r="H151" s="1">
         <v>200</v>
       </c>
-      <c r="I151" s="1"/>
+      <c r="I151" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J151" s="1">
         <v>20000</v>
       </c>
@@ -17959,7 +18077,9 @@
       <c r="H152" s="1">
         <v>200</v>
       </c>
-      <c r="I152" s="1"/>
+      <c r="I152" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J152" s="1">
         <v>20000</v>
       </c>
@@ -17983,7 +18103,9 @@
       <c r="H153" s="1">
         <v>200</v>
       </c>
-      <c r="I153" s="1"/>
+      <c r="I153" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J153" s="1">
         <v>20000</v>
       </c>
@@ -18007,7 +18129,9 @@
       <c r="H154" s="1">
         <v>200</v>
       </c>
-      <c r="I154" s="1"/>
+      <c r="I154" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J154" s="1">
         <v>20000</v>
       </c>
@@ -18031,7 +18155,9 @@
       <c r="H155" s="1">
         <v>200</v>
       </c>
-      <c r="I155" s="1"/>
+      <c r="I155" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J155" s="1">
         <v>20000</v>
       </c>
@@ -18055,7 +18181,9 @@
       <c r="H156" s="1">
         <v>200</v>
       </c>
-      <c r="I156" s="1"/>
+      <c r="I156" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J156" s="1">
         <v>20000</v>
       </c>
@@ -18079,7 +18207,9 @@
       <c r="H157" s="1">
         <v>200</v>
       </c>
-      <c r="I157" s="1"/>
+      <c r="I157" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="J157" s="1">
         <v>20000</v>
       </c>
